--- a/Database-V-25-06-2026.xlsx
+++ b/Database-V-25-06-2026.xlsx
@@ -8,28 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sightlinemedia-my.sharepoint.com/personal/lconord_lydech_com/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{8FA6B830-9F8D-4CD6-A0E0-F8B525334B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F920B2FD-1C7A-4D77-97A6-38FE7ED28055}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{8FA6B830-9F8D-4CD6-A0E0-F8B525334B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D01B4A98-87F0-486B-99C4-70721A9FA7A0}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GNRL Characteristics" sheetId="1" r:id="rId1"/>
-    <sheet name="DATA " sheetId="2" r:id="rId2"/>
+    <sheet name="ABSORPTION" sheetId="2" r:id="rId2"/>
     <sheet name="STL" sheetId="3" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'GNRL Characteristics'!$B$7:$T$25</definedName>
     <definedName name="S.1" localSheetId="2">STL!$M$6</definedName>
-    <definedName name="S.1">'DATA '!$N$6</definedName>
+    <definedName name="S.1">ABSORPTION!$N$6</definedName>
     <definedName name="S.2" localSheetId="2">STL!$M$33</definedName>
-    <definedName name="S.2">'DATA '!$N$33</definedName>
+    <definedName name="S.2">ABSORPTION!$N$33</definedName>
     <definedName name="S.3" localSheetId="2">STL!$M$59</definedName>
-    <definedName name="S.3">'DATA '!$N$59</definedName>
+    <definedName name="S.3">ABSORPTION!$N$59</definedName>
     <definedName name="S.4" localSheetId="2">STL!$M$85</definedName>
-    <definedName name="S.4">'DATA '!$N$85</definedName>
+    <definedName name="S.4">ABSORPTION!$N$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -724,11 +721,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -741,6 +733,11 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1057,7 +1054,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'DATA '!$A$20:$A$37</c:f>
+              <c:f>ABSORPTION!$A$20:$A$37</c:f>
               <c:strCache>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
@@ -1080,7 +1077,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'DATA '!$C$22:$C$37</c:f>
+              <c:f>ABSORPTION!$C$22:$C$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -1147,7 +1144,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'DATA '!$A$38:$A$55</c:f>
+              <c:f>ABSORPTION!$A$38:$A$55</c:f>
               <c:strCache>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
@@ -1170,7 +1167,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'DATA '!$C$40:$C$55</c:f>
+              <c:f>ABSORPTION!$C$40:$C$55</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
@@ -1237,7 +1234,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'DATA '!$A$56:$A$73</c:f>
+              <c:f>ABSORPTION!$A$56:$A$73</c:f>
               <c:strCache>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
@@ -1260,7 +1257,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'DATA '!$C$58:$C$73</c:f>
+              <c:f>ABSORPTION!$C$58:$C$73</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
@@ -3159,117 +3156,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="GNRL Characteristics"/>
-      <sheetName val="ABSORPTION"/>
-      <sheetName val="STL"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2">
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>E0002</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="C22">
-            <v>42.6982</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="C23">
-            <v>41.793599999999998</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="C24">
-            <v>42.074800000000003</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="C25">
-            <v>41.737099999999998</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="C26">
-            <v>40.949800000000003</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="C27">
-            <v>37.861899999999999</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="C28">
-            <v>40.177199999999999</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="C29">
-            <v>44.713200000000001</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="C30">
-            <v>47.029600000000002</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="C31">
-            <v>49.722200000000001</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="C32">
-            <v>51.986899999999999</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="C33">
-            <v>50.470799999999997</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="C34">
-            <v>47.082099999999997</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="C35">
-            <v>41.153300000000002</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="C36">
-            <v>32.591200000000001</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>E0003</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56" t="str">
-            <v>E0004</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -38787,7 +38673,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="32" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="17">
@@ -38799,7 +38685,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="29"/>
+      <c r="A3" s="33"/>
       <c r="B3" s="11">
         <v>250</v>
       </c>
@@ -38809,7 +38695,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="29"/>
+      <c r="A4" s="33"/>
       <c r="B4" s="11">
         <v>315</v>
       </c>
@@ -38821,7 +38707,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="29"/>
+      <c r="A5" s="33"/>
       <c r="B5" s="11">
         <v>400</v>
       </c>
@@ -38833,7 +38719,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="29"/>
+      <c r="A6" s="33"/>
       <c r="B6" s="11">
         <v>500</v>
       </c>
@@ -38845,7 +38731,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="29"/>
+      <c r="A7" s="33"/>
       <c r="B7" s="11">
         <v>630</v>
       </c>
@@ -38857,7 +38743,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="11">
         <v>800</v>
       </c>
@@ -38869,7 +38755,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
+      <c r="A9" s="33"/>
       <c r="B9" s="11">
         <v>1000</v>
       </c>
@@ -38881,7 +38767,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="11">
         <v>1250</v>
       </c>
@@ -38893,7 +38779,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
+      <c r="A11" s="33"/>
       <c r="B11" s="11">
         <v>1600</v>
       </c>
@@ -38905,7 +38791,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
+      <c r="A12" s="33"/>
       <c r="B12" s="11">
         <v>2000</v>
       </c>
@@ -38917,7 +38803,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
+      <c r="A13" s="33"/>
       <c r="B13" s="11">
         <v>2500</v>
       </c>
@@ -38929,7 +38815,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="29"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="11">
         <v>3150</v>
       </c>
@@ -38941,7 +38827,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="11">
         <v>4000</v>
       </c>
@@ -38953,7 +38839,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="29"/>
+      <c r="A16" s="33"/>
       <c r="B16" s="11">
         <v>5000</v>
       </c>
@@ -38965,7 +38851,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
+      <c r="A17" s="33"/>
       <c r="B17" s="11">
         <v>6300</v>
       </c>
@@ -38977,7 +38863,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="29"/>
+      <c r="A18" s="33"/>
       <c r="B18" s="11">
         <v>8000</v>
       </c>
@@ -38987,7 +38873,7 @@
       <c r="D18" s="12"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
+      <c r="A19" s="34"/>
       <c r="B19" s="11">
         <v>10000</v>
       </c>
@@ -38997,7 +38883,7 @@
       <c r="D19" s="12"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="32" t="s">
         <v>30</v>
       </c>
       <c r="B20" s="17">
@@ -39009,7 +38895,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="29"/>
+      <c r="A21" s="33"/>
       <c r="B21" s="11">
         <v>250</v>
       </c>
@@ -39019,7 +38905,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="29"/>
+      <c r="A22" s="33"/>
       <c r="B22" s="11">
         <v>315</v>
       </c>
@@ -39031,7 +38917,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="29"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="11">
         <v>400</v>
       </c>
@@ -39043,7 +38929,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="29"/>
+      <c r="A24" s="33"/>
       <c r="B24" s="11">
         <v>500</v>
       </c>
@@ -39055,7 +38941,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="29"/>
+      <c r="A25" s="33"/>
       <c r="B25" s="11">
         <v>630</v>
       </c>
@@ -39067,7 +38953,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="29"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="11">
         <v>800</v>
       </c>
@@ -39079,7 +38965,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="29"/>
+      <c r="A27" s="33"/>
       <c r="B27" s="11">
         <v>1000</v>
       </c>
@@ -39091,7 +38977,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="29"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="11">
         <v>1250</v>
       </c>
@@ -39103,7 +38989,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
+      <c r="A29" s="33"/>
       <c r="B29" s="11">
         <v>1600</v>
       </c>
@@ -39115,7 +39001,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
+      <c r="A30" s="33"/>
       <c r="B30" s="11">
         <v>2000</v>
       </c>
@@ -39127,7 +39013,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="11">
         <v>2500</v>
       </c>
@@ -39139,7 +39025,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="29"/>
+      <c r="A32" s="33"/>
       <c r="B32" s="11">
         <v>3150</v>
       </c>
@@ -39151,7 +39037,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="29"/>
+      <c r="A33" s="33"/>
       <c r="B33" s="11">
         <v>4000</v>
       </c>
@@ -39163,7 +39049,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="29"/>
+      <c r="A34" s="33"/>
       <c r="B34" s="11">
         <v>5000</v>
       </c>
@@ -39175,7 +39061,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="29"/>
+      <c r="A35" s="33"/>
       <c r="B35" s="11">
         <v>6300</v>
       </c>
@@ -39187,7 +39073,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="29"/>
+      <c r="A36" s="33"/>
       <c r="B36" s="11">
         <v>8000</v>
       </c>
@@ -39197,7 +39083,7 @@
       <c r="D36" s="12"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="30"/>
+      <c r="A37" s="34"/>
       <c r="B37" s="11">
         <v>10000</v>
       </c>
@@ -39207,7 +39093,7 @@
       <c r="D37" s="12"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B38" s="17">
@@ -39217,7 +39103,7 @@
       <c r="D38" s="24"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="29"/>
+      <c r="A39" s="33"/>
       <c r="B39" s="11">
         <v>250</v>
       </c>
@@ -39225,7 +39111,7 @@
       <c r="D39" s="24"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="29"/>
+      <c r="A40" s="33"/>
       <c r="B40" s="11">
         <v>315</v>
       </c>
@@ -39235,7 +39121,7 @@
       <c r="D40" s="24"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="29"/>
+      <c r="A41" s="33"/>
       <c r="B41" s="11">
         <v>400</v>
       </c>
@@ -39245,7 +39131,7 @@
       <c r="D41" s="24"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="29"/>
+      <c r="A42" s="33"/>
       <c r="B42" s="11">
         <v>500</v>
       </c>
@@ -39255,7 +39141,7 @@
       <c r="D42" s="24"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="29"/>
+      <c r="A43" s="33"/>
       <c r="B43" s="11">
         <v>630</v>
       </c>
@@ -39265,7 +39151,7 @@
       <c r="D43" s="24"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="29"/>
+      <c r="A44" s="33"/>
       <c r="B44" s="11">
         <v>800</v>
       </c>
@@ -39275,7 +39161,7 @@
       <c r="D44" s="24"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="29"/>
+      <c r="A45" s="33"/>
       <c r="B45" s="11">
         <v>1000</v>
       </c>
@@ -39285,7 +39171,7 @@
       <c r="D45" s="24"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="29"/>
+      <c r="A46" s="33"/>
       <c r="B46" s="11">
         <v>1250</v>
       </c>
@@ -39295,7 +39181,7 @@
       <c r="D46" s="24"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="29"/>
+      <c r="A47" s="33"/>
       <c r="B47" s="11">
         <v>1600</v>
       </c>
@@ -39305,7 +39191,7 @@
       <c r="D47" s="24"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="29"/>
+      <c r="A48" s="33"/>
       <c r="B48" s="11">
         <v>2000</v>
       </c>
@@ -39315,7 +39201,7 @@
       <c r="D48" s="24"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="29"/>
+      <c r="A49" s="33"/>
       <c r="B49" s="11">
         <v>2500</v>
       </c>
@@ -39325,7 +39211,7 @@
       <c r="D49" s="24"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="29"/>
+      <c r="A50" s="33"/>
       <c r="B50" s="11">
         <v>3150</v>
       </c>
@@ -39335,7 +39221,7 @@
       <c r="D50" s="24"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="29"/>
+      <c r="A51" s="33"/>
       <c r="B51" s="11">
         <v>4000</v>
       </c>
@@ -39345,7 +39231,7 @@
       <c r="D51" s="24"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="29"/>
+      <c r="A52" s="33"/>
       <c r="B52" s="11">
         <v>5000</v>
       </c>
@@ -39355,7 +39241,7 @@
       <c r="D52" s="24"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="29"/>
+      <c r="A53" s="33"/>
       <c r="B53" s="11">
         <v>6300</v>
       </c>
@@ -39365,7 +39251,7 @@
       <c r="D53" s="24"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="29"/>
+      <c r="A54" s="33"/>
       <c r="B54" s="11">
         <v>8000</v>
       </c>
@@ -39375,7 +39261,7 @@
       <c r="D54" s="24"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="30"/>
+      <c r="A55" s="34"/>
       <c r="B55" s="11">
         <v>10000</v>
       </c>
@@ -39385,7 +39271,7 @@
       <c r="D55" s="24"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="28" t="s">
+      <c r="A56" s="32" t="s">
         <v>38</v>
       </c>
       <c r="B56" s="17">
@@ -39395,7 +39281,7 @@
       <c r="D56" s="24"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="29"/>
+      <c r="A57" s="33"/>
       <c r="B57" s="11">
         <v>250</v>
       </c>
@@ -39403,7 +39289,7 @@
       <c r="D57" s="24"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="29"/>
+      <c r="A58" s="33"/>
       <c r="B58" s="11">
         <v>315</v>
       </c>
@@ -39413,7 +39299,7 @@
       <c r="D58" s="24"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="29"/>
+      <c r="A59" s="33"/>
       <c r="B59" s="11">
         <v>400</v>
       </c>
@@ -39423,7 +39309,7 @@
       <c r="D59" s="24"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="29"/>
+      <c r="A60" s="33"/>
       <c r="B60" s="11">
         <v>500</v>
       </c>
@@ -39433,7 +39319,7 @@
       <c r="D60" s="24"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="29"/>
+      <c r="A61" s="33"/>
       <c r="B61" s="11">
         <v>630</v>
       </c>
@@ -39443,7 +39329,7 @@
       <c r="D61" s="24"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="29"/>
+      <c r="A62" s="33"/>
       <c r="B62" s="11">
         <v>800</v>
       </c>
@@ -39453,7 +39339,7 @@
       <c r="D62" s="24"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="29"/>
+      <c r="A63" s="33"/>
       <c r="B63" s="11">
         <v>1000</v>
       </c>
@@ -39463,7 +39349,7 @@
       <c r="D63" s="24"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="29"/>
+      <c r="A64" s="33"/>
       <c r="B64" s="11">
         <v>1250</v>
       </c>
@@ -39473,7 +39359,7 @@
       <c r="D64" s="24"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="29"/>
+      <c r="A65" s="33"/>
       <c r="B65" s="11">
         <v>1600</v>
       </c>
@@ -39483,7 +39369,7 @@
       <c r="D65" s="24"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="29"/>
+      <c r="A66" s="33"/>
       <c r="B66" s="11">
         <v>2000</v>
       </c>
@@ -39493,7 +39379,7 @@
       <c r="D66" s="24"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="29"/>
+      <c r="A67" s="33"/>
       <c r="B67" s="11">
         <v>2500</v>
       </c>
@@ -39503,7 +39389,7 @@
       <c r="D67" s="24"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="29"/>
+      <c r="A68" s="33"/>
       <c r="B68" s="11">
         <v>3150</v>
       </c>
@@ -39513,7 +39399,7 @@
       <c r="D68" s="24"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="29"/>
+      <c r="A69" s="33"/>
       <c r="B69" s="11">
         <v>4000</v>
       </c>
@@ -39523,7 +39409,7 @@
       <c r="D69" s="24"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="29"/>
+      <c r="A70" s="33"/>
       <c r="B70" s="11">
         <v>5000</v>
       </c>
@@ -39533,7 +39419,7 @@
       <c r="D70" s="24"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="29"/>
+      <c r="A71" s="33"/>
       <c r="B71" s="11">
         <v>6300</v>
       </c>
@@ -39543,7 +39429,7 @@
       <c r="D71" s="24"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="29"/>
+      <c r="A72" s="33"/>
       <c r="B72" s="11">
         <v>8000</v>
       </c>
@@ -39553,7 +39439,7 @@
       <c r="D72" s="24"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="30"/>
+      <c r="A73" s="34"/>
       <c r="B73" s="11">
         <v>10000</v>
       </c>
@@ -39563,7 +39449,7 @@
       <c r="D73" s="24"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="28" t="s">
+      <c r="A74" s="32" t="s">
         <v>41</v>
       </c>
       <c r="B74" s="17">
@@ -39575,7 +39461,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="29"/>
+      <c r="A75" s="33"/>
       <c r="B75" s="11">
         <v>250</v>
       </c>
@@ -39585,7 +39471,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="29"/>
+      <c r="A76" s="33"/>
       <c r="B76" s="11">
         <v>315</v>
       </c>
@@ -39597,7 +39483,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="29"/>
+      <c r="A77" s="33"/>
       <c r="B77" s="11">
         <v>400</v>
       </c>
@@ -39609,7 +39495,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="29"/>
+      <c r="A78" s="33"/>
       <c r="B78" s="11">
         <v>500</v>
       </c>
@@ -39621,7 +39507,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="29"/>
+      <c r="A79" s="33"/>
       <c r="B79" s="11">
         <v>630</v>
       </c>
@@ -39633,7 +39519,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="29"/>
+      <c r="A80" s="33"/>
       <c r="B80" s="11">
         <v>800</v>
       </c>
@@ -39645,7 +39531,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="29"/>
+      <c r="A81" s="33"/>
       <c r="B81" s="11">
         <v>1000</v>
       </c>
@@ -39657,7 +39543,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="29"/>
+      <c r="A82" s="33"/>
       <c r="B82" s="11">
         <v>1250</v>
       </c>
@@ -39669,7 +39555,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="29"/>
+      <c r="A83" s="33"/>
       <c r="B83" s="11">
         <v>1600</v>
       </c>
@@ -39681,7 +39567,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="29"/>
+      <c r="A84" s="33"/>
       <c r="B84" s="11">
         <v>2000</v>
       </c>
@@ -39693,7 +39579,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="29"/>
+      <c r="A85" s="33"/>
       <c r="B85" s="11">
         <v>2500</v>
       </c>
@@ -39705,7 +39591,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="29"/>
+      <c r="A86" s="33"/>
       <c r="B86" s="11">
         <v>3150</v>
       </c>
@@ -39717,7 +39603,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="29"/>
+      <c r="A87" s="33"/>
       <c r="B87" s="11">
         <v>4000</v>
       </c>
@@ -39729,7 +39615,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="29"/>
+      <c r="A88" s="33"/>
       <c r="B88" s="11">
         <v>5000</v>
       </c>
@@ -39741,7 +39627,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="29"/>
+      <c r="A89" s="33"/>
       <c r="B89" s="11">
         <v>6300</v>
       </c>
@@ -39753,7 +39639,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="29"/>
+      <c r="A90" s="33"/>
       <c r="B90" s="11">
         <v>8000</v>
       </c>
@@ -39763,7 +39649,7 @@
       <c r="D90" s="12"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="30"/>
+      <c r="A91" s="34"/>
       <c r="B91" s="11">
         <v>10000</v>
       </c>
@@ -39773,7 +39659,7 @@
       <c r="D91" s="12"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="28" t="s">
+      <c r="A92" s="32" t="s">
         <v>42</v>
       </c>
       <c r="B92" s="17">
@@ -39785,7 +39671,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="29"/>
+      <c r="A93" s="33"/>
       <c r="B93" s="11">
         <v>250</v>
       </c>
@@ -39795,7 +39681,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="29"/>
+      <c r="A94" s="33"/>
       <c r="B94" s="11">
         <v>315</v>
       </c>
@@ -39807,7 +39693,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="29"/>
+      <c r="A95" s="33"/>
       <c r="B95" s="11">
         <v>400</v>
       </c>
@@ -39819,7 +39705,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="29"/>
+      <c r="A96" s="33"/>
       <c r="B96" s="11">
         <v>500</v>
       </c>
@@ -39831,7 +39717,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="29"/>
+      <c r="A97" s="33"/>
       <c r="B97" s="11">
         <v>630</v>
       </c>
@@ -39843,7 +39729,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="29"/>
+      <c r="A98" s="33"/>
       <c r="B98" s="11">
         <v>800</v>
       </c>
@@ -39855,7 +39741,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="29"/>
+      <c r="A99" s="33"/>
       <c r="B99" s="11">
         <v>1000</v>
       </c>
@@ -39867,7 +39753,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="29"/>
+      <c r="A100" s="33"/>
       <c r="B100" s="11">
         <v>1250</v>
       </c>
@@ -39879,7 +39765,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="29"/>
+      <c r="A101" s="33"/>
       <c r="B101" s="11">
         <v>1600</v>
       </c>
@@ -39891,7 +39777,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="29"/>
+      <c r="A102" s="33"/>
       <c r="B102" s="11">
         <v>2000</v>
       </c>
@@ -39903,7 +39789,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="29"/>
+      <c r="A103" s="33"/>
       <c r="B103" s="11">
         <v>2500</v>
       </c>
@@ -39915,7 +39801,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="29"/>
+      <c r="A104" s="33"/>
       <c r="B104" s="11">
         <v>3150</v>
       </c>
@@ -39927,7 +39813,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="29"/>
+      <c r="A105" s="33"/>
       <c r="B105" s="11">
         <v>4000</v>
       </c>
@@ -39939,7 +39825,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="29"/>
+      <c r="A106" s="33"/>
       <c r="B106" s="11">
         <v>5000</v>
       </c>
@@ -39951,7 +39837,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="29"/>
+      <c r="A107" s="33"/>
       <c r="B107" s="11">
         <v>6300</v>
       </c>
@@ -39963,7 +39849,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="29"/>
+      <c r="A108" s="33"/>
       <c r="B108" s="11">
         <v>8000</v>
       </c>
@@ -39973,7 +39859,7 @@
       <c r="D108" s="12"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="30"/>
+      <c r="A109" s="34"/>
       <c r="B109" s="11">
         <v>10000</v>
       </c>
@@ -39983,7 +39869,7 @@
       <c r="D109" s="12"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="28" t="s">
+      <c r="A110" s="32" t="s">
         <v>43</v>
       </c>
       <c r="B110" s="17">
@@ -39995,7 +39881,7 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="29"/>
+      <c r="A111" s="33"/>
       <c r="B111" s="11">
         <v>250</v>
       </c>
@@ -40005,7 +39891,7 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="29"/>
+      <c r="A112" s="33"/>
       <c r="B112" s="11">
         <v>315</v>
       </c>
@@ -40017,7 +39903,7 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="29"/>
+      <c r="A113" s="33"/>
       <c r="B113" s="11">
         <v>400</v>
       </c>
@@ -40029,7 +39915,7 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="29"/>
+      <c r="A114" s="33"/>
       <c r="B114" s="11">
         <v>500</v>
       </c>
@@ -40041,7 +39927,7 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="29"/>
+      <c r="A115" s="33"/>
       <c r="B115" s="11">
         <v>630</v>
       </c>
@@ -40053,7 +39939,7 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="29"/>
+      <c r="A116" s="33"/>
       <c r="B116" s="11">
         <v>800</v>
       </c>
@@ -40065,7 +39951,7 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="29"/>
+      <c r="A117" s="33"/>
       <c r="B117" s="11">
         <v>1000</v>
       </c>
@@ -40077,7 +39963,7 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="29"/>
+      <c r="A118" s="33"/>
       <c r="B118" s="11">
         <v>1250</v>
       </c>
@@ -40089,7 +39975,7 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="29"/>
+      <c r="A119" s="33"/>
       <c r="B119" s="11">
         <v>1600</v>
       </c>
@@ -40101,7 +39987,7 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="29"/>
+      <c r="A120" s="33"/>
       <c r="B120" s="11">
         <v>2000</v>
       </c>
@@ -40113,7 +39999,7 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="29"/>
+      <c r="A121" s="33"/>
       <c r="B121" s="11">
         <v>2500</v>
       </c>
@@ -40125,7 +40011,7 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="29"/>
+      <c r="A122" s="33"/>
       <c r="B122" s="11">
         <v>3150</v>
       </c>
@@ -40137,7 +40023,7 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="29"/>
+      <c r="A123" s="33"/>
       <c r="B123" s="11">
         <v>4000</v>
       </c>
@@ -40149,7 +40035,7 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="29"/>
+      <c r="A124" s="33"/>
       <c r="B124" s="11">
         <v>5000</v>
       </c>
@@ -40161,7 +40047,7 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="29"/>
+      <c r="A125" s="33"/>
       <c r="B125" s="11">
         <v>6300</v>
       </c>
@@ -40173,7 +40059,7 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="29"/>
+      <c r="A126" s="33"/>
       <c r="B126" s="11">
         <v>8000</v>
       </c>
@@ -40183,7 +40069,7 @@
       <c r="D126" s="12"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="30"/>
+      <c r="A127" s="34"/>
       <c r="B127" s="11">
         <v>10000</v>
       </c>
@@ -40193,7 +40079,7 @@
       <c r="D127" s="12"/>
     </row>
     <row r="128" spans="1:4" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="28" t="s">
+      <c r="A128" s="32" t="s">
         <v>46</v>
       </c>
       <c r="B128" s="17">
@@ -40205,7 +40091,7 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="29"/>
+      <c r="A129" s="33"/>
       <c r="B129" s="11">
         <v>250</v>
       </c>
@@ -40215,7 +40101,7 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="29"/>
+      <c r="A130" s="33"/>
       <c r="B130" s="11">
         <v>315</v>
       </c>
@@ -40227,7 +40113,7 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="29"/>
+      <c r="A131" s="33"/>
       <c r="B131" s="11">
         <v>400</v>
       </c>
@@ -40239,7 +40125,7 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="29"/>
+      <c r="A132" s="33"/>
       <c r="B132" s="11">
         <v>500</v>
       </c>
@@ -40251,7 +40137,7 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="29"/>
+      <c r="A133" s="33"/>
       <c r="B133" s="11">
         <v>630</v>
       </c>
@@ -40263,7 +40149,7 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="29"/>
+      <c r="A134" s="33"/>
       <c r="B134" s="11">
         <v>800</v>
       </c>
@@ -40275,7 +40161,7 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="29"/>
+      <c r="A135" s="33"/>
       <c r="B135" s="11">
         <v>1000</v>
       </c>
@@ -40287,7 +40173,7 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="29"/>
+      <c r="A136" s="33"/>
       <c r="B136" s="11">
         <v>1250</v>
       </c>
@@ -40299,7 +40185,7 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="29"/>
+      <c r="A137" s="33"/>
       <c r="B137" s="11">
         <v>1600</v>
       </c>
@@ -40311,7 +40197,7 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="29"/>
+      <c r="A138" s="33"/>
       <c r="B138" s="11">
         <v>2000</v>
       </c>
@@ -40323,7 +40209,7 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="29"/>
+      <c r="A139" s="33"/>
       <c r="B139" s="11">
         <v>2500</v>
       </c>
@@ -40335,7 +40221,7 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" s="29"/>
+      <c r="A140" s="33"/>
       <c r="B140" s="11">
         <v>3150</v>
       </c>
@@ -40347,7 +40233,7 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="29"/>
+      <c r="A141" s="33"/>
       <c r="B141" s="11">
         <v>4000</v>
       </c>
@@ -40359,7 +40245,7 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="29"/>
+      <c r="A142" s="33"/>
       <c r="B142" s="11">
         <v>5000</v>
       </c>
@@ -40371,7 +40257,7 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="29"/>
+      <c r="A143" s="33"/>
       <c r="B143" s="11">
         <v>6300</v>
       </c>
@@ -40383,7 +40269,7 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" s="29"/>
+      <c r="A144" s="33"/>
       <c r="B144" s="11">
         <v>8000</v>
       </c>
@@ -40393,7 +40279,7 @@
       <c r="D144" s="12"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" s="30"/>
+      <c r="A145" s="34"/>
       <c r="B145" s="11">
         <v>10000</v>
       </c>
@@ -40403,7 +40289,7 @@
       <c r="D145" s="12"/>
     </row>
     <row r="146" spans="1:4" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="28" t="s">
+      <c r="A146" s="32" t="s">
         <v>50</v>
       </c>
       <c r="B146" s="17">
@@ -40413,7 +40299,7 @@
       <c r="D146" s="24"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" s="29"/>
+      <c r="A147" s="33"/>
       <c r="B147" s="11">
         <v>250</v>
       </c>
@@ -40421,7 +40307,7 @@
       <c r="D147" s="24"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A148" s="29"/>
+      <c r="A148" s="33"/>
       <c r="B148" s="11">
         <v>315</v>
       </c>
@@ -40431,7 +40317,7 @@
       <c r="D148" s="24"/>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" s="29"/>
+      <c r="A149" s="33"/>
       <c r="B149" s="11">
         <v>400</v>
       </c>
@@ -40441,7 +40327,7 @@
       <c r="D149" s="24"/>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150" s="29"/>
+      <c r="A150" s="33"/>
       <c r="B150" s="11">
         <v>500</v>
       </c>
@@ -40451,7 +40337,7 @@
       <c r="D150" s="24"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" s="29"/>
+      <c r="A151" s="33"/>
       <c r="B151" s="11">
         <v>630</v>
       </c>
@@ -40461,7 +40347,7 @@
       <c r="D151" s="24"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A152" s="29"/>
+      <c r="A152" s="33"/>
       <c r="B152" s="11">
         <v>800</v>
       </c>
@@ -40471,7 +40357,7 @@
       <c r="D152" s="24"/>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A153" s="29"/>
+      <c r="A153" s="33"/>
       <c r="B153" s="11">
         <v>1000</v>
       </c>
@@ -40481,7 +40367,7 @@
       <c r="D153" s="24"/>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A154" s="29"/>
+      <c r="A154" s="33"/>
       <c r="B154" s="11">
         <v>1250</v>
       </c>
@@ -40491,7 +40377,7 @@
       <c r="D154" s="24"/>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" s="29"/>
+      <c r="A155" s="33"/>
       <c r="B155" s="11">
         <v>1600</v>
       </c>
@@ -40501,7 +40387,7 @@
       <c r="D155" s="24"/>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" s="29"/>
+      <c r="A156" s="33"/>
       <c r="B156" s="11">
         <v>2000</v>
       </c>
@@ -40511,7 +40397,7 @@
       <c r="D156" s="24"/>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A157" s="29"/>
+      <c r="A157" s="33"/>
       <c r="B157" s="11">
         <v>2500</v>
       </c>
@@ -40521,7 +40407,7 @@
       <c r="D157" s="24"/>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" s="29"/>
+      <c r="A158" s="33"/>
       <c r="B158" s="11">
         <v>3150</v>
       </c>
@@ -40531,7 +40417,7 @@
       <c r="D158" s="24"/>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A159" s="29"/>
+      <c r="A159" s="33"/>
       <c r="B159" s="11">
         <v>4000</v>
       </c>
@@ -40541,7 +40427,7 @@
       <c r="D159" s="24"/>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A160" s="29"/>
+      <c r="A160" s="33"/>
       <c r="B160" s="11">
         <v>5000</v>
       </c>
@@ -40551,7 +40437,7 @@
       <c r="D160" s="24"/>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" s="29"/>
+      <c r="A161" s="33"/>
       <c r="B161" s="11">
         <v>6300</v>
       </c>
@@ -40561,7 +40447,7 @@
       <c r="D161" s="24"/>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="29"/>
+      <c r="A162" s="33"/>
       <c r="B162" s="11">
         <v>8000</v>
       </c>
@@ -40571,7 +40457,7 @@
       <c r="D162" s="24"/>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" s="30"/>
+      <c r="A163" s="34"/>
       <c r="B163" s="11">
         <v>10000</v>
       </c>
@@ -40581,7 +40467,7 @@
       <c r="D163" s="24"/>
     </row>
     <row r="164" spans="1:4" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="28" t="s">
+      <c r="A164" s="32" t="s">
         <v>53</v>
       </c>
       <c r="B164" s="17">
@@ -40591,7 +40477,7 @@
       <c r="D164" s="12"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" s="29"/>
+      <c r="A165" s="33"/>
       <c r="B165" s="11">
         <v>250</v>
       </c>
@@ -40599,7 +40485,7 @@
       <c r="D165" s="12"/>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" s="29"/>
+      <c r="A166" s="33"/>
       <c r="B166" s="11">
         <v>315</v>
       </c>
@@ -40609,7 +40495,7 @@
       <c r="D166" s="12"/>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" s="29"/>
+      <c r="A167" s="33"/>
       <c r="B167" s="11">
         <v>400</v>
       </c>
@@ -40619,7 +40505,7 @@
       <c r="D167" s="12"/>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" s="29"/>
+      <c r="A168" s="33"/>
       <c r="B168" s="11">
         <v>500</v>
       </c>
@@ -40629,7 +40515,7 @@
       <c r="D168" s="12"/>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" s="29"/>
+      <c r="A169" s="33"/>
       <c r="B169" s="11">
         <v>630</v>
       </c>
@@ -40639,7 +40525,7 @@
       <c r="D169" s="12"/>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="29"/>
+      <c r="A170" s="33"/>
       <c r="B170" s="11">
         <v>800</v>
       </c>
@@ -40649,7 +40535,7 @@
       <c r="D170" s="12"/>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="29"/>
+      <c r="A171" s="33"/>
       <c r="B171" s="11">
         <v>1000</v>
       </c>
@@ -40659,7 +40545,7 @@
       <c r="D171" s="12"/>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" s="29"/>
+      <c r="A172" s="33"/>
       <c r="B172" s="11">
         <v>1250</v>
       </c>
@@ -40669,7 +40555,7 @@
       <c r="D172" s="12"/>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" s="29"/>
+      <c r="A173" s="33"/>
       <c r="B173" s="11">
         <v>1600</v>
       </c>
@@ -40679,7 +40565,7 @@
       <c r="D173" s="12"/>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="29"/>
+      <c r="A174" s="33"/>
       <c r="B174" s="11">
         <v>2000</v>
       </c>
@@ -40689,7 +40575,7 @@
       <c r="D174" s="12"/>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="29"/>
+      <c r="A175" s="33"/>
       <c r="B175" s="11">
         <v>2500</v>
       </c>
@@ -40699,7 +40585,7 @@
       <c r="D175" s="12"/>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="29"/>
+      <c r="A176" s="33"/>
       <c r="B176" s="11">
         <v>3150</v>
       </c>
@@ -40709,7 +40595,7 @@
       <c r="D176" s="12"/>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" s="29"/>
+      <c r="A177" s="33"/>
       <c r="B177" s="11">
         <v>4000</v>
       </c>
@@ -40719,7 +40605,7 @@
       <c r="D177" s="12"/>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" s="29"/>
+      <c r="A178" s="33"/>
       <c r="B178" s="11">
         <v>5000</v>
       </c>
@@ -40729,7 +40615,7 @@
       <c r="D178" s="12"/>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" s="29"/>
+      <c r="A179" s="33"/>
       <c r="B179" s="11">
         <v>6300</v>
       </c>
@@ -40739,7 +40625,7 @@
       <c r="D179" s="12"/>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" s="29"/>
+      <c r="A180" s="33"/>
       <c r="B180" s="11">
         <v>8000</v>
       </c>
@@ -40749,7 +40635,7 @@
       <c r="D180" s="12"/>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" s="30"/>
+      <c r="A181" s="34"/>
       <c r="B181" s="11">
         <v>10000</v>
       </c>
@@ -40759,7 +40645,7 @@
       <c r="D181" s="12"/>
     </row>
     <row r="182" spans="1:4" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="28" t="s">
+      <c r="A182" s="32" t="s">
         <v>55</v>
       </c>
       <c r="B182" s="17">
@@ -40769,7 +40655,7 @@
       <c r="D182" s="12"/>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="29"/>
+      <c r="A183" s="33"/>
       <c r="B183" s="11">
         <v>250</v>
       </c>
@@ -40777,7 +40663,7 @@
       <c r="D183" s="12"/>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="29"/>
+      <c r="A184" s="33"/>
       <c r="B184" s="11">
         <v>315</v>
       </c>
@@ -40787,7 +40673,7 @@
       <c r="D184" s="12"/>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" s="29"/>
+      <c r="A185" s="33"/>
       <c r="B185" s="11">
         <v>400</v>
       </c>
@@ -40797,7 +40683,7 @@
       <c r="D185" s="12"/>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="29"/>
+      <c r="A186" s="33"/>
       <c r="B186" s="11">
         <v>500</v>
       </c>
@@ -40807,7 +40693,7 @@
       <c r="D186" s="12"/>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" s="29"/>
+      <c r="A187" s="33"/>
       <c r="B187" s="11">
         <v>630</v>
       </c>
@@ -40817,7 +40703,7 @@
       <c r="D187" s="12"/>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="29"/>
+      <c r="A188" s="33"/>
       <c r="B188" s="11">
         <v>800</v>
       </c>
@@ -40827,7 +40713,7 @@
       <c r="D188" s="12"/>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="29"/>
+      <c r="A189" s="33"/>
       <c r="B189" s="11">
         <v>1000</v>
       </c>
@@ -40837,7 +40723,7 @@
       <c r="D189" s="12"/>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="29"/>
+      <c r="A190" s="33"/>
       <c r="B190" s="11">
         <v>1250</v>
       </c>
@@ -40847,7 +40733,7 @@
       <c r="D190" s="12"/>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A191" s="29"/>
+      <c r="A191" s="33"/>
       <c r="B191" s="11">
         <v>1600</v>
       </c>
@@ -40857,7 +40743,7 @@
       <c r="D191" s="12"/>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="29"/>
+      <c r="A192" s="33"/>
       <c r="B192" s="11">
         <v>2000</v>
       </c>
@@ -40867,7 +40753,7 @@
       <c r="D192" s="12"/>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A193" s="29"/>
+      <c r="A193" s="33"/>
       <c r="B193" s="11">
         <v>2500</v>
       </c>
@@ -40877,7 +40763,7 @@
       <c r="D193" s="12"/>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A194" s="29"/>
+      <c r="A194" s="33"/>
       <c r="B194" s="11">
         <v>3150</v>
       </c>
@@ -40887,7 +40773,7 @@
       <c r="D194" s="12"/>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" s="29"/>
+      <c r="A195" s="33"/>
       <c r="B195" s="11">
         <v>4000</v>
       </c>
@@ -40897,7 +40783,7 @@
       <c r="D195" s="12"/>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A196" s="29"/>
+      <c r="A196" s="33"/>
       <c r="B196" s="11">
         <v>5000</v>
       </c>
@@ -40907,7 +40793,7 @@
       <c r="D196" s="12"/>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" s="29"/>
+      <c r="A197" s="33"/>
       <c r="B197" s="11">
         <v>6300</v>
       </c>
@@ -40917,7 +40803,7 @@
       <c r="D197" s="12"/>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A198" s="29"/>
+      <c r="A198" s="33"/>
       <c r="B198" s="11">
         <v>8000</v>
       </c>
@@ -40927,7 +40813,7 @@
       <c r="D198" s="12"/>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A199" s="30"/>
+      <c r="A199" s="34"/>
       <c r="B199" s="11">
         <v>10000</v>
       </c>
@@ -40937,7 +40823,7 @@
       <c r="D199" s="12"/>
     </row>
     <row r="200" spans="1:4" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="28" t="s">
+      <c r="A200" s="32" t="s">
         <v>56</v>
       </c>
       <c r="B200" s="17">
@@ -40949,7 +40835,7 @@
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A201" s="29"/>
+      <c r="A201" s="33"/>
       <c r="B201" s="11">
         <v>250</v>
       </c>
@@ -40959,7 +40845,7 @@
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A202" s="29"/>
+      <c r="A202" s="33"/>
       <c r="B202" s="11">
         <v>315</v>
       </c>
@@ -40971,7 +40857,7 @@
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A203" s="29"/>
+      <c r="A203" s="33"/>
       <c r="B203" s="11">
         <v>400</v>
       </c>
@@ -40983,7 +40869,7 @@
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A204" s="29"/>
+      <c r="A204" s="33"/>
       <c r="B204" s="11">
         <v>500</v>
       </c>
@@ -40995,7 +40881,7 @@
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A205" s="29"/>
+      <c r="A205" s="33"/>
       <c r="B205" s="11">
         <v>630</v>
       </c>
@@ -41007,7 +40893,7 @@
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A206" s="29"/>
+      <c r="A206" s="33"/>
       <c r="B206" s="11">
         <v>800</v>
       </c>
@@ -41019,7 +40905,7 @@
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A207" s="29"/>
+      <c r="A207" s="33"/>
       <c r="B207" s="11">
         <v>1000</v>
       </c>
@@ -41031,7 +40917,7 @@
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A208" s="29"/>
+      <c r="A208" s="33"/>
       <c r="B208" s="11">
         <v>1250</v>
       </c>
@@ -41043,7 +40929,7 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A209" s="29"/>
+      <c r="A209" s="33"/>
       <c r="B209" s="11">
         <v>1600</v>
       </c>
@@ -41055,7 +40941,7 @@
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A210" s="29"/>
+      <c r="A210" s="33"/>
       <c r="B210" s="11">
         <v>2000</v>
       </c>
@@ -41067,7 +40953,7 @@
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A211" s="29"/>
+      <c r="A211" s="33"/>
       <c r="B211" s="11">
         <v>2500</v>
       </c>
@@ -41079,7 +40965,7 @@
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A212" s="29"/>
+      <c r="A212" s="33"/>
       <c r="B212" s="11">
         <v>3150</v>
       </c>
@@ -41091,7 +40977,7 @@
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A213" s="29"/>
+      <c r="A213" s="33"/>
       <c r="B213" s="11">
         <v>4000</v>
       </c>
@@ -41103,7 +40989,7 @@
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A214" s="29"/>
+      <c r="A214" s="33"/>
       <c r="B214" s="11">
         <v>5000</v>
       </c>
@@ -41115,7 +41001,7 @@
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A215" s="29"/>
+      <c r="A215" s="33"/>
       <c r="B215" s="11">
         <v>6300</v>
       </c>
@@ -41127,7 +41013,7 @@
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A216" s="29"/>
+      <c r="A216" s="33"/>
       <c r="B216" s="11">
         <v>8000</v>
       </c>
@@ -41137,7 +41023,7 @@
       <c r="D216" s="12"/>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A217" s="30"/>
+      <c r="A217" s="34"/>
       <c r="B217" s="11">
         <v>10000</v>
       </c>
@@ -41147,7 +41033,7 @@
       <c r="D217" s="12"/>
     </row>
     <row r="218" spans="1:4" s="2" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="28" t="s">
+      <c r="A218" s="32" t="s">
         <v>58</v>
       </c>
       <c r="B218" s="17">
@@ -41159,7 +41045,7 @@
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A219" s="29"/>
+      <c r="A219" s="33"/>
       <c r="B219" s="11">
         <v>250</v>
       </c>
@@ -41169,7 +41055,7 @@
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A220" s="29"/>
+      <c r="A220" s="33"/>
       <c r="B220" s="11">
         <v>315</v>
       </c>
@@ -41181,7 +41067,7 @@
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A221" s="29"/>
+      <c r="A221" s="33"/>
       <c r="B221" s="11">
         <v>400</v>
       </c>
@@ -41193,7 +41079,7 @@
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A222" s="29"/>
+      <c r="A222" s="33"/>
       <c r="B222" s="11">
         <v>500</v>
       </c>
@@ -41205,7 +41091,7 @@
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A223" s="29"/>
+      <c r="A223" s="33"/>
       <c r="B223" s="11">
         <v>630</v>
       </c>
@@ -41217,7 +41103,7 @@
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A224" s="29"/>
+      <c r="A224" s="33"/>
       <c r="B224" s="11">
         <v>800</v>
       </c>
@@ -41229,7 +41115,7 @@
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A225" s="29"/>
+      <c r="A225" s="33"/>
       <c r="B225" s="11">
         <v>1000</v>
       </c>
@@ -41241,7 +41127,7 @@
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A226" s="29"/>
+      <c r="A226" s="33"/>
       <c r="B226" s="11">
         <v>1250</v>
       </c>
@@ -41253,7 +41139,7 @@
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A227" s="29"/>
+      <c r="A227" s="33"/>
       <c r="B227" s="11">
         <v>1600</v>
       </c>
@@ -41265,7 +41151,7 @@
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A228" s="29"/>
+      <c r="A228" s="33"/>
       <c r="B228" s="11">
         <v>2000</v>
       </c>
@@ -41277,7 +41163,7 @@
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A229" s="29"/>
+      <c r="A229" s="33"/>
       <c r="B229" s="11">
         <v>2500</v>
       </c>
@@ -41289,7 +41175,7 @@
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A230" s="29"/>
+      <c r="A230" s="33"/>
       <c r="B230" s="11">
         <v>3150</v>
       </c>
@@ -41301,7 +41187,7 @@
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A231" s="29"/>
+      <c r="A231" s="33"/>
       <c r="B231" s="11">
         <v>4000</v>
       </c>
@@ -41313,7 +41199,7 @@
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A232" s="29"/>
+      <c r="A232" s="33"/>
       <c r="B232" s="11">
         <v>5000</v>
       </c>
@@ -41325,7 +41211,7 @@
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A233" s="29"/>
+      <c r="A233" s="33"/>
       <c r="B233" s="11">
         <v>6300</v>
       </c>
@@ -41337,7 +41223,7 @@
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A234" s="29"/>
+      <c r="A234" s="33"/>
       <c r="B234" s="11">
         <v>8000</v>
       </c>
@@ -41347,7 +41233,7 @@
       <c r="D234" s="12"/>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A235" s="30"/>
+      <c r="A235" s="34"/>
       <c r="B235" s="11">
         <v>10000</v>
       </c>
@@ -41357,7 +41243,7 @@
       <c r="D235" s="12"/>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A236" s="28" t="s">
+      <c r="A236" s="32" t="s">
         <v>60</v>
       </c>
       <c r="B236" s="17">
@@ -41367,7 +41253,7 @@
       <c r="D236" s="24"/>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A237" s="29"/>
+      <c r="A237" s="33"/>
       <c r="B237" s="11">
         <v>250</v>
       </c>
@@ -41375,7 +41261,7 @@
       <c r="D237" s="24"/>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A238" s="29"/>
+      <c r="A238" s="33"/>
       <c r="B238" s="11">
         <v>315</v>
       </c>
@@ -41385,7 +41271,7 @@
       <c r="D238" s="24"/>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A239" s="29"/>
+      <c r="A239" s="33"/>
       <c r="B239" s="11">
         <v>400</v>
       </c>
@@ -41395,7 +41281,7 @@
       <c r="D239" s="24"/>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A240" s="29"/>
+      <c r="A240" s="33"/>
       <c r="B240" s="11">
         <v>500</v>
       </c>
@@ -41405,7 +41291,7 @@
       <c r="D240" s="24"/>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A241" s="29"/>
+      <c r="A241" s="33"/>
       <c r="B241" s="11">
         <v>630</v>
       </c>
@@ -41415,7 +41301,7 @@
       <c r="D241" s="24"/>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A242" s="29"/>
+      <c r="A242" s="33"/>
       <c r="B242" s="11">
         <v>800</v>
       </c>
@@ -41425,7 +41311,7 @@
       <c r="D242" s="24"/>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A243" s="29"/>
+      <c r="A243" s="33"/>
       <c r="B243" s="11">
         <v>1000</v>
       </c>
@@ -41435,7 +41321,7 @@
       <c r="D243" s="24"/>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A244" s="29"/>
+      <c r="A244" s="33"/>
       <c r="B244" s="11">
         <v>1250</v>
       </c>
@@ -41445,7 +41331,7 @@
       <c r="D244" s="24"/>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A245" s="29"/>
+      <c r="A245" s="33"/>
       <c r="B245" s="11">
         <v>1600</v>
       </c>
@@ -41455,7 +41341,7 @@
       <c r="D245" s="24"/>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A246" s="29"/>
+      <c r="A246" s="33"/>
       <c r="B246" s="11">
         <v>2000</v>
       </c>
@@ -41465,7 +41351,7 @@
       <c r="D246" s="24"/>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A247" s="29"/>
+      <c r="A247" s="33"/>
       <c r="B247" s="11">
         <v>2500</v>
       </c>
@@ -41475,7 +41361,7 @@
       <c r="D247" s="24"/>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A248" s="29"/>
+      <c r="A248" s="33"/>
       <c r="B248" s="11">
         <v>3150</v>
       </c>
@@ -41485,7 +41371,7 @@
       <c r="D248" s="24"/>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A249" s="29"/>
+      <c r="A249" s="33"/>
       <c r="B249" s="11">
         <v>4000</v>
       </c>
@@ -41495,7 +41381,7 @@
       <c r="D249" s="24"/>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A250" s="29"/>
+      <c r="A250" s="33"/>
       <c r="B250" s="11">
         <v>5000</v>
       </c>
@@ -41505,7 +41391,7 @@
       <c r="D250" s="24"/>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A251" s="29"/>
+      <c r="A251" s="33"/>
       <c r="B251" s="11">
         <v>6300</v>
       </c>
@@ -41515,7 +41401,7 @@
       <c r="D251" s="24"/>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A252" s="29"/>
+      <c r="A252" s="33"/>
       <c r="B252" s="11">
         <v>8000</v>
       </c>
@@ -41525,7 +41411,7 @@
       <c r="D252" s="24"/>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A253" s="30"/>
+      <c r="A253" s="34"/>
       <c r="B253" s="11">
         <v>10000</v>
       </c>
@@ -41535,7 +41421,7 @@
       <c r="D253" s="24"/>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A254" s="28" t="s">
+      <c r="A254" s="32" t="s">
         <v>62</v>
       </c>
       <c r="B254" s="17">
@@ -41545,7 +41431,7 @@
       <c r="D254" s="27"/>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A255" s="29"/>
+      <c r="A255" s="33"/>
       <c r="B255" s="11">
         <v>250</v>
       </c>
@@ -41553,7 +41439,7 @@
       <c r="D255" s="27"/>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A256" s="29"/>
+      <c r="A256" s="33"/>
       <c r="B256" s="11">
         <v>315</v>
       </c>
@@ -41563,7 +41449,7 @@
       <c r="D256" s="27"/>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A257" s="29"/>
+      <c r="A257" s="33"/>
       <c r="B257" s="11">
         <v>400</v>
       </c>
@@ -41573,7 +41459,7 @@
       <c r="D257" s="27"/>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A258" s="29"/>
+      <c r="A258" s="33"/>
       <c r="B258" s="11">
         <v>500</v>
       </c>
@@ -41583,7 +41469,7 @@
       <c r="D258" s="27"/>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A259" s="29"/>
+      <c r="A259" s="33"/>
       <c r="B259" s="11">
         <v>630</v>
       </c>
@@ -41593,7 +41479,7 @@
       <c r="D259" s="27"/>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A260" s="29"/>
+      <c r="A260" s="33"/>
       <c r="B260" s="11">
         <v>800</v>
       </c>
@@ -41603,7 +41489,7 @@
       <c r="D260" s="27"/>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A261" s="29"/>
+      <c r="A261" s="33"/>
       <c r="B261" s="11">
         <v>1000</v>
       </c>
@@ -41613,7 +41499,7 @@
       <c r="D261" s="27"/>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A262" s="29"/>
+      <c r="A262" s="33"/>
       <c r="B262" s="11">
         <v>1250</v>
       </c>
@@ -41623,7 +41509,7 @@
       <c r="D262" s="27"/>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A263" s="29"/>
+      <c r="A263" s="33"/>
       <c r="B263" s="11">
         <v>1600</v>
       </c>
@@ -41633,7 +41519,7 @@
       <c r="D263" s="27"/>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A264" s="29"/>
+      <c r="A264" s="33"/>
       <c r="B264" s="11">
         <v>2000</v>
       </c>
@@ -41643,7 +41529,7 @@
       <c r="D264" s="27"/>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A265" s="29"/>
+      <c r="A265" s="33"/>
       <c r="B265" s="11">
         <v>2500</v>
       </c>
@@ -41653,7 +41539,7 @@
       <c r="D265" s="27"/>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A266" s="29"/>
+      <c r="A266" s="33"/>
       <c r="B266" s="11">
         <v>3150</v>
       </c>
@@ -41663,7 +41549,7 @@
       <c r="D266" s="27"/>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A267" s="29"/>
+      <c r="A267" s="33"/>
       <c r="B267" s="11">
         <v>4000</v>
       </c>
@@ -41673,7 +41559,7 @@
       <c r="D267" s="27"/>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A268" s="29"/>
+      <c r="A268" s="33"/>
       <c r="B268" s="11">
         <v>5000</v>
       </c>
@@ -41683,7 +41569,7 @@
       <c r="D268" s="27"/>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A269" s="29"/>
+      <c r="A269" s="33"/>
       <c r="B269" s="11">
         <v>6300</v>
       </c>
@@ -41693,7 +41579,7 @@
       <c r="D269" s="27"/>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A270" s="29"/>
+      <c r="A270" s="33"/>
       <c r="B270" s="11">
         <v>8000</v>
       </c>
@@ -41703,7 +41589,7 @@
       <c r="D270" s="27"/>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A271" s="30"/>
+      <c r="A271" s="34"/>
       <c r="B271" s="11">
         <v>10000</v>
       </c>
@@ -41713,7 +41599,7 @@
       <c r="D271" s="27"/>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A272" s="28" t="s">
+      <c r="A272" s="32" t="s">
         <v>65</v>
       </c>
       <c r="B272" s="17">
@@ -41725,7 +41611,7 @@
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A273" s="29"/>
+      <c r="A273" s="33"/>
       <c r="B273" s="11">
         <v>250</v>
       </c>
@@ -41735,7 +41621,7 @@
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A274" s="29"/>
+      <c r="A274" s="33"/>
       <c r="B274" s="11">
         <v>315</v>
       </c>
@@ -41747,7 +41633,7 @@
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A275" s="29"/>
+      <c r="A275" s="33"/>
       <c r="B275" s="11">
         <v>400</v>
       </c>
@@ -41759,7 +41645,7 @@
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A276" s="29"/>
+      <c r="A276" s="33"/>
       <c r="B276" s="11">
         <v>500</v>
       </c>
@@ -41771,7 +41657,7 @@
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A277" s="29"/>
+      <c r="A277" s="33"/>
       <c r="B277" s="11">
         <v>630</v>
       </c>
@@ -41783,7 +41669,7 @@
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A278" s="29"/>
+      <c r="A278" s="33"/>
       <c r="B278" s="11">
         <v>800</v>
       </c>
@@ -41795,7 +41681,7 @@
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A279" s="29"/>
+      <c r="A279" s="33"/>
       <c r="B279" s="11">
         <v>1000</v>
       </c>
@@ -41807,7 +41693,7 @@
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A280" s="29"/>
+      <c r="A280" s="33"/>
       <c r="B280" s="11">
         <v>1250</v>
       </c>
@@ -41819,7 +41705,7 @@
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A281" s="29"/>
+      <c r="A281" s="33"/>
       <c r="B281" s="11">
         <v>1600</v>
       </c>
@@ -41831,7 +41717,7 @@
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A282" s="29"/>
+      <c r="A282" s="33"/>
       <c r="B282" s="11">
         <v>2000</v>
       </c>
@@ -41843,7 +41729,7 @@
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A283" s="29"/>
+      <c r="A283" s="33"/>
       <c r="B283" s="11">
         <v>2500</v>
       </c>
@@ -41855,7 +41741,7 @@
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A284" s="29"/>
+      <c r="A284" s="33"/>
       <c r="B284" s="11">
         <v>3150</v>
       </c>
@@ -41867,7 +41753,7 @@
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A285" s="29"/>
+      <c r="A285" s="33"/>
       <c r="B285" s="11">
         <v>4000</v>
       </c>
@@ -41879,7 +41765,7 @@
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A286" s="29"/>
+      <c r="A286" s="33"/>
       <c r="B286" s="11">
         <v>5000</v>
       </c>
@@ -41891,7 +41777,7 @@
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A287" s="29"/>
+      <c r="A287" s="33"/>
       <c r="B287" s="11">
         <v>6300</v>
       </c>
@@ -41903,7 +41789,7 @@
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A288" s="29"/>
+      <c r="A288" s="33"/>
       <c r="B288" s="11">
         <v>8000</v>
       </c>
@@ -41913,7 +41799,7 @@
       <c r="D288" s="27"/>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A289" s="30"/>
+      <c r="A289" s="34"/>
       <c r="B289" s="11">
         <v>10000</v>
       </c>
@@ -41923,7 +41809,7 @@
       <c r="D289" s="27"/>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A290" s="28" t="s">
+      <c r="A290" s="32" t="s">
         <v>67</v>
       </c>
       <c r="B290" s="17">
@@ -41935,7 +41821,7 @@
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A291" s="29"/>
+      <c r="A291" s="33"/>
       <c r="B291" s="11">
         <v>250</v>
       </c>
@@ -41945,7 +41831,7 @@
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A292" s="29"/>
+      <c r="A292" s="33"/>
       <c r="B292" s="11">
         <v>315</v>
       </c>
@@ -41957,7 +41843,7 @@
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A293" s="29"/>
+      <c r="A293" s="33"/>
       <c r="B293" s="11">
         <v>400</v>
       </c>
@@ -41969,7 +41855,7 @@
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A294" s="29"/>
+      <c r="A294" s="33"/>
       <c r="B294" s="11">
         <v>500</v>
       </c>
@@ -41981,7 +41867,7 @@
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" s="29"/>
+      <c r="A295" s="33"/>
       <c r="B295" s="11">
         <v>630</v>
       </c>
@@ -41993,7 +41879,7 @@
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A296" s="29"/>
+      <c r="A296" s="33"/>
       <c r="B296" s="11">
         <v>800</v>
       </c>
@@ -42005,7 +41891,7 @@
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A297" s="29"/>
+      <c r="A297" s="33"/>
       <c r="B297" s="11">
         <v>1000</v>
       </c>
@@ -42017,7 +41903,7 @@
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A298" s="29"/>
+      <c r="A298" s="33"/>
       <c r="B298" s="11">
         <v>1250</v>
       </c>
@@ -42029,7 +41915,7 @@
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" s="29"/>
+      <c r="A299" s="33"/>
       <c r="B299" s="11">
         <v>1600</v>
       </c>
@@ -42041,7 +41927,7 @@
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A300" s="29"/>
+      <c r="A300" s="33"/>
       <c r="B300" s="11">
         <v>2000</v>
       </c>
@@ -42053,7 +41939,7 @@
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A301" s="29"/>
+      <c r="A301" s="33"/>
       <c r="B301" s="11">
         <v>2500</v>
       </c>
@@ -42065,7 +41951,7 @@
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A302" s="29"/>
+      <c r="A302" s="33"/>
       <c r="B302" s="11">
         <v>3150</v>
       </c>
@@ -42077,7 +41963,7 @@
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A303" s="29"/>
+      <c r="A303" s="33"/>
       <c r="B303" s="11">
         <v>4000</v>
       </c>
@@ -42089,7 +41975,7 @@
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A304" s="29"/>
+      <c r="A304" s="33"/>
       <c r="B304" s="11">
         <v>5000</v>
       </c>
@@ -42101,7 +41987,7 @@
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A305" s="29"/>
+      <c r="A305" s="33"/>
       <c r="B305" s="11">
         <v>6300</v>
       </c>
@@ -42113,7 +41999,7 @@
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A306" s="29"/>
+      <c r="A306" s="33"/>
       <c r="B306" s="11">
         <v>8000</v>
       </c>
@@ -42123,7 +42009,7 @@
       <c r="D306" s="27"/>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A307" s="30"/>
+      <c r="A307" s="34"/>
       <c r="B307" s="11">
         <v>10000</v>
       </c>
@@ -42133,7 +42019,7 @@
       <c r="D307" s="27"/>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A308" s="28" t="s">
+      <c r="A308" s="32" t="s">
         <v>72</v>
       </c>
       <c r="B308" s="17">
@@ -42143,7 +42029,7 @@
       <c r="D308" s="26"/>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A309" s="29"/>
+      <c r="A309" s="33"/>
       <c r="B309" s="11">
         <v>250</v>
       </c>
@@ -42151,7 +42037,7 @@
       <c r="D309" s="26"/>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A310" s="29"/>
+      <c r="A310" s="33"/>
       <c r="B310" s="11">
         <v>315</v>
       </c>
@@ -42161,7 +42047,7 @@
       <c r="D310" s="26"/>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A311" s="29"/>
+      <c r="A311" s="33"/>
       <c r="B311" s="11">
         <v>400</v>
       </c>
@@ -42171,7 +42057,7 @@
       <c r="D311" s="26"/>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A312" s="29"/>
+      <c r="A312" s="33"/>
       <c r="B312" s="11">
         <v>500</v>
       </c>
@@ -42181,7 +42067,7 @@
       <c r="D312" s="26"/>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A313" s="29"/>
+      <c r="A313" s="33"/>
       <c r="B313" s="11">
         <v>630</v>
       </c>
@@ -42191,7 +42077,7 @@
       <c r="D313" s="26"/>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A314" s="29"/>
+      <c r="A314" s="33"/>
       <c r="B314" s="11">
         <v>800</v>
       </c>
@@ -42201,7 +42087,7 @@
       <c r="D314" s="26"/>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A315" s="29"/>
+      <c r="A315" s="33"/>
       <c r="B315" s="11">
         <v>1000</v>
       </c>
@@ -42211,7 +42097,7 @@
       <c r="D315" s="26"/>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A316" s="29"/>
+      <c r="A316" s="33"/>
       <c r="B316" s="11">
         <v>1250</v>
       </c>
@@ -42221,7 +42107,7 @@
       <c r="D316" s="26"/>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A317" s="29"/>
+      <c r="A317" s="33"/>
       <c r="B317" s="11">
         <v>1600</v>
       </c>
@@ -42231,7 +42117,7 @@
       <c r="D317" s="26"/>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A318" s="29"/>
+      <c r="A318" s="33"/>
       <c r="B318" s="11">
         <v>2000</v>
       </c>
@@ -42241,7 +42127,7 @@
       <c r="D318" s="26"/>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A319" s="29"/>
+      <c r="A319" s="33"/>
       <c r="B319" s="11">
         <v>2500</v>
       </c>
@@ -42251,7 +42137,7 @@
       <c r="D319" s="26"/>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A320" s="29"/>
+      <c r="A320" s="33"/>
       <c r="B320" s="11">
         <v>3150</v>
       </c>
@@ -42261,7 +42147,7 @@
       <c r="D320" s="26"/>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A321" s="29"/>
+      <c r="A321" s="33"/>
       <c r="B321" s="11">
         <v>4000</v>
       </c>
@@ -42271,7 +42157,7 @@
       <c r="D321" s="26"/>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A322" s="29"/>
+      <c r="A322" s="33"/>
       <c r="B322" s="11">
         <v>5000</v>
       </c>
@@ -42281,7 +42167,7 @@
       <c r="D322" s="26"/>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A323" s="29"/>
+      <c r="A323" s="33"/>
       <c r="B323" s="11">
         <v>6300</v>
       </c>
@@ -42291,7 +42177,7 @@
       <c r="D323" s="26"/>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A324" s="29"/>
+      <c r="A324" s="33"/>
       <c r="B324" s="11">
         <v>8000</v>
       </c>
@@ -42301,7 +42187,7 @@
       <c r="D324" s="26"/>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A325" s="30"/>
+      <c r="A325" s="34"/>
       <c r="B325" s="11">
         <v>10000</v>
       </c>
@@ -42311,7 +42197,7 @@
       <c r="D325" s="26"/>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A326" s="28" t="s">
+      <c r="A326" s="32" t="s">
         <v>74</v>
       </c>
       <c r="B326" s="17">
@@ -42321,7 +42207,7 @@
       <c r="D326" s="26"/>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A327" s="29"/>
+      <c r="A327" s="33"/>
       <c r="B327" s="11">
         <v>250</v>
       </c>
@@ -42329,7 +42215,7 @@
       <c r="D327" s="26"/>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A328" s="29"/>
+      <c r="A328" s="33"/>
       <c r="B328" s="11">
         <v>315</v>
       </c>
@@ -42339,7 +42225,7 @@
       <c r="D328" s="26"/>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A329" s="29"/>
+      <c r="A329" s="33"/>
       <c r="B329" s="11">
         <v>400</v>
       </c>
@@ -42349,7 +42235,7 @@
       <c r="D329" s="26"/>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A330" s="29"/>
+      <c r="A330" s="33"/>
       <c r="B330" s="11">
         <v>500</v>
       </c>
@@ -42359,7 +42245,7 @@
       <c r="D330" s="26"/>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A331" s="29"/>
+      <c r="A331" s="33"/>
       <c r="B331" s="11">
         <v>630</v>
       </c>
@@ -42369,7 +42255,7 @@
       <c r="D331" s="26"/>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A332" s="29"/>
+      <c r="A332" s="33"/>
       <c r="B332" s="11">
         <v>800</v>
       </c>
@@ -42379,7 +42265,7 @@
       <c r="D332" s="26"/>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A333" s="29"/>
+      <c r="A333" s="33"/>
       <c r="B333" s="11">
         <v>1000</v>
       </c>
@@ -42389,7 +42275,7 @@
       <c r="D333" s="26"/>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A334" s="29"/>
+      <c r="A334" s="33"/>
       <c r="B334" s="11">
         <v>1250</v>
       </c>
@@ -42399,7 +42285,7 @@
       <c r="D334" s="26"/>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A335" s="29"/>
+      <c r="A335" s="33"/>
       <c r="B335" s="11">
         <v>1600</v>
       </c>
@@ -42409,7 +42295,7 @@
       <c r="D335" s="26"/>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A336" s="29"/>
+      <c r="A336" s="33"/>
       <c r="B336" s="11">
         <v>2000</v>
       </c>
@@ -42419,7 +42305,7 @@
       <c r="D336" s="26"/>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A337" s="29"/>
+      <c r="A337" s="33"/>
       <c r="B337" s="11">
         <v>2500</v>
       </c>
@@ -42429,7 +42315,7 @@
       <c r="D337" s="26"/>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A338" s="29"/>
+      <c r="A338" s="33"/>
       <c r="B338" s="11">
         <v>3150</v>
       </c>
@@ -42439,7 +42325,7 @@
       <c r="D338" s="26"/>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A339" s="29"/>
+      <c r="A339" s="33"/>
       <c r="B339" s="11">
         <v>4000</v>
       </c>
@@ -42449,7 +42335,7 @@
       <c r="D339" s="26"/>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A340" s="29"/>
+      <c r="A340" s="33"/>
       <c r="B340" s="11">
         <v>5000</v>
       </c>
@@ -42459,7 +42345,7 @@
       <c r="D340" s="26"/>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A341" s="29"/>
+      <c r="A341" s="33"/>
       <c r="B341" s="11">
         <v>6300</v>
       </c>
@@ -42469,7 +42355,7 @@
       <c r="D341" s="26"/>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A342" s="29"/>
+      <c r="A342" s="33"/>
       <c r="B342" s="11">
         <v>8000</v>
       </c>
@@ -42479,7 +42365,7 @@
       <c r="D342" s="26"/>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A343" s="30"/>
+      <c r="A343" s="34"/>
       <c r="B343" s="11">
         <v>10000</v>
       </c>
@@ -42489,7 +42375,7 @@
       <c r="D343" s="26"/>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A344" s="28" t="s">
+      <c r="A344" s="32" t="s">
         <v>91</v>
       </c>
       <c r="B344" s="17">
@@ -42499,7 +42385,7 @@
       <c r="D344" s="26"/>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A345" s="29"/>
+      <c r="A345" s="33"/>
       <c r="B345" s="11">
         <v>250</v>
       </c>
@@ -42507,7 +42393,7 @@
       <c r="D345" s="26"/>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A346" s="29"/>
+      <c r="A346" s="33"/>
       <c r="B346" s="11">
         <v>315</v>
       </c>
@@ -42517,7 +42403,7 @@
       <c r="D346" s="26"/>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A347" s="29"/>
+      <c r="A347" s="33"/>
       <c r="B347" s="11">
         <v>400</v>
       </c>
@@ -42527,7 +42413,7 @@
       <c r="D347" s="26"/>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A348" s="29"/>
+      <c r="A348" s="33"/>
       <c r="B348" s="11">
         <v>500</v>
       </c>
@@ -42537,7 +42423,7 @@
       <c r="D348" s="26"/>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A349" s="29"/>
+      <c r="A349" s="33"/>
       <c r="B349" s="11">
         <v>630</v>
       </c>
@@ -42547,7 +42433,7 @@
       <c r="D349" s="26"/>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A350" s="29"/>
+      <c r="A350" s="33"/>
       <c r="B350" s="11">
         <v>800</v>
       </c>
@@ -42557,7 +42443,7 @@
       <c r="D350" s="26"/>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A351" s="29"/>
+      <c r="A351" s="33"/>
       <c r="B351" s="11">
         <v>1000</v>
       </c>
@@ -42567,7 +42453,7 @@
       <c r="D351" s="26"/>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A352" s="29"/>
+      <c r="A352" s="33"/>
       <c r="B352" s="11">
         <v>1250</v>
       </c>
@@ -42577,7 +42463,7 @@
       <c r="D352" s="26"/>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A353" s="29"/>
+      <c r="A353" s="33"/>
       <c r="B353" s="11">
         <v>1600</v>
       </c>
@@ -42587,7 +42473,7 @@
       <c r="D353" s="26"/>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A354" s="29"/>
+      <c r="A354" s="33"/>
       <c r="B354" s="11">
         <v>2000</v>
       </c>
@@ -42597,7 +42483,7 @@
       <c r="D354" s="26"/>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A355" s="29"/>
+      <c r="A355" s="33"/>
       <c r="B355" s="11">
         <v>2500</v>
       </c>
@@ -42607,7 +42493,7 @@
       <c r="D355" s="26"/>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A356" s="29"/>
+      <c r="A356" s="33"/>
       <c r="B356" s="11">
         <v>3150</v>
       </c>
@@ -42617,7 +42503,7 @@
       <c r="D356" s="26"/>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A357" s="29"/>
+      <c r="A357" s="33"/>
       <c r="B357" s="11">
         <v>4000</v>
       </c>
@@ -42627,7 +42513,7 @@
       <c r="D357" s="26"/>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A358" s="29"/>
+      <c r="A358" s="33"/>
       <c r="B358" s="11">
         <v>5000</v>
       </c>
@@ -42637,7 +42523,7 @@
       <c r="D358" s="26"/>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A359" s="29"/>
+      <c r="A359" s="33"/>
       <c r="B359" s="11">
         <v>6300</v>
       </c>
@@ -42647,7 +42533,7 @@
       <c r="D359" s="26"/>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A360" s="29"/>
+      <c r="A360" s="33"/>
       <c r="B360" s="11">
         <v>8000</v>
       </c>
@@ -42657,7 +42543,7 @@
       <c r="D360" s="26"/>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A361" s="30"/>
+      <c r="A361" s="34"/>
       <c r="B361" s="11">
         <v>10000</v>
       </c>
@@ -42667,7 +42553,7 @@
       <c r="D361" s="26"/>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A362" s="28" t="s">
+      <c r="A362" s="32" t="s">
         <v>92</v>
       </c>
       <c r="B362" s="17">
@@ -42677,7 +42563,7 @@
       <c r="D362" s="15"/>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A363" s="29"/>
+      <c r="A363" s="33"/>
       <c r="B363" s="11">
         <v>250</v>
       </c>
@@ -42685,7 +42571,7 @@
       <c r="D363" s="15"/>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A364" s="29"/>
+      <c r="A364" s="33"/>
       <c r="B364" s="11">
         <v>315</v>
       </c>
@@ -42695,7 +42581,7 @@
       <c r="D364" s="15"/>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A365" s="29"/>
+      <c r="A365" s="33"/>
       <c r="B365" s="11">
         <v>400</v>
       </c>
@@ -42705,7 +42591,7 @@
       <c r="D365" s="15"/>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A366" s="29"/>
+      <c r="A366" s="33"/>
       <c r="B366" s="11">
         <v>500</v>
       </c>
@@ -42715,7 +42601,7 @@
       <c r="D366" s="15"/>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A367" s="29"/>
+      <c r="A367" s="33"/>
       <c r="B367" s="11">
         <v>630</v>
       </c>
@@ -42725,7 +42611,7 @@
       <c r="D367" s="15"/>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A368" s="29"/>
+      <c r="A368" s="33"/>
       <c r="B368" s="11">
         <v>800</v>
       </c>
@@ -42735,7 +42621,7 @@
       <c r="D368" s="15"/>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A369" s="29"/>
+      <c r="A369" s="33"/>
       <c r="B369" s="11">
         <v>1000</v>
       </c>
@@ -42745,7 +42631,7 @@
       <c r="D369" s="15"/>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A370" s="29"/>
+      <c r="A370" s="33"/>
       <c r="B370" s="11">
         <v>1250</v>
       </c>
@@ -42755,7 +42641,7 @@
       <c r="D370" s="15"/>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A371" s="29"/>
+      <c r="A371" s="33"/>
       <c r="B371" s="11">
         <v>1600</v>
       </c>
@@ -42765,7 +42651,7 @@
       <c r="D371" s="15"/>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A372" s="29"/>
+      <c r="A372" s="33"/>
       <c r="B372" s="11">
         <v>2000</v>
       </c>
@@ -42775,7 +42661,7 @@
       <c r="D372" s="15"/>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A373" s="29"/>
+      <c r="A373" s="33"/>
       <c r="B373" s="11">
         <v>2500</v>
       </c>
@@ -42785,7 +42671,7 @@
       <c r="D373" s="15"/>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A374" s="29"/>
+      <c r="A374" s="33"/>
       <c r="B374" s="11">
         <v>3150</v>
       </c>
@@ -42795,7 +42681,7 @@
       <c r="D374" s="15"/>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A375" s="29"/>
+      <c r="A375" s="33"/>
       <c r="B375" s="11">
         <v>4000</v>
       </c>
@@ -42805,7 +42691,7 @@
       <c r="D375" s="15"/>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A376" s="29"/>
+      <c r="A376" s="33"/>
       <c r="B376" s="11">
         <v>5000</v>
       </c>
@@ -42815,7 +42701,7 @@
       <c r="D376" s="15"/>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A377" s="29"/>
+      <c r="A377" s="33"/>
       <c r="B377" s="11">
         <v>6300</v>
       </c>
@@ -42825,7 +42711,7 @@
       <c r="D377" s="15"/>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A378" s="29"/>
+      <c r="A378" s="33"/>
       <c r="B378" s="11">
         <v>8000</v>
       </c>
@@ -42835,7 +42721,7 @@
       <c r="D378" s="15"/>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A379" s="30"/>
+      <c r="A379" s="34"/>
       <c r="B379" s="11">
         <v>10000</v>
       </c>
@@ -42845,7 +42731,7 @@
       <c r="D379" s="15"/>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A380" s="28" t="s">
+      <c r="A380" s="32" t="s">
         <v>93</v>
       </c>
       <c r="B380" s="17">
@@ -42855,7 +42741,7 @@
       <c r="D380" s="15"/>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A381" s="29"/>
+      <c r="A381" s="33"/>
       <c r="B381" s="11">
         <v>250</v>
       </c>
@@ -42863,7 +42749,7 @@
       <c r="D381" s="15"/>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A382" s="29"/>
+      <c r="A382" s="33"/>
       <c r="B382" s="11">
         <v>315</v>
       </c>
@@ -42873,7 +42759,7 @@
       <c r="D382" s="15"/>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A383" s="29"/>
+      <c r="A383" s="33"/>
       <c r="B383" s="11">
         <v>400</v>
       </c>
@@ -42883,7 +42769,7 @@
       <c r="D383" s="15"/>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A384" s="29"/>
+      <c r="A384" s="33"/>
       <c r="B384" s="11">
         <v>500</v>
       </c>
@@ -42893,7 +42779,7 @@
       <c r="D384" s="15"/>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A385" s="29"/>
+      <c r="A385" s="33"/>
       <c r="B385" s="11">
         <v>630</v>
       </c>
@@ -42903,7 +42789,7 @@
       <c r="D385" s="15"/>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A386" s="29"/>
+      <c r="A386" s="33"/>
       <c r="B386" s="11">
         <v>800</v>
       </c>
@@ -42913,7 +42799,7 @@
       <c r="D386" s="15"/>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A387" s="29"/>
+      <c r="A387" s="33"/>
       <c r="B387" s="11">
         <v>1000</v>
       </c>
@@ -42923,7 +42809,7 @@
       <c r="D387" s="15"/>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A388" s="29"/>
+      <c r="A388" s="33"/>
       <c r="B388" s="11">
         <v>1250</v>
       </c>
@@ -42933,7 +42819,7 @@
       <c r="D388" s="15"/>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A389" s="29"/>
+      <c r="A389" s="33"/>
       <c r="B389" s="11">
         <v>1600</v>
       </c>
@@ -42943,7 +42829,7 @@
       <c r="D389" s="15"/>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A390" s="29"/>
+      <c r="A390" s="33"/>
       <c r="B390" s="11">
         <v>2000</v>
       </c>
@@ -42953,7 +42839,7 @@
       <c r="D390" s="15"/>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A391" s="29"/>
+      <c r="A391" s="33"/>
       <c r="B391" s="11">
         <v>2500</v>
       </c>
@@ -42963,7 +42849,7 @@
       <c r="D391" s="15"/>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A392" s="29"/>
+      <c r="A392" s="33"/>
       <c r="B392" s="11">
         <v>3150</v>
       </c>
@@ -42973,7 +42859,7 @@
       <c r="D392" s="15"/>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A393" s="29"/>
+      <c r="A393" s="33"/>
       <c r="B393" s="11">
         <v>4000</v>
       </c>
@@ -42983,7 +42869,7 @@
       <c r="D393" s="15"/>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A394" s="29"/>
+      <c r="A394" s="33"/>
       <c r="B394" s="11">
         <v>5000</v>
       </c>
@@ -42993,7 +42879,7 @@
       <c r="D394" s="15"/>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A395" s="29"/>
+      <c r="A395" s="33"/>
       <c r="B395" s="11">
         <v>6300</v>
       </c>
@@ -43003,7 +42889,7 @@
       <c r="D395" s="15"/>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A396" s="29"/>
+      <c r="A396" s="33"/>
       <c r="B396" s="11">
         <v>8000</v>
       </c>
@@ -43013,7 +42899,7 @@
       <c r="D396" s="15"/>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A397" s="30"/>
+      <c r="A397" s="34"/>
       <c r="B397" s="11">
         <v>10000</v>
       </c>
@@ -43023,7 +42909,7 @@
       <c r="D397" s="15"/>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A398" s="28" t="s">
+      <c r="A398" s="32" t="s">
         <v>100</v>
       </c>
       <c r="B398" s="17">
@@ -43033,7 +42919,7 @@
       <c r="D398" s="15"/>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A399" s="29"/>
+      <c r="A399" s="33"/>
       <c r="B399" s="11">
         <v>250</v>
       </c>
@@ -43041,7 +42927,7 @@
       <c r="D399" s="15"/>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A400" s="29"/>
+      <c r="A400" s="33"/>
       <c r="B400" s="11">
         <v>315</v>
       </c>
@@ -43051,7 +42937,7 @@
       <c r="D400" s="15"/>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A401" s="29"/>
+      <c r="A401" s="33"/>
       <c r="B401" s="11">
         <v>400</v>
       </c>
@@ -43061,7 +42947,7 @@
       <c r="D401" s="15"/>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A402" s="29"/>
+      <c r="A402" s="33"/>
       <c r="B402" s="11">
         <v>500</v>
       </c>
@@ -43071,7 +42957,7 @@
       <c r="D402" s="15"/>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A403" s="29"/>
+      <c r="A403" s="33"/>
       <c r="B403" s="11">
         <v>630</v>
       </c>
@@ -43081,7 +42967,7 @@
       <c r="D403" s="15"/>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A404" s="29"/>
+      <c r="A404" s="33"/>
       <c r="B404" s="11">
         <v>800</v>
       </c>
@@ -43091,7 +42977,7 @@
       <c r="D404" s="15"/>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A405" s="29"/>
+      <c r="A405" s="33"/>
       <c r="B405" s="11">
         <v>1000</v>
       </c>
@@ -43101,7 +42987,7 @@
       <c r="D405" s="15"/>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A406" s="29"/>
+      <c r="A406" s="33"/>
       <c r="B406" s="11">
         <v>1250</v>
       </c>
@@ -43111,7 +42997,7 @@
       <c r="D406" s="15"/>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A407" s="29"/>
+      <c r="A407" s="33"/>
       <c r="B407" s="11">
         <v>1600</v>
       </c>
@@ -43121,7 +43007,7 @@
       <c r="D407" s="15"/>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A408" s="29"/>
+      <c r="A408" s="33"/>
       <c r="B408" s="11">
         <v>2000</v>
       </c>
@@ -43131,7 +43017,7 @@
       <c r="D408" s="15"/>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A409" s="29"/>
+      <c r="A409" s="33"/>
       <c r="B409" s="11">
         <v>2500</v>
       </c>
@@ -43141,7 +43027,7 @@
       <c r="D409" s="15"/>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A410" s="29"/>
+      <c r="A410" s="33"/>
       <c r="B410" s="11">
         <v>3150</v>
       </c>
@@ -43151,7 +43037,7 @@
       <c r="D410" s="15"/>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A411" s="29"/>
+      <c r="A411" s="33"/>
       <c r="B411" s="11">
         <v>4000</v>
       </c>
@@ -43161,7 +43047,7 @@
       <c r="D411" s="15"/>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A412" s="29"/>
+      <c r="A412" s="33"/>
       <c r="B412" s="11">
         <v>5000</v>
       </c>
@@ -43171,7 +43057,7 @@
       <c r="D412" s="15"/>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A413" s="29"/>
+      <c r="A413" s="33"/>
       <c r="B413" s="11">
         <v>6300</v>
       </c>
@@ -43181,7 +43067,7 @@
       <c r="D413" s="15"/>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A414" s="29"/>
+      <c r="A414" s="33"/>
       <c r="B414" s="11">
         <v>8000</v>
       </c>
@@ -43191,7 +43077,7 @@
       <c r="D414" s="15"/>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A415" s="30"/>
+      <c r="A415" s="34"/>
       <c r="B415" s="11">
         <v>10000</v>
       </c>
@@ -43201,7 +43087,7 @@
       <c r="D415" s="15"/>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A416" s="28" t="s">
+      <c r="A416" s="32" t="s">
         <v>106</v>
       </c>
       <c r="B416" s="17">
@@ -43211,7 +43097,7 @@
       <c r="D416" s="15"/>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A417" s="29"/>
+      <c r="A417" s="33"/>
       <c r="B417" s="11">
         <v>250</v>
       </c>
@@ -43219,7 +43105,7 @@
       <c r="D417" s="15"/>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A418" s="29"/>
+      <c r="A418" s="33"/>
       <c r="B418" s="11">
         <v>315</v>
       </c>
@@ -43229,7 +43115,7 @@
       <c r="D418" s="15"/>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A419" s="29"/>
+      <c r="A419" s="33"/>
       <c r="B419" s="11">
         <v>400</v>
       </c>
@@ -43239,7 +43125,7 @@
       <c r="D419" s="15"/>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A420" s="29"/>
+      <c r="A420" s="33"/>
       <c r="B420" s="11">
         <v>500</v>
       </c>
@@ -43249,7 +43135,7 @@
       <c r="D420" s="15"/>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A421" s="29"/>
+      <c r="A421" s="33"/>
       <c r="B421" s="11">
         <v>630</v>
       </c>
@@ -43259,7 +43145,7 @@
       <c r="D421" s="15"/>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A422" s="29"/>
+      <c r="A422" s="33"/>
       <c r="B422" s="11">
         <v>800</v>
       </c>
@@ -43269,7 +43155,7 @@
       <c r="D422" s="15"/>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A423" s="29"/>
+      <c r="A423" s="33"/>
       <c r="B423" s="11">
         <v>1000</v>
       </c>
@@ -43279,7 +43165,7 @@
       <c r="D423" s="15"/>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A424" s="29"/>
+      <c r="A424" s="33"/>
       <c r="B424" s="11">
         <v>1250</v>
       </c>
@@ -43289,7 +43175,7 @@
       <c r="D424" s="15"/>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A425" s="29"/>
+      <c r="A425" s="33"/>
       <c r="B425" s="11">
         <v>1600</v>
       </c>
@@ -43299,7 +43185,7 @@
       <c r="D425" s="15"/>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A426" s="29"/>
+      <c r="A426" s="33"/>
       <c r="B426" s="11">
         <v>2000</v>
       </c>
@@ -43309,7 +43195,7 @@
       <c r="D426" s="15"/>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A427" s="29"/>
+      <c r="A427" s="33"/>
       <c r="B427" s="11">
         <v>2500</v>
       </c>
@@ -43319,7 +43205,7 @@
       <c r="D427" s="15"/>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A428" s="29"/>
+      <c r="A428" s="33"/>
       <c r="B428" s="11">
         <v>3150</v>
       </c>
@@ -43329,7 +43215,7 @@
       <c r="D428" s="15"/>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A429" s="29"/>
+      <c r="A429" s="33"/>
       <c r="B429" s="11">
         <v>4000</v>
       </c>
@@ -43339,7 +43225,7 @@
       <c r="D429" s="15"/>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A430" s="29"/>
+      <c r="A430" s="33"/>
       <c r="B430" s="11">
         <v>5000</v>
       </c>
@@ -43349,7 +43235,7 @@
       <c r="D430" s="15"/>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A431" s="29"/>
+      <c r="A431" s="33"/>
       <c r="B431" s="11">
         <v>6300</v>
       </c>
@@ -43359,7 +43245,7 @@
       <c r="D431" s="15"/>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A432" s="29"/>
+      <c r="A432" s="33"/>
       <c r="B432" s="11">
         <v>8000</v>
       </c>
@@ -43369,7 +43255,7 @@
       <c r="D432" s="15"/>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A433" s="30"/>
+      <c r="A433" s="34"/>
       <c r="B433" s="11">
         <v>10000</v>
       </c>
@@ -43379,7 +43265,7 @@
       <c r="D433" s="15"/>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A434" s="28" t="s">
+      <c r="A434" s="32" t="s">
         <v>107</v>
       </c>
       <c r="B434" s="17">
@@ -43389,7 +43275,7 @@
       <c r="D434" s="15"/>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A435" s="29"/>
+      <c r="A435" s="33"/>
       <c r="B435" s="11">
         <v>250</v>
       </c>
@@ -43397,7 +43283,7 @@
       <c r="D435" s="15"/>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A436" s="29"/>
+      <c r="A436" s="33"/>
       <c r="B436" s="11">
         <v>315</v>
       </c>
@@ -43407,7 +43293,7 @@
       <c r="D436" s="15"/>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A437" s="29"/>
+      <c r="A437" s="33"/>
       <c r="B437" s="11">
         <v>400</v>
       </c>
@@ -43417,7 +43303,7 @@
       <c r="D437" s="15"/>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A438" s="29"/>
+      <c r="A438" s="33"/>
       <c r="B438" s="11">
         <v>500</v>
       </c>
@@ -43427,7 +43313,7 @@
       <c r="D438" s="15"/>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A439" s="29"/>
+      <c r="A439" s="33"/>
       <c r="B439" s="11">
         <v>630</v>
       </c>
@@ -43437,7 +43323,7 @@
       <c r="D439" s="15"/>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A440" s="29"/>
+      <c r="A440" s="33"/>
       <c r="B440" s="11">
         <v>800</v>
       </c>
@@ -43447,7 +43333,7 @@
       <c r="D440" s="15"/>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A441" s="29"/>
+      <c r="A441" s="33"/>
       <c r="B441" s="11">
         <v>1000</v>
       </c>
@@ -43457,7 +43343,7 @@
       <c r="D441" s="15"/>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A442" s="29"/>
+      <c r="A442" s="33"/>
       <c r="B442" s="11">
         <v>1250</v>
       </c>
@@ -43467,7 +43353,7 @@
       <c r="D442" s="15"/>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A443" s="29"/>
+      <c r="A443" s="33"/>
       <c r="B443" s="11">
         <v>1600</v>
       </c>
@@ -43477,7 +43363,7 @@
       <c r="D443" s="15"/>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A444" s="29"/>
+      <c r="A444" s="33"/>
       <c r="B444" s="11">
         <v>2000</v>
       </c>
@@ -43487,7 +43373,7 @@
       <c r="D444" s="15"/>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A445" s="29"/>
+      <c r="A445" s="33"/>
       <c r="B445" s="11">
         <v>2500</v>
       </c>
@@ -43497,7 +43383,7 @@
       <c r="D445" s="15"/>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A446" s="29"/>
+      <c r="A446" s="33"/>
       <c r="B446" s="11">
         <v>3150</v>
       </c>
@@ -43507,7 +43393,7 @@
       <c r="D446" s="15"/>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A447" s="29"/>
+      <c r="A447" s="33"/>
       <c r="B447" s="11">
         <v>4000</v>
       </c>
@@ -43517,7 +43403,7 @@
       <c r="D447" s="15"/>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A448" s="29"/>
+      <c r="A448" s="33"/>
       <c r="B448" s="11">
         <v>5000</v>
       </c>
@@ -43527,7 +43413,7 @@
       <c r="D448" s="15"/>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A449" s="29"/>
+      <c r="A449" s="33"/>
       <c r="B449" s="11">
         <v>6300</v>
       </c>
@@ -43537,7 +43423,7 @@
       <c r="D449" s="15"/>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A450" s="29"/>
+      <c r="A450" s="33"/>
       <c r="B450" s="11">
         <v>8000</v>
       </c>
@@ -43547,7 +43433,7 @@
       <c r="D450" s="15"/>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A451" s="30"/>
+      <c r="A451" s="34"/>
       <c r="B451" s="11">
         <v>10000</v>
       </c>
@@ -43557,7 +43443,7 @@
       <c r="D451" s="15"/>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A452" s="28" t="s">
+      <c r="A452" s="32" t="s">
         <v>111</v>
       </c>
       <c r="B452" s="17">
@@ -43567,7 +43453,7 @@
       <c r="D452" s="15"/>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A453" s="29"/>
+      <c r="A453" s="33"/>
       <c r="B453" s="11">
         <v>250</v>
       </c>
@@ -43575,7 +43461,7 @@
       <c r="D453" s="15"/>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A454" s="29"/>
+      <c r="A454" s="33"/>
       <c r="B454" s="11">
         <v>315</v>
       </c>
@@ -43585,7 +43471,7 @@
       <c r="D454" s="15"/>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A455" s="29"/>
+      <c r="A455" s="33"/>
       <c r="B455" s="11">
         <v>400</v>
       </c>
@@ -43595,7 +43481,7 @@
       <c r="D455" s="15"/>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A456" s="29"/>
+      <c r="A456" s="33"/>
       <c r="B456" s="11">
         <v>500</v>
       </c>
@@ -43605,7 +43491,7 @@
       <c r="D456" s="15"/>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A457" s="29"/>
+      <c r="A457" s="33"/>
       <c r="B457" s="11">
         <v>630</v>
       </c>
@@ -43615,7 +43501,7 @@
       <c r="D457" s="15"/>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A458" s="29"/>
+      <c r="A458" s="33"/>
       <c r="B458" s="11">
         <v>800</v>
       </c>
@@ -43625,7 +43511,7 @@
       <c r="D458" s="15"/>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A459" s="29"/>
+      <c r="A459" s="33"/>
       <c r="B459" s="11">
         <v>1000</v>
       </c>
@@ -43635,7 +43521,7 @@
       <c r="D459" s="15"/>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A460" s="29"/>
+      <c r="A460" s="33"/>
       <c r="B460" s="11">
         <v>1250</v>
       </c>
@@ -43645,7 +43531,7 @@
       <c r="D460" s="15"/>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A461" s="29"/>
+      <c r="A461" s="33"/>
       <c r="B461" s="11">
         <v>1600</v>
       </c>
@@ -43655,7 +43541,7 @@
       <c r="D461" s="15"/>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A462" s="29"/>
+      <c r="A462" s="33"/>
       <c r="B462" s="11">
         <v>2000</v>
       </c>
@@ -43665,7 +43551,7 @@
       <c r="D462" s="15"/>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A463" s="29"/>
+      <c r="A463" s="33"/>
       <c r="B463" s="11">
         <v>2500</v>
       </c>
@@ -43675,7 +43561,7 @@
       <c r="D463" s="15"/>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A464" s="29"/>
+      <c r="A464" s="33"/>
       <c r="B464" s="11">
         <v>3150</v>
       </c>
@@ -43685,7 +43571,7 @@
       <c r="D464" s="15"/>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A465" s="29"/>
+      <c r="A465" s="33"/>
       <c r="B465" s="11">
         <v>4000</v>
       </c>
@@ -43695,7 +43581,7 @@
       <c r="D465" s="15"/>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A466" s="29"/>
+      <c r="A466" s="33"/>
       <c r="B466" s="11">
         <v>5000</v>
       </c>
@@ -43705,7 +43591,7 @@
       <c r="D466" s="15"/>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A467" s="29"/>
+      <c r="A467" s="33"/>
       <c r="B467" s="11">
         <v>6300</v>
       </c>
@@ -43715,7 +43601,7 @@
       <c r="D467" s="15"/>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A468" s="29"/>
+      <c r="A468" s="33"/>
       <c r="B468" s="11">
         <v>8000</v>
       </c>
@@ -43725,7 +43611,7 @@
       <c r="D468" s="15"/>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A469" s="30"/>
+      <c r="A469" s="34"/>
       <c r="B469" s="11">
         <v>10000</v>
       </c>
@@ -43736,6 +43622,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A452:A469"/>
+    <mergeCell ref="A164:A181"/>
+    <mergeCell ref="A434:A451"/>
+    <mergeCell ref="A344:A361"/>
+    <mergeCell ref="A326:A343"/>
+    <mergeCell ref="A308:A325"/>
+    <mergeCell ref="A380:A397"/>
+    <mergeCell ref="A398:A415"/>
+    <mergeCell ref="A362:A379"/>
+    <mergeCell ref="A416:A433"/>
     <mergeCell ref="A2:A19"/>
     <mergeCell ref="A290:A307"/>
     <mergeCell ref="A254:A271"/>
@@ -43752,16 +43648,6 @@
     <mergeCell ref="A146:A163"/>
     <mergeCell ref="A218:A235"/>
     <mergeCell ref="A128:A145"/>
-    <mergeCell ref="A452:A469"/>
-    <mergeCell ref="A164:A181"/>
-    <mergeCell ref="A434:A451"/>
-    <mergeCell ref="A344:A361"/>
-    <mergeCell ref="A326:A343"/>
-    <mergeCell ref="A308:A325"/>
-    <mergeCell ref="A380:A397"/>
-    <mergeCell ref="A398:A415"/>
-    <mergeCell ref="A362:A379"/>
-    <mergeCell ref="A416:A433"/>
   </mergeCells>
   <conditionalFormatting sqref="B470:B1048576 C1:C469">
     <cfRule type="colorScale" priority="113">
@@ -44135,10 +44021,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="31">
+      <c r="B2" s="28">
         <v>315</v>
       </c>
       <c r="C2">
@@ -44146,8 +44032,8 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="29"/>
-      <c r="B3" s="32">
+      <c r="A3" s="33"/>
+      <c r="B3" s="29">
         <v>400</v>
       </c>
       <c r="C3">
@@ -44155,8 +44041,8 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="29"/>
-      <c r="B4" s="32">
+      <c r="A4" s="33"/>
+      <c r="B4" s="29">
         <v>500</v>
       </c>
       <c r="C4">
@@ -44164,8 +44050,8 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="29"/>
-      <c r="B5" s="32">
+      <c r="A5" s="33"/>
+      <c r="B5" s="29">
         <v>630</v>
       </c>
       <c r="C5">
@@ -44173,8 +44059,8 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="29"/>
-      <c r="B6" s="32">
+      <c r="A6" s="33"/>
+      <c r="B6" s="29">
         <v>800</v>
       </c>
       <c r="C6">
@@ -44182,8 +44068,8 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="29"/>
-      <c r="B7" s="32">
+      <c r="A7" s="33"/>
+      <c r="B7" s="29">
         <v>1000</v>
       </c>
       <c r="C7">
@@ -44191,8 +44077,8 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
-      <c r="B8" s="32">
+      <c r="A8" s="33"/>
+      <c r="B8" s="29">
         <v>1250</v>
       </c>
       <c r="C8">
@@ -44200,8 +44086,8 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
-      <c r="B9" s="32">
+      <c r="A9" s="33"/>
+      <c r="B9" s="29">
         <v>1600</v>
       </c>
       <c r="C9">
@@ -44209,8 +44095,8 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="32">
+      <c r="A10" s="33"/>
+      <c r="B10" s="29">
         <v>2000</v>
       </c>
       <c r="C10">
@@ -44218,8 +44104,8 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="32">
+      <c r="A11" s="33"/>
+      <c r="B11" s="29">
         <v>2500</v>
       </c>
       <c r="C11">
@@ -44227,8 +44113,8 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="32">
+      <c r="A12" s="33"/>
+      <c r="B12" s="29">
         <v>3150</v>
       </c>
       <c r="C12">
@@ -44236,8 +44122,8 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
-      <c r="B13" s="32">
+      <c r="A13" s="33"/>
+      <c r="B13" s="29">
         <v>4000</v>
       </c>
       <c r="C13">
@@ -44245,8 +44131,8 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="29"/>
-      <c r="B14" s="32">
+      <c r="A14" s="33"/>
+      <c r="B14" s="29">
         <v>5000</v>
       </c>
       <c r="C14">
@@ -44254,8 +44140,8 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
-      <c r="B15" s="32">
+      <c r="A15" s="33"/>
+      <c r="B15" s="29">
         <v>6300</v>
       </c>
       <c r="C15">
@@ -44263,8 +44149,8 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="29"/>
-      <c r="B16" s="32">
+      <c r="A16" s="33"/>
+      <c r="B16" s="29">
         <v>8000</v>
       </c>
       <c r="C16">
@@ -44272,8 +44158,8 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
-      <c r="B17" s="32">
+      <c r="A17" s="33"/>
+      <c r="B17" s="29">
         <v>10000</v>
       </c>
       <c r="C17">
@@ -44281,8 +44167,8 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="29"/>
-      <c r="B18" s="32">
+      <c r="A18" s="33"/>
+      <c r="B18" s="29">
         <v>12700</v>
       </c>
       <c r="C18">
@@ -44290,15 +44176,15 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="34"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="28">
         <v>315</v>
       </c>
       <c r="C20">
@@ -44306,8 +44192,8 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="29"/>
-      <c r="B21" s="32">
+      <c r="A21" s="33"/>
+      <c r="B21" s="29">
         <v>400</v>
       </c>
       <c r="C21">
@@ -44315,8 +44201,8 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="29"/>
-      <c r="B22" s="32">
+      <c r="A22" s="33"/>
+      <c r="B22" s="29">
         <v>500</v>
       </c>
       <c r="C22">
@@ -44324,8 +44210,8 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="29"/>
-      <c r="B23" s="32">
+      <c r="A23" s="33"/>
+      <c r="B23" s="29">
         <v>630</v>
       </c>
       <c r="C23">
@@ -44333,8 +44219,8 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="29"/>
-      <c r="B24" s="32">
+      <c r="A24" s="33"/>
+      <c r="B24" s="29">
         <v>800</v>
       </c>
       <c r="C24">
@@ -44342,8 +44228,8 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="29"/>
-      <c r="B25" s="32">
+      <c r="A25" s="33"/>
+      <c r="B25" s="29">
         <v>1000</v>
       </c>
       <c r="C25">
@@ -44351,8 +44237,8 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="29"/>
-      <c r="B26" s="32">
+      <c r="A26" s="33"/>
+      <c r="B26" s="29">
         <v>1250</v>
       </c>
       <c r="C26">
@@ -44360,8 +44246,8 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="29"/>
-      <c r="B27" s="32">
+      <c r="A27" s="33"/>
+      <c r="B27" s="29">
         <v>1600</v>
       </c>
       <c r="C27">
@@ -44369,8 +44255,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="29"/>
-      <c r="B28" s="32">
+      <c r="A28" s="33"/>
+      <c r="B28" s="29">
         <v>2000</v>
       </c>
       <c r="C28">
@@ -44378,8 +44264,8 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
-      <c r="B29" s="32">
+      <c r="A29" s="33"/>
+      <c r="B29" s="29">
         <v>2500</v>
       </c>
       <c r="C29">
@@ -44387,8 +44273,8 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
-      <c r="B30" s="32">
+      <c r="A30" s="33"/>
+      <c r="B30" s="29">
         <v>3150</v>
       </c>
       <c r="C30">
@@ -44396,8 +44282,8 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
-      <c r="B31" s="32">
+      <c r="A31" s="33"/>
+      <c r="B31" s="29">
         <v>4000</v>
       </c>
       <c r="C31">
@@ -44405,8 +44291,8 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="29"/>
-      <c r="B32" s="32">
+      <c r="A32" s="33"/>
+      <c r="B32" s="29">
         <v>5000</v>
       </c>
       <c r="C32">
@@ -44414,8 +44300,8 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="29"/>
-      <c r="B33" s="32">
+      <c r="A33" s="33"/>
+      <c r="B33" s="29">
         <v>6300</v>
       </c>
       <c r="C33">
@@ -44423,8 +44309,8 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="29"/>
-      <c r="B34" s="32">
+      <c r="A34" s="33"/>
+      <c r="B34" s="29">
         <v>8000</v>
       </c>
       <c r="C34">
@@ -44432,8 +44318,8 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="29"/>
-      <c r="B35" s="32">
+      <c r="A35" s="33"/>
+      <c r="B35" s="29">
         <v>10000</v>
       </c>
       <c r="C35">
@@ -44441,8 +44327,8 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="29"/>
-      <c r="B36" s="32">
+      <c r="A36" s="33"/>
+      <c r="B36" s="29">
         <v>12700</v>
       </c>
       <c r="C36">
@@ -44450,2661 +44336,2661 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="30"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="34"/>
+      <c r="A37" s="34"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="31"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="31">
+      <c r="B38" s="28">
         <v>315</v>
       </c>
       <c r="C38" s="23"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="29"/>
-      <c r="B39" s="32">
+      <c r="A39" s="33"/>
+      <c r="B39" s="29">
         <v>400</v>
       </c>
       <c r="C39" s="23"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="29"/>
-      <c r="B40" s="32">
+      <c r="A40" s="33"/>
+      <c r="B40" s="29">
         <v>500</v>
       </c>
       <c r="C40" s="23"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="29"/>
-      <c r="B41" s="32">
+      <c r="A41" s="33"/>
+      <c r="B41" s="29">
         <v>630</v>
       </c>
       <c r="C41" s="23"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="29"/>
-      <c r="B42" s="32">
+      <c r="A42" s="33"/>
+      <c r="B42" s="29">
         <v>800</v>
       </c>
       <c r="C42" s="23"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="29"/>
-      <c r="B43" s="32">
+      <c r="A43" s="33"/>
+      <c r="B43" s="29">
         <v>1000</v>
       </c>
       <c r="C43" s="23"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="29"/>
-      <c r="B44" s="32">
+      <c r="A44" s="33"/>
+      <c r="B44" s="29">
         <v>1250</v>
       </c>
       <c r="C44" s="23"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="29"/>
-      <c r="B45" s="32">
+      <c r="A45" s="33"/>
+      <c r="B45" s="29">
         <v>1600</v>
       </c>
       <c r="C45" s="23"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="29"/>
-      <c r="B46" s="32">
+      <c r="A46" s="33"/>
+      <c r="B46" s="29">
         <v>2000</v>
       </c>
       <c r="C46" s="23"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="29"/>
-      <c r="B47" s="32">
+      <c r="A47" s="33"/>
+      <c r="B47" s="29">
         <v>2500</v>
       </c>
       <c r="C47" s="23"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="29"/>
-      <c r="B48" s="32">
+      <c r="A48" s="33"/>
+      <c r="B48" s="29">
         <v>3150</v>
       </c>
       <c r="C48" s="23"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="29"/>
-      <c r="B49" s="32">
+      <c r="A49" s="33"/>
+      <c r="B49" s="29">
         <v>4000</v>
       </c>
       <c r="C49" s="23"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="29"/>
-      <c r="B50" s="32">
+      <c r="A50" s="33"/>
+      <c r="B50" s="29">
         <v>5000</v>
       </c>
       <c r="C50" s="23"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="29"/>
-      <c r="B51" s="32">
+      <c r="A51" s="33"/>
+      <c r="B51" s="29">
         <v>6300</v>
       </c>
       <c r="C51" s="23"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="29"/>
-      <c r="B52" s="32">
+      <c r="A52" s="33"/>
+      <c r="B52" s="29">
         <v>8000</v>
       </c>
       <c r="C52" s="23"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="29"/>
-      <c r="B53" s="32">
+      <c r="A53" s="33"/>
+      <c r="B53" s="29">
         <v>10000</v>
       </c>
       <c r="C53" s="23"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="29"/>
-      <c r="B54" s="32">
+      <c r="A54" s="33"/>
+      <c r="B54" s="29">
         <v>12700</v>
       </c>
       <c r="C54" s="23"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="30"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="34"/>
+      <c r="A55" s="34"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="31"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="28" t="s">
+      <c r="A56" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B56" s="31">
+      <c r="B56" s="28">
         <v>315</v>
       </c>
       <c r="C56" s="23"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="29"/>
-      <c r="B57" s="32">
+      <c r="A57" s="33"/>
+      <c r="B57" s="29">
         <v>400</v>
       </c>
       <c r="C57" s="23"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="29"/>
-      <c r="B58" s="32">
+      <c r="A58" s="33"/>
+      <c r="B58" s="29">
         <v>500</v>
       </c>
       <c r="C58" s="23"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="29"/>
-      <c r="B59" s="32">
+      <c r="A59" s="33"/>
+      <c r="B59" s="29">
         <v>630</v>
       </c>
       <c r="C59" s="23"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="29"/>
-      <c r="B60" s="32">
+      <c r="A60" s="33"/>
+      <c r="B60" s="29">
         <v>800</v>
       </c>
       <c r="C60" s="23"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="29"/>
-      <c r="B61" s="32">
+      <c r="A61" s="33"/>
+      <c r="B61" s="29">
         <v>1000</v>
       </c>
       <c r="C61" s="23"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="29"/>
-      <c r="B62" s="32">
+      <c r="A62" s="33"/>
+      <c r="B62" s="29">
         <v>1250</v>
       </c>
       <c r="C62" s="23"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="29"/>
-      <c r="B63" s="32">
+      <c r="A63" s="33"/>
+      <c r="B63" s="29">
         <v>1600</v>
       </c>
       <c r="C63" s="23"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="29"/>
-      <c r="B64" s="32">
+      <c r="A64" s="33"/>
+      <c r="B64" s="29">
         <v>2000</v>
       </c>
       <c r="C64" s="23"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="29"/>
-      <c r="B65" s="32">
+      <c r="A65" s="33"/>
+      <c r="B65" s="29">
         <v>2500</v>
       </c>
       <c r="C65" s="23"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="29"/>
-      <c r="B66" s="32">
+      <c r="A66" s="33"/>
+      <c r="B66" s="29">
         <v>3150</v>
       </c>
       <c r="C66" s="23"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="29"/>
-      <c r="B67" s="32">
+      <c r="A67" s="33"/>
+      <c r="B67" s="29">
         <v>4000</v>
       </c>
       <c r="C67" s="23"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="29"/>
-      <c r="B68" s="32">
+      <c r="A68" s="33"/>
+      <c r="B68" s="29">
         <v>5000</v>
       </c>
       <c r="C68" s="23"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="29"/>
-      <c r="B69" s="32">
+      <c r="A69" s="33"/>
+      <c r="B69" s="29">
         <v>6300</v>
       </c>
       <c r="C69" s="23"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="29"/>
-      <c r="B70" s="32">
+      <c r="A70" s="33"/>
+      <c r="B70" s="29">
         <v>8000</v>
       </c>
       <c r="C70" s="23"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="29"/>
-      <c r="B71" s="32">
+      <c r="A71" s="33"/>
+      <c r="B71" s="29">
         <v>10000</v>
       </c>
       <c r="C71" s="23"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="29"/>
-      <c r="B72" s="32">
+      <c r="A72" s="33"/>
+      <c r="B72" s="29">
         <v>12700</v>
       </c>
       <c r="C72" s="23"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="30"/>
-      <c r="B73" s="33"/>
-      <c r="C73" s="34"/>
+      <c r="A73" s="34"/>
+      <c r="B73" s="30"/>
+      <c r="C73" s="31"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="28" t="s">
+      <c r="A74" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B74" s="31">
+      <c r="B74" s="28">
         <v>315</v>
       </c>
       <c r="C74" s="23"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="29"/>
-      <c r="B75" s="32">
+      <c r="A75" s="33"/>
+      <c r="B75" s="29">
         <v>400</v>
       </c>
       <c r="C75" s="23"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="29"/>
-      <c r="B76" s="32">
+      <c r="A76" s="33"/>
+      <c r="B76" s="29">
         <v>500</v>
       </c>
       <c r="C76" s="23"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="29"/>
-      <c r="B77" s="32">
+      <c r="A77" s="33"/>
+      <c r="B77" s="29">
         <v>630</v>
       </c>
       <c r="C77" s="23"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="29"/>
-      <c r="B78" s="32">
+      <c r="A78" s="33"/>
+      <c r="B78" s="29">
         <v>800</v>
       </c>
       <c r="C78" s="23"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="29"/>
-      <c r="B79" s="32">
+      <c r="A79" s="33"/>
+      <c r="B79" s="29">
         <v>1000</v>
       </c>
       <c r="C79" s="23"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="29"/>
-      <c r="B80" s="32">
+      <c r="A80" s="33"/>
+      <c r="B80" s="29">
         <v>1250</v>
       </c>
       <c r="C80" s="23"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="29"/>
-      <c r="B81" s="32">
+      <c r="A81" s="33"/>
+      <c r="B81" s="29">
         <v>1600</v>
       </c>
       <c r="C81" s="23"/>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="29"/>
-      <c r="B82" s="32">
+      <c r="A82" s="33"/>
+      <c r="B82" s="29">
         <v>2000</v>
       </c>
       <c r="C82" s="23"/>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="29"/>
-      <c r="B83" s="32">
+      <c r="A83" s="33"/>
+      <c r="B83" s="29">
         <v>2500</v>
       </c>
       <c r="C83" s="23"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="29"/>
-      <c r="B84" s="32">
+      <c r="A84" s="33"/>
+      <c r="B84" s="29">
         <v>3150</v>
       </c>
       <c r="C84" s="23"/>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="29"/>
-      <c r="B85" s="32">
+      <c r="A85" s="33"/>
+      <c r="B85" s="29">
         <v>4000</v>
       </c>
       <c r="C85" s="23"/>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="29"/>
-      <c r="B86" s="32">
+      <c r="A86" s="33"/>
+      <c r="B86" s="29">
         <v>5000</v>
       </c>
       <c r="C86" s="23"/>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="29"/>
-      <c r="B87" s="32">
+      <c r="A87" s="33"/>
+      <c r="B87" s="29">
         <v>6300</v>
       </c>
       <c r="C87" s="23"/>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="29"/>
-      <c r="B88" s="32">
+      <c r="A88" s="33"/>
+      <c r="B88" s="29">
         <v>8000</v>
       </c>
       <c r="C88" s="23"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="29"/>
-      <c r="B89" s="32">
+      <c r="A89" s="33"/>
+      <c r="B89" s="29">
         <v>10000</v>
       </c>
       <c r="C89" s="23"/>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="29"/>
-      <c r="B90" s="32">
+      <c r="A90" s="33"/>
+      <c r="B90" s="29">
         <v>12700</v>
       </c>
       <c r="C90" s="23"/>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="30"/>
-      <c r="B91" s="33"/>
-      <c r="C91" s="34"/>
+      <c r="A91" s="34"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="31"/>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="28" t="s">
+      <c r="A92" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="B92" s="31">
+      <c r="B92" s="28">
         <v>315</v>
       </c>
       <c r="C92" s="23"/>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="29"/>
-      <c r="B93" s="32">
+      <c r="A93" s="33"/>
+      <c r="B93" s="29">
         <v>400</v>
       </c>
       <c r="C93" s="23"/>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="29"/>
-      <c r="B94" s="32">
+      <c r="A94" s="33"/>
+      <c r="B94" s="29">
         <v>500</v>
       </c>
       <c r="C94" s="23"/>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="29"/>
-      <c r="B95" s="32">
+      <c r="A95" s="33"/>
+      <c r="B95" s="29">
         <v>630</v>
       </c>
       <c r="C95" s="23"/>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="29"/>
-      <c r="B96" s="32">
+      <c r="A96" s="33"/>
+      <c r="B96" s="29">
         <v>800</v>
       </c>
       <c r="C96" s="23"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="29"/>
-      <c r="B97" s="32">
+      <c r="A97" s="33"/>
+      <c r="B97" s="29">
         <v>1000</v>
       </c>
       <c r="C97" s="23"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="29"/>
-      <c r="B98" s="32">
+      <c r="A98" s="33"/>
+      <c r="B98" s="29">
         <v>1250</v>
       </c>
       <c r="C98" s="23"/>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="29"/>
-      <c r="B99" s="32">
+      <c r="A99" s="33"/>
+      <c r="B99" s="29">
         <v>1600</v>
       </c>
       <c r="C99" s="23"/>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="29"/>
-      <c r="B100" s="32">
+      <c r="A100" s="33"/>
+      <c r="B100" s="29">
         <v>2000</v>
       </c>
       <c r="C100" s="23"/>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="29"/>
-      <c r="B101" s="32">
+      <c r="A101" s="33"/>
+      <c r="B101" s="29">
         <v>2500</v>
       </c>
       <c r="C101" s="23"/>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="29"/>
-      <c r="B102" s="32">
+      <c r="A102" s="33"/>
+      <c r="B102" s="29">
         <v>3150</v>
       </c>
       <c r="C102" s="23"/>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="29"/>
-      <c r="B103" s="32">
+      <c r="A103" s="33"/>
+      <c r="B103" s="29">
         <v>4000</v>
       </c>
       <c r="C103" s="23"/>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="29"/>
-      <c r="B104" s="32">
+      <c r="A104" s="33"/>
+      <c r="B104" s="29">
         <v>5000</v>
       </c>
       <c r="C104" s="23"/>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="29"/>
-      <c r="B105" s="32">
+      <c r="A105" s="33"/>
+      <c r="B105" s="29">
         <v>6300</v>
       </c>
       <c r="C105" s="23"/>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="29"/>
-      <c r="B106" s="32">
+      <c r="A106" s="33"/>
+      <c r="B106" s="29">
         <v>8000</v>
       </c>
       <c r="C106" s="23"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="29"/>
-      <c r="B107" s="32">
+      <c r="A107" s="33"/>
+      <c r="B107" s="29">
         <v>10000</v>
       </c>
       <c r="C107" s="23"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="29"/>
-      <c r="B108" s="32">
+      <c r="A108" s="33"/>
+      <c r="B108" s="29">
         <v>12700</v>
       </c>
       <c r="C108" s="23"/>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="30"/>
-      <c r="B109" s="33"/>
-      <c r="C109" s="34"/>
+      <c r="A109" s="34"/>
+      <c r="B109" s="30"/>
+      <c r="C109" s="31"/>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="28" t="s">
+      <c r="A110" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="B110" s="31">
+      <c r="B110" s="28">
         <v>315</v>
       </c>
       <c r="C110" s="23"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="29"/>
-      <c r="B111" s="32">
+      <c r="A111" s="33"/>
+      <c r="B111" s="29">
         <v>400</v>
       </c>
       <c r="C111" s="23"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="29"/>
-      <c r="B112" s="32">
+      <c r="A112" s="33"/>
+      <c r="B112" s="29">
         <v>500</v>
       </c>
       <c r="C112" s="23"/>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="29"/>
-      <c r="B113" s="32">
+      <c r="A113" s="33"/>
+      <c r="B113" s="29">
         <v>630</v>
       </c>
       <c r="C113" s="23"/>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="29"/>
-      <c r="B114" s="32">
+      <c r="A114" s="33"/>
+      <c r="B114" s="29">
         <v>800</v>
       </c>
       <c r="C114" s="23"/>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="29"/>
-      <c r="B115" s="32">
+      <c r="A115" s="33"/>
+      <c r="B115" s="29">
         <v>1000</v>
       </c>
       <c r="C115" s="23"/>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="29"/>
-      <c r="B116" s="32">
+      <c r="A116" s="33"/>
+      <c r="B116" s="29">
         <v>1250</v>
       </c>
       <c r="C116" s="23"/>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="29"/>
-      <c r="B117" s="32">
+      <c r="A117" s="33"/>
+      <c r="B117" s="29">
         <v>1600</v>
       </c>
       <c r="C117" s="23"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="29"/>
-      <c r="B118" s="32">
+      <c r="A118" s="33"/>
+      <c r="B118" s="29">
         <v>2000</v>
       </c>
       <c r="C118" s="23"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="29"/>
-      <c r="B119" s="32">
+      <c r="A119" s="33"/>
+      <c r="B119" s="29">
         <v>2500</v>
       </c>
       <c r="C119" s="23"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="29"/>
-      <c r="B120" s="32">
+      <c r="A120" s="33"/>
+      <c r="B120" s="29">
         <v>3150</v>
       </c>
       <c r="C120" s="23"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="29"/>
-      <c r="B121" s="32">
+      <c r="A121" s="33"/>
+      <c r="B121" s="29">
         <v>4000</v>
       </c>
       <c r="C121" s="23"/>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="29"/>
-      <c r="B122" s="32">
+      <c r="A122" s="33"/>
+      <c r="B122" s="29">
         <v>5000</v>
       </c>
       <c r="C122" s="23"/>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="29"/>
-      <c r="B123" s="32">
+      <c r="A123" s="33"/>
+      <c r="B123" s="29">
         <v>6300</v>
       </c>
       <c r="C123" s="23"/>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="29"/>
-      <c r="B124" s="32">
+      <c r="A124" s="33"/>
+      <c r="B124" s="29">
         <v>8000</v>
       </c>
       <c r="C124" s="23"/>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="29"/>
-      <c r="B125" s="32">
+      <c r="A125" s="33"/>
+      <c r="B125" s="29">
         <v>10000</v>
       </c>
       <c r="C125" s="23"/>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="29"/>
-      <c r="B126" s="32">
+      <c r="A126" s="33"/>
+      <c r="B126" s="29">
         <v>12700</v>
       </c>
       <c r="C126" s="23"/>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="30"/>
-      <c r="B127" s="33"/>
-      <c r="C127" s="34"/>
+      <c r="A127" s="34"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="31"/>
     </row>
     <row r="128" spans="1:3" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="28" t="s">
+      <c r="A128" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="B128" s="31">
+      <c r="B128" s="28">
         <v>315</v>
       </c>
       <c r="C128" s="23"/>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="29"/>
-      <c r="B129" s="32">
+      <c r="A129" s="33"/>
+      <c r="B129" s="29">
         <v>400</v>
       </c>
       <c r="C129" s="23"/>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="29"/>
-      <c r="B130" s="32">
+      <c r="A130" s="33"/>
+      <c r="B130" s="29">
         <v>500</v>
       </c>
       <c r="C130" s="23"/>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="29"/>
-      <c r="B131" s="32">
+      <c r="A131" s="33"/>
+      <c r="B131" s="29">
         <v>630</v>
       </c>
       <c r="C131" s="23"/>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="29"/>
-      <c r="B132" s="32">
+      <c r="A132" s="33"/>
+      <c r="B132" s="29">
         <v>800</v>
       </c>
       <c r="C132" s="23"/>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="29"/>
-      <c r="B133" s="32">
+      <c r="A133" s="33"/>
+      <c r="B133" s="29">
         <v>1000</v>
       </c>
       <c r="C133" s="23"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="29"/>
-      <c r="B134" s="32">
+      <c r="A134" s="33"/>
+      <c r="B134" s="29">
         <v>1250</v>
       </c>
       <c r="C134" s="23"/>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="29"/>
-      <c r="B135" s="32">
+      <c r="A135" s="33"/>
+      <c r="B135" s="29">
         <v>1600</v>
       </c>
       <c r="C135" s="23"/>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="29"/>
-      <c r="B136" s="32">
+      <c r="A136" s="33"/>
+      <c r="B136" s="29">
         <v>2000</v>
       </c>
       <c r="C136" s="23"/>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="29"/>
-      <c r="B137" s="32">
+      <c r="A137" s="33"/>
+      <c r="B137" s="29">
         <v>2500</v>
       </c>
       <c r="C137" s="23"/>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="29"/>
-      <c r="B138" s="32">
+      <c r="A138" s="33"/>
+      <c r="B138" s="29">
         <v>3150</v>
       </c>
       <c r="C138" s="23"/>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="29"/>
-      <c r="B139" s="32">
+      <c r="A139" s="33"/>
+      <c r="B139" s="29">
         <v>4000</v>
       </c>
       <c r="C139" s="23"/>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="29"/>
-      <c r="B140" s="32">
+      <c r="A140" s="33"/>
+      <c r="B140" s="29">
         <v>5000</v>
       </c>
       <c r="C140" s="23"/>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="29"/>
-      <c r="B141" s="32">
+      <c r="A141" s="33"/>
+      <c r="B141" s="29">
         <v>6300</v>
       </c>
       <c r="C141" s="23"/>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="29"/>
-      <c r="B142" s="32">
+      <c r="A142" s="33"/>
+      <c r="B142" s="29">
         <v>8000</v>
       </c>
       <c r="C142" s="23"/>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="29"/>
-      <c r="B143" s="32">
+      <c r="A143" s="33"/>
+      <c r="B143" s="29">
         <v>10000</v>
       </c>
       <c r="C143" s="23"/>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="29"/>
-      <c r="B144" s="32">
+      <c r="A144" s="33"/>
+      <c r="B144" s="29">
         <v>12700</v>
       </c>
       <c r="C144" s="23"/>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="30"/>
-      <c r="B145" s="33"/>
-      <c r="C145" s="34"/>
+      <c r="A145" s="34"/>
+      <c r="B145" s="30"/>
+      <c r="C145" s="31"/>
     </row>
     <row r="146" spans="1:3" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="28" t="s">
+      <c r="A146" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="B146" s="31">
+      <c r="B146" s="28">
         <v>315</v>
       </c>
       <c r="C146" s="23"/>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="29"/>
-      <c r="B147" s="32">
+      <c r="A147" s="33"/>
+      <c r="B147" s="29">
         <v>400</v>
       </c>
       <c r="C147" s="23"/>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="29"/>
-      <c r="B148" s="32">
+      <c r="A148" s="33"/>
+      <c r="B148" s="29">
         <v>500</v>
       </c>
       <c r="C148" s="23"/>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="29"/>
-      <c r="B149" s="32">
+      <c r="A149" s="33"/>
+      <c r="B149" s="29">
         <v>630</v>
       </c>
       <c r="C149" s="23"/>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="29"/>
-      <c r="B150" s="32">
+      <c r="A150" s="33"/>
+      <c r="B150" s="29">
         <v>800</v>
       </c>
       <c r="C150" s="23"/>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="29"/>
-      <c r="B151" s="32">
+      <c r="A151" s="33"/>
+      <c r="B151" s="29">
         <v>1000</v>
       </c>
       <c r="C151" s="23"/>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="29"/>
-      <c r="B152" s="32">
+      <c r="A152" s="33"/>
+      <c r="B152" s="29">
         <v>1250</v>
       </c>
       <c r="C152" s="23"/>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="29"/>
-      <c r="B153" s="32">
+      <c r="A153" s="33"/>
+      <c r="B153" s="29">
         <v>1600</v>
       </c>
       <c r="C153" s="23"/>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="29"/>
-      <c r="B154" s="32">
+      <c r="A154" s="33"/>
+      <c r="B154" s="29">
         <v>2000</v>
       </c>
       <c r="C154" s="23"/>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="29"/>
-      <c r="B155" s="32">
+      <c r="A155" s="33"/>
+      <c r="B155" s="29">
         <v>2500</v>
       </c>
       <c r="C155" s="23"/>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="29"/>
-      <c r="B156" s="32">
+      <c r="A156" s="33"/>
+      <c r="B156" s="29">
         <v>3150</v>
       </c>
       <c r="C156" s="23"/>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="29"/>
-      <c r="B157" s="32">
+      <c r="A157" s="33"/>
+      <c r="B157" s="29">
         <v>4000</v>
       </c>
       <c r="C157" s="23"/>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="29"/>
-      <c r="B158" s="32">
+      <c r="A158" s="33"/>
+      <c r="B158" s="29">
         <v>5000</v>
       </c>
       <c r="C158" s="23"/>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="29"/>
-      <c r="B159" s="32">
+      <c r="A159" s="33"/>
+      <c r="B159" s="29">
         <v>6300</v>
       </c>
       <c r="C159" s="23"/>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="29"/>
-      <c r="B160" s="32">
+      <c r="A160" s="33"/>
+      <c r="B160" s="29">
         <v>8000</v>
       </c>
       <c r="C160" s="23"/>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="29"/>
-      <c r="B161" s="32">
+      <c r="A161" s="33"/>
+      <c r="B161" s="29">
         <v>10000</v>
       </c>
       <c r="C161" s="23"/>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="29"/>
-      <c r="B162" s="32">
+      <c r="A162" s="33"/>
+      <c r="B162" s="29">
         <v>12700</v>
       </c>
       <c r="C162" s="23"/>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="30"/>
-      <c r="B163" s="33"/>
-      <c r="C163" s="34"/>
+      <c r="A163" s="34"/>
+      <c r="B163" s="30"/>
+      <c r="C163" s="31"/>
     </row>
     <row r="164" spans="1:3" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="28" t="s">
+      <c r="A164" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="B164" s="31">
+      <c r="B164" s="28">
         <v>315</v>
       </c>
       <c r="C164" s="23"/>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="29"/>
-      <c r="B165" s="32">
+      <c r="A165" s="33"/>
+      <c r="B165" s="29">
         <v>400</v>
       </c>
       <c r="C165" s="23"/>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" s="29"/>
-      <c r="B166" s="32">
+      <c r="A166" s="33"/>
+      <c r="B166" s="29">
         <v>500</v>
       </c>
       <c r="C166" s="23"/>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" s="29"/>
-      <c r="B167" s="32">
+      <c r="A167" s="33"/>
+      <c r="B167" s="29">
         <v>630</v>
       </c>
       <c r="C167" s="23"/>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" s="29"/>
-      <c r="B168" s="32">
+      <c r="A168" s="33"/>
+      <c r="B168" s="29">
         <v>800</v>
       </c>
       <c r="C168" s="23"/>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="29"/>
-      <c r="B169" s="32">
+      <c r="A169" s="33"/>
+      <c r="B169" s="29">
         <v>1000</v>
       </c>
       <c r="C169" s="23"/>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="29"/>
-      <c r="B170" s="32">
+      <c r="A170" s="33"/>
+      <c r="B170" s="29">
         <v>1250</v>
       </c>
       <c r="C170" s="23"/>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="29"/>
-      <c r="B171" s="32">
+      <c r="A171" s="33"/>
+      <c r="B171" s="29">
         <v>1600</v>
       </c>
       <c r="C171" s="23"/>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" s="29"/>
-      <c r="B172" s="32">
+      <c r="A172" s="33"/>
+      <c r="B172" s="29">
         <v>2000</v>
       </c>
       <c r="C172" s="23"/>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="29"/>
-      <c r="B173" s="32">
+      <c r="A173" s="33"/>
+      <c r="B173" s="29">
         <v>2500</v>
       </c>
       <c r="C173" s="23"/>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="29"/>
-      <c r="B174" s="32">
+      <c r="A174" s="33"/>
+      <c r="B174" s="29">
         <v>3150</v>
       </c>
       <c r="C174" s="23"/>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="29"/>
-      <c r="B175" s="32">
+      <c r="A175" s="33"/>
+      <c r="B175" s="29">
         <v>4000</v>
       </c>
       <c r="C175" s="23"/>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="29"/>
-      <c r="B176" s="32">
+      <c r="A176" s="33"/>
+      <c r="B176" s="29">
         <v>5000</v>
       </c>
       <c r="C176" s="23"/>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="29"/>
-      <c r="B177" s="32">
+      <c r="A177" s="33"/>
+      <c r="B177" s="29">
         <v>6300</v>
       </c>
       <c r="C177" s="23"/>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="29"/>
-      <c r="B178" s="32">
+      <c r="A178" s="33"/>
+      <c r="B178" s="29">
         <v>8000</v>
       </c>
       <c r="C178" s="23"/>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="29"/>
-      <c r="B179" s="32">
+      <c r="A179" s="33"/>
+      <c r="B179" s="29">
         <v>10000</v>
       </c>
       <c r="C179" s="23"/>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="29"/>
-      <c r="B180" s="32">
+      <c r="A180" s="33"/>
+      <c r="B180" s="29">
         <v>12700</v>
       </c>
       <c r="C180" s="23"/>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="30"/>
-      <c r="B181" s="33"/>
-      <c r="C181" s="34"/>
+      <c r="A181" s="34"/>
+      <c r="B181" s="30"/>
+      <c r="C181" s="31"/>
     </row>
     <row r="182" spans="1:3" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="28" t="s">
+      <c r="A182" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="B182" s="31">
+      <c r="B182" s="28">
         <v>315</v>
       </c>
       <c r="C182" s="23"/>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="29"/>
-      <c r="B183" s="32">
+      <c r="A183" s="33"/>
+      <c r="B183" s="29">
         <v>400</v>
       </c>
       <c r="C183" s="23"/>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="29"/>
-      <c r="B184" s="32">
+      <c r="A184" s="33"/>
+      <c r="B184" s="29">
         <v>500</v>
       </c>
       <c r="C184" s="23"/>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="29"/>
-      <c r="B185" s="32">
+      <c r="A185" s="33"/>
+      <c r="B185" s="29">
         <v>630</v>
       </c>
       <c r="C185" s="23"/>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="29"/>
-      <c r="B186" s="32">
+      <c r="A186" s="33"/>
+      <c r="B186" s="29">
         <v>800</v>
       </c>
       <c r="C186" s="23"/>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="29"/>
-      <c r="B187" s="32">
+      <c r="A187" s="33"/>
+      <c r="B187" s="29">
         <v>1000</v>
       </c>
       <c r="C187" s="23"/>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="29"/>
-      <c r="B188" s="32">
+      <c r="A188" s="33"/>
+      <c r="B188" s="29">
         <v>1250</v>
       </c>
       <c r="C188" s="23"/>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="29"/>
-      <c r="B189" s="32">
+      <c r="A189" s="33"/>
+      <c r="B189" s="29">
         <v>1600</v>
       </c>
       <c r="C189" s="23"/>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="29"/>
-      <c r="B190" s="32">
+      <c r="A190" s="33"/>
+      <c r="B190" s="29">
         <v>2000</v>
       </c>
       <c r="C190" s="23"/>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="29"/>
-      <c r="B191" s="32">
+      <c r="A191" s="33"/>
+      <c r="B191" s="29">
         <v>2500</v>
       </c>
       <c r="C191" s="23"/>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="29"/>
-      <c r="B192" s="32">
+      <c r="A192" s="33"/>
+      <c r="B192" s="29">
         <v>3150</v>
       </c>
       <c r="C192" s="23"/>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="29"/>
-      <c r="B193" s="32">
+      <c r="A193" s="33"/>
+      <c r="B193" s="29">
         <v>4000</v>
       </c>
       <c r="C193" s="23"/>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="29"/>
-      <c r="B194" s="32">
+      <c r="A194" s="33"/>
+      <c r="B194" s="29">
         <v>5000</v>
       </c>
       <c r="C194" s="23"/>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="29"/>
-      <c r="B195" s="32">
+      <c r="A195" s="33"/>
+      <c r="B195" s="29">
         <v>6300</v>
       </c>
       <c r="C195" s="23"/>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="29"/>
-      <c r="B196" s="32">
+      <c r="A196" s="33"/>
+      <c r="B196" s="29">
         <v>8000</v>
       </c>
       <c r="C196" s="23"/>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="29"/>
-      <c r="B197" s="32">
+      <c r="A197" s="33"/>
+      <c r="B197" s="29">
         <v>10000</v>
       </c>
       <c r="C197" s="23"/>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="29"/>
-      <c r="B198" s="32">
+      <c r="A198" s="33"/>
+      <c r="B198" s="29">
         <v>12700</v>
       </c>
       <c r="C198" s="23"/>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="30"/>
-      <c r="B199" s="33"/>
-      <c r="C199" s="34"/>
+      <c r="A199" s="34"/>
+      <c r="B199" s="30"/>
+      <c r="C199" s="31"/>
     </row>
     <row r="200" spans="1:3" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="28" t="s">
+      <c r="A200" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="B200" s="31">
+      <c r="B200" s="28">
         <v>315</v>
       </c>
       <c r="C200" s="23"/>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="29"/>
-      <c r="B201" s="32">
+      <c r="A201" s="33"/>
+      <c r="B201" s="29">
         <v>400</v>
       </c>
       <c r="C201" s="23"/>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="29"/>
-      <c r="B202" s="32">
+      <c r="A202" s="33"/>
+      <c r="B202" s="29">
         <v>500</v>
       </c>
       <c r="C202" s="23"/>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="29"/>
-      <c r="B203" s="32">
+      <c r="A203" s="33"/>
+      <c r="B203" s="29">
         <v>630</v>
       </c>
       <c r="C203" s="23"/>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="29"/>
-      <c r="B204" s="32">
+      <c r="A204" s="33"/>
+      <c r="B204" s="29">
         <v>800</v>
       </c>
       <c r="C204" s="23"/>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="29"/>
-      <c r="B205" s="32">
+      <c r="A205" s="33"/>
+      <c r="B205" s="29">
         <v>1000</v>
       </c>
       <c r="C205" s="23"/>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="29"/>
-      <c r="B206" s="32">
+      <c r="A206" s="33"/>
+      <c r="B206" s="29">
         <v>1250</v>
       </c>
       <c r="C206" s="23"/>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="29"/>
-      <c r="B207" s="32">
+      <c r="A207" s="33"/>
+      <c r="B207" s="29">
         <v>1600</v>
       </c>
       <c r="C207" s="23"/>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="29"/>
-      <c r="B208" s="32">
+      <c r="A208" s="33"/>
+      <c r="B208" s="29">
         <v>2000</v>
       </c>
       <c r="C208" s="23"/>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="29"/>
-      <c r="B209" s="32">
+      <c r="A209" s="33"/>
+      <c r="B209" s="29">
         <v>2500</v>
       </c>
       <c r="C209" s="23"/>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" s="29"/>
-      <c r="B210" s="32">
+      <c r="A210" s="33"/>
+      <c r="B210" s="29">
         <v>3150</v>
       </c>
       <c r="C210" s="23"/>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="29"/>
-      <c r="B211" s="32">
+      <c r="A211" s="33"/>
+      <c r="B211" s="29">
         <v>4000</v>
       </c>
       <c r="C211" s="23"/>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" s="29"/>
-      <c r="B212" s="32">
+      <c r="A212" s="33"/>
+      <c r="B212" s="29">
         <v>5000</v>
       </c>
       <c r="C212" s="23"/>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" s="29"/>
-      <c r="B213" s="32">
+      <c r="A213" s="33"/>
+      <c r="B213" s="29">
         <v>6300</v>
       </c>
       <c r="C213" s="23"/>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="29"/>
-      <c r="B214" s="32">
+      <c r="A214" s="33"/>
+      <c r="B214" s="29">
         <v>8000</v>
       </c>
       <c r="C214" s="23"/>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" s="29"/>
-      <c r="B215" s="32">
+      <c r="A215" s="33"/>
+      <c r="B215" s="29">
         <v>10000</v>
       </c>
       <c r="C215" s="23"/>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="29"/>
-      <c r="B216" s="32">
+      <c r="A216" s="33"/>
+      <c r="B216" s="29">
         <v>12700</v>
       </c>
       <c r="C216" s="23"/>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="30"/>
-      <c r="B217" s="33"/>
-      <c r="C217" s="34"/>
+      <c r="A217" s="34"/>
+      <c r="B217" s="30"/>
+      <c r="C217" s="31"/>
     </row>
     <row r="218" spans="1:3" s="2" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="28" t="s">
+      <c r="A218" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="B218" s="31">
+      <c r="B218" s="28">
         <v>315</v>
       </c>
       <c r="C218" s="23"/>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" s="29"/>
-      <c r="B219" s="32">
+      <c r="A219" s="33"/>
+      <c r="B219" s="29">
         <v>400</v>
       </c>
       <c r="C219" s="23"/>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="29"/>
-      <c r="B220" s="32">
+      <c r="A220" s="33"/>
+      <c r="B220" s="29">
         <v>500</v>
       </c>
       <c r="C220" s="23"/>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" s="29"/>
-      <c r="B221" s="32">
+      <c r="A221" s="33"/>
+      <c r="B221" s="29">
         <v>630</v>
       </c>
       <c r="C221" s="23"/>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="29"/>
-      <c r="B222" s="32">
+      <c r="A222" s="33"/>
+      <c r="B222" s="29">
         <v>800</v>
       </c>
       <c r="C222" s="23"/>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="29"/>
-      <c r="B223" s="32">
+      <c r="A223" s="33"/>
+      <c r="B223" s="29">
         <v>1000</v>
       </c>
       <c r="C223" s="23"/>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="29"/>
-      <c r="B224" s="32">
+      <c r="A224" s="33"/>
+      <c r="B224" s="29">
         <v>1250</v>
       </c>
       <c r="C224" s="23"/>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="29"/>
-      <c r="B225" s="32">
+      <c r="A225" s="33"/>
+      <c r="B225" s="29">
         <v>1600</v>
       </c>
       <c r="C225" s="23"/>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="29"/>
-      <c r="B226" s="32">
+      <c r="A226" s="33"/>
+      <c r="B226" s="29">
         <v>2000</v>
       </c>
       <c r="C226" s="23"/>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="29"/>
-      <c r="B227" s="32">
+      <c r="A227" s="33"/>
+      <c r="B227" s="29">
         <v>2500</v>
       </c>
       <c r="C227" s="23"/>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="29"/>
-      <c r="B228" s="32">
+      <c r="A228" s="33"/>
+      <c r="B228" s="29">
         <v>3150</v>
       </c>
       <c r="C228" s="23"/>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="29"/>
-      <c r="B229" s="32">
+      <c r="A229" s="33"/>
+      <c r="B229" s="29">
         <v>4000</v>
       </c>
       <c r="C229" s="23"/>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="29"/>
-      <c r="B230" s="32">
+      <c r="A230" s="33"/>
+      <c r="B230" s="29">
         <v>5000</v>
       </c>
       <c r="C230" s="23"/>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="29"/>
-      <c r="B231" s="32">
+      <c r="A231" s="33"/>
+      <c r="B231" s="29">
         <v>6300</v>
       </c>
       <c r="C231" s="23"/>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="29"/>
-      <c r="B232" s="32">
+      <c r="A232" s="33"/>
+      <c r="B232" s="29">
         <v>8000</v>
       </c>
       <c r="C232" s="23"/>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" s="29"/>
-      <c r="B233" s="32">
+      <c r="A233" s="33"/>
+      <c r="B233" s="29">
         <v>10000</v>
       </c>
       <c r="C233" s="23"/>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" s="29"/>
-      <c r="B234" s="32">
+      <c r="A234" s="33"/>
+      <c r="B234" s="29">
         <v>12700</v>
       </c>
       <c r="C234" s="23"/>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" s="30"/>
-      <c r="B235" s="33"/>
-      <c r="C235" s="34"/>
+      <c r="A235" s="34"/>
+      <c r="B235" s="30"/>
+      <c r="C235" s="31"/>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" s="28" t="s">
+      <c r="A236" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="B236" s="31">
+      <c r="B236" s="28">
         <v>315</v>
       </c>
       <c r="C236" s="23"/>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" s="29"/>
-      <c r="B237" s="32">
+      <c r="A237" s="33"/>
+      <c r="B237" s="29">
         <v>400</v>
       </c>
       <c r="C237" s="23"/>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" s="29"/>
-      <c r="B238" s="32">
+      <c r="A238" s="33"/>
+      <c r="B238" s="29">
         <v>500</v>
       </c>
       <c r="C238" s="23"/>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" s="29"/>
-      <c r="B239" s="32">
+      <c r="A239" s="33"/>
+      <c r="B239" s="29">
         <v>630</v>
       </c>
       <c r="C239" s="23"/>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" s="29"/>
-      <c r="B240" s="32">
+      <c r="A240" s="33"/>
+      <c r="B240" s="29">
         <v>800</v>
       </c>
       <c r="C240" s="23"/>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" s="29"/>
-      <c r="B241" s="32">
+      <c r="A241" s="33"/>
+      <c r="B241" s="29">
         <v>1000</v>
       </c>
       <c r="C241" s="23"/>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" s="29"/>
-      <c r="B242" s="32">
+      <c r="A242" s="33"/>
+      <c r="B242" s="29">
         <v>1250</v>
       </c>
       <c r="C242" s="23"/>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" s="29"/>
-      <c r="B243" s="32">
+      <c r="A243" s="33"/>
+      <c r="B243" s="29">
         <v>1600</v>
       </c>
       <c r="C243" s="23"/>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" s="29"/>
-      <c r="B244" s="32">
+      <c r="A244" s="33"/>
+      <c r="B244" s="29">
         <v>2000</v>
       </c>
       <c r="C244" s="23"/>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" s="29"/>
-      <c r="B245" s="32">
+      <c r="A245" s="33"/>
+      <c r="B245" s="29">
         <v>2500</v>
       </c>
       <c r="C245" s="23"/>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" s="29"/>
-      <c r="B246" s="32">
+      <c r="A246" s="33"/>
+      <c r="B246" s="29">
         <v>3150</v>
       </c>
       <c r="C246" s="23"/>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" s="29"/>
-      <c r="B247" s="32">
+      <c r="A247" s="33"/>
+      <c r="B247" s="29">
         <v>4000</v>
       </c>
       <c r="C247" s="23"/>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" s="29"/>
-      <c r="B248" s="32">
+      <c r="A248" s="33"/>
+      <c r="B248" s="29">
         <v>5000</v>
       </c>
       <c r="C248" s="23"/>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" s="29"/>
-      <c r="B249" s="32">
+      <c r="A249" s="33"/>
+      <c r="B249" s="29">
         <v>6300</v>
       </c>
       <c r="C249" s="23"/>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" s="29"/>
-      <c r="B250" s="32">
+      <c r="A250" s="33"/>
+      <c r="B250" s="29">
         <v>8000</v>
       </c>
       <c r="C250" s="23"/>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251" s="29"/>
-      <c r="B251" s="32">
+      <c r="A251" s="33"/>
+      <c r="B251" s="29">
         <v>10000</v>
       </c>
       <c r="C251" s="23"/>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" s="29"/>
-      <c r="B252" s="32">
+      <c r="A252" s="33"/>
+      <c r="B252" s="29">
         <v>12700</v>
       </c>
       <c r="C252" s="23"/>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" s="30"/>
-      <c r="B253" s="33"/>
-      <c r="C253" s="34"/>
+      <c r="A253" s="34"/>
+      <c r="B253" s="30"/>
+      <c r="C253" s="31"/>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" s="28" t="s">
+      <c r="A254" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="B254" s="31">
+      <c r="B254" s="28">
         <v>315</v>
       </c>
       <c r="C254" s="23"/>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" s="29"/>
-      <c r="B255" s="32">
+      <c r="A255" s="33"/>
+      <c r="B255" s="29">
         <v>400</v>
       </c>
       <c r="C255" s="23"/>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" s="29"/>
-      <c r="B256" s="32">
+      <c r="A256" s="33"/>
+      <c r="B256" s="29">
         <v>500</v>
       </c>
       <c r="C256" s="23"/>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" s="29"/>
-      <c r="B257" s="32">
+      <c r="A257" s="33"/>
+      <c r="B257" s="29">
         <v>630</v>
       </c>
       <c r="C257" s="23"/>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" s="29"/>
-      <c r="B258" s="32">
+      <c r="A258" s="33"/>
+      <c r="B258" s="29">
         <v>800</v>
       </c>
       <c r="C258" s="23"/>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" s="29"/>
-      <c r="B259" s="32">
+      <c r="A259" s="33"/>
+      <c r="B259" s="29">
         <v>1000</v>
       </c>
       <c r="C259" s="23"/>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" s="29"/>
-      <c r="B260" s="32">
+      <c r="A260" s="33"/>
+      <c r="B260" s="29">
         <v>1250</v>
       </c>
       <c r="C260" s="23"/>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" s="29"/>
-      <c r="B261" s="32">
+      <c r="A261" s="33"/>
+      <c r="B261" s="29">
         <v>1600</v>
       </c>
       <c r="C261" s="23"/>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" s="29"/>
-      <c r="B262" s="32">
+      <c r="A262" s="33"/>
+      <c r="B262" s="29">
         <v>2000</v>
       </c>
       <c r="C262" s="23"/>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" s="29"/>
-      <c r="B263" s="32">
+      <c r="A263" s="33"/>
+      <c r="B263" s="29">
         <v>2500</v>
       </c>
       <c r="C263" s="23"/>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" s="29"/>
-      <c r="B264" s="32">
+      <c r="A264" s="33"/>
+      <c r="B264" s="29">
         <v>3150</v>
       </c>
       <c r="C264" s="23"/>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" s="29"/>
-      <c r="B265" s="32">
+      <c r="A265" s="33"/>
+      <c r="B265" s="29">
         <v>4000</v>
       </c>
       <c r="C265" s="23"/>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" s="29"/>
-      <c r="B266" s="32">
+      <c r="A266" s="33"/>
+      <c r="B266" s="29">
         <v>5000</v>
       </c>
       <c r="C266" s="23"/>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" s="29"/>
-      <c r="B267" s="32">
+      <c r="A267" s="33"/>
+      <c r="B267" s="29">
         <v>6300</v>
       </c>
       <c r="C267" s="23"/>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" s="29"/>
-      <c r="B268" s="32">
+      <c r="A268" s="33"/>
+      <c r="B268" s="29">
         <v>8000</v>
       </c>
       <c r="C268" s="23"/>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" s="29"/>
-      <c r="B269" s="32">
+      <c r="A269" s="33"/>
+      <c r="B269" s="29">
         <v>10000</v>
       </c>
       <c r="C269" s="23"/>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270" s="29"/>
-      <c r="B270" s="32">
+      <c r="A270" s="33"/>
+      <c r="B270" s="29">
         <v>12700</v>
       </c>
       <c r="C270" s="23"/>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" s="30"/>
-      <c r="B271" s="33"/>
-      <c r="C271" s="34"/>
+      <c r="A271" s="34"/>
+      <c r="B271" s="30"/>
+      <c r="C271" s="31"/>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272" s="28" t="s">
+      <c r="A272" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="B272" s="31">
+      <c r="B272" s="28">
         <v>315</v>
       </c>
       <c r="C272" s="23"/>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273" s="29"/>
-      <c r="B273" s="32">
+      <c r="A273" s="33"/>
+      <c r="B273" s="29">
         <v>400</v>
       </c>
       <c r="C273" s="23"/>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" s="29"/>
-      <c r="B274" s="32">
+      <c r="A274" s="33"/>
+      <c r="B274" s="29">
         <v>500</v>
       </c>
       <c r="C274" s="23"/>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275" s="29"/>
-      <c r="B275" s="32">
+      <c r="A275" s="33"/>
+      <c r="B275" s="29">
         <v>630</v>
       </c>
       <c r="C275" s="23"/>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276" s="29"/>
-      <c r="B276" s="32">
+      <c r="A276" s="33"/>
+      <c r="B276" s="29">
         <v>800</v>
       </c>
       <c r="C276" s="23"/>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277" s="29"/>
-      <c r="B277" s="32">
+      <c r="A277" s="33"/>
+      <c r="B277" s="29">
         <v>1000</v>
       </c>
       <c r="C277" s="23"/>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A278" s="29"/>
-      <c r="B278" s="32">
+      <c r="A278" s="33"/>
+      <c r="B278" s="29">
         <v>1250</v>
       </c>
       <c r="C278" s="23"/>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279" s="29"/>
-      <c r="B279" s="32">
+      <c r="A279" s="33"/>
+      <c r="B279" s="29">
         <v>1600</v>
       </c>
       <c r="C279" s="23"/>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" s="29"/>
-      <c r="B280" s="32">
+      <c r="A280" s="33"/>
+      <c r="B280" s="29">
         <v>2000</v>
       </c>
       <c r="C280" s="23"/>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" s="29"/>
-      <c r="B281" s="32">
+      <c r="A281" s="33"/>
+      <c r="B281" s="29">
         <v>2500</v>
       </c>
       <c r="C281" s="23"/>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" s="29"/>
-      <c r="B282" s="32">
+      <c r="A282" s="33"/>
+      <c r="B282" s="29">
         <v>3150</v>
       </c>
       <c r="C282" s="23"/>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" s="29"/>
-      <c r="B283" s="32">
+      <c r="A283" s="33"/>
+      <c r="B283" s="29">
         <v>4000</v>
       </c>
       <c r="C283" s="23"/>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284" s="29"/>
-      <c r="B284" s="32">
+      <c r="A284" s="33"/>
+      <c r="B284" s="29">
         <v>5000</v>
       </c>
       <c r="C284" s="23"/>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285" s="29"/>
-      <c r="B285" s="32">
+      <c r="A285" s="33"/>
+      <c r="B285" s="29">
         <v>6300</v>
       </c>
       <c r="C285" s="23"/>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A286" s="29"/>
-      <c r="B286" s="32">
+      <c r="A286" s="33"/>
+      <c r="B286" s="29">
         <v>8000</v>
       </c>
       <c r="C286" s="23"/>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287" s="29"/>
-      <c r="B287" s="32">
+      <c r="A287" s="33"/>
+      <c r="B287" s="29">
         <v>10000</v>
       </c>
       <c r="C287" s="23"/>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288" s="29"/>
-      <c r="B288" s="32">
+      <c r="A288" s="33"/>
+      <c r="B288" s="29">
         <v>12700</v>
       </c>
       <c r="C288" s="23"/>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" s="30"/>
-      <c r="B289" s="33"/>
-      <c r="C289" s="34"/>
+      <c r="A289" s="34"/>
+      <c r="B289" s="30"/>
+      <c r="C289" s="31"/>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290" s="28" t="s">
+      <c r="A290" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="B290" s="31">
+      <c r="B290" s="28">
         <v>315</v>
       </c>
       <c r="C290" s="23"/>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291" s="29"/>
-      <c r="B291" s="32">
+      <c r="A291" s="33"/>
+      <c r="B291" s="29">
         <v>400</v>
       </c>
       <c r="C291" s="23"/>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A292" s="29"/>
-      <c r="B292" s="32">
+      <c r="A292" s="33"/>
+      <c r="B292" s="29">
         <v>500</v>
       </c>
       <c r="C292" s="23"/>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A293" s="29"/>
-      <c r="B293" s="32">
+      <c r="A293" s="33"/>
+      <c r="B293" s="29">
         <v>630</v>
       </c>
       <c r="C293" s="23"/>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294" s="29"/>
-      <c r="B294" s="32">
+      <c r="A294" s="33"/>
+      <c r="B294" s="29">
         <v>800</v>
       </c>
       <c r="C294" s="23"/>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A295" s="29"/>
-      <c r="B295" s="32">
+      <c r="A295" s="33"/>
+      <c r="B295" s="29">
         <v>1000</v>
       </c>
       <c r="C295" s="23"/>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296" s="29"/>
-      <c r="B296" s="32">
+      <c r="A296" s="33"/>
+      <c r="B296" s="29">
         <v>1250</v>
       </c>
       <c r="C296" s="23"/>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A297" s="29"/>
-      <c r="B297" s="32">
+      <c r="A297" s="33"/>
+      <c r="B297" s="29">
         <v>1600</v>
       </c>
       <c r="C297" s="23"/>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298" s="29"/>
-      <c r="B298" s="32">
+      <c r="A298" s="33"/>
+      <c r="B298" s="29">
         <v>2000</v>
       </c>
       <c r="C298" s="23"/>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A299" s="29"/>
-      <c r="B299" s="32">
+      <c r="A299" s="33"/>
+      <c r="B299" s="29">
         <v>2500</v>
       </c>
       <c r="C299" s="23"/>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A300" s="29"/>
-      <c r="B300" s="32">
+      <c r="A300" s="33"/>
+      <c r="B300" s="29">
         <v>3150</v>
       </c>
       <c r="C300" s="23"/>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A301" s="29"/>
-      <c r="B301" s="32">
+      <c r="A301" s="33"/>
+      <c r="B301" s="29">
         <v>4000</v>
       </c>
       <c r="C301" s="23"/>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A302" s="29"/>
-      <c r="B302" s="32">
+      <c r="A302" s="33"/>
+      <c r="B302" s="29">
         <v>5000</v>
       </c>
       <c r="C302" s="23"/>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A303" s="29"/>
-      <c r="B303" s="32">
+      <c r="A303" s="33"/>
+      <c r="B303" s="29">
         <v>6300</v>
       </c>
       <c r="C303" s="23"/>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A304" s="29"/>
-      <c r="B304" s="32">
+      <c r="A304" s="33"/>
+      <c r="B304" s="29">
         <v>8000</v>
       </c>
       <c r="C304" s="23"/>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" s="29"/>
-      <c r="B305" s="32">
+      <c r="A305" s="33"/>
+      <c r="B305" s="29">
         <v>10000</v>
       </c>
       <c r="C305" s="23"/>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A306" s="29"/>
-      <c r="B306" s="32">
+      <c r="A306" s="33"/>
+      <c r="B306" s="29">
         <v>12700</v>
       </c>
       <c r="C306" s="23"/>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A307" s="30"/>
-      <c r="B307" s="33"/>
-      <c r="C307" s="34"/>
+      <c r="A307" s="34"/>
+      <c r="B307" s="30"/>
+      <c r="C307" s="31"/>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308" s="28" t="s">
+      <c r="A308" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B308" s="31">
+      <c r="B308" s="28">
         <v>315</v>
       </c>
       <c r="C308" s="23"/>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" s="29"/>
-      <c r="B309" s="32">
+      <c r="A309" s="33"/>
+      <c r="B309" s="29">
         <v>400</v>
       </c>
       <c r="C309" s="23"/>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" s="29"/>
-      <c r="B310" s="32">
+      <c r="A310" s="33"/>
+      <c r="B310" s="29">
         <v>500</v>
       </c>
       <c r="C310" s="23"/>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311" s="29"/>
-      <c r="B311" s="32">
+      <c r="A311" s="33"/>
+      <c r="B311" s="29">
         <v>630</v>
       </c>
       <c r="C311" s="23"/>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312" s="29"/>
-      <c r="B312" s="32">
+      <c r="A312" s="33"/>
+      <c r="B312" s="29">
         <v>800</v>
       </c>
       <c r="C312" s="23"/>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313" s="29"/>
-      <c r="B313" s="32">
+      <c r="A313" s="33"/>
+      <c r="B313" s="29">
         <v>1000</v>
       </c>
       <c r="C313" s="23"/>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314" s="29"/>
-      <c r="B314" s="32">
+      <c r="A314" s="33"/>
+      <c r="B314" s="29">
         <v>1250</v>
       </c>
       <c r="C314" s="23"/>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A315" s="29"/>
-      <c r="B315" s="32">
+      <c r="A315" s="33"/>
+      <c r="B315" s="29">
         <v>1600</v>
       </c>
       <c r="C315" s="23"/>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316" s="29"/>
-      <c r="B316" s="32">
+      <c r="A316" s="33"/>
+      <c r="B316" s="29">
         <v>2000</v>
       </c>
       <c r="C316" s="23"/>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A317" s="29"/>
-      <c r="B317" s="32">
+      <c r="A317" s="33"/>
+      <c r="B317" s="29">
         <v>2500</v>
       </c>
       <c r="C317" s="23"/>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A318" s="29"/>
-      <c r="B318" s="32">
+      <c r="A318" s="33"/>
+      <c r="B318" s="29">
         <v>3150</v>
       </c>
       <c r="C318" s="23"/>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319" s="29"/>
-      <c r="B319" s="32">
+      <c r="A319" s="33"/>
+      <c r="B319" s="29">
         <v>4000</v>
       </c>
       <c r="C319" s="23"/>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A320" s="29"/>
-      <c r="B320" s="32">
+      <c r="A320" s="33"/>
+      <c r="B320" s="29">
         <v>5000</v>
       </c>
       <c r="C320" s="23"/>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A321" s="29"/>
-      <c r="B321" s="32">
+      <c r="A321" s="33"/>
+      <c r="B321" s="29">
         <v>6300</v>
       </c>
       <c r="C321" s="23"/>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A322" s="29"/>
-      <c r="B322" s="32">
+      <c r="A322" s="33"/>
+      <c r="B322" s="29">
         <v>8000</v>
       </c>
       <c r="C322" s="23"/>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A323" s="29"/>
-      <c r="B323" s="32">
+      <c r="A323" s="33"/>
+      <c r="B323" s="29">
         <v>10000</v>
       </c>
       <c r="C323" s="23"/>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A324" s="29"/>
-      <c r="B324" s="32">
+      <c r="A324" s="33"/>
+      <c r="B324" s="29">
         <v>12700</v>
       </c>
       <c r="C324" s="23"/>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A325" s="30"/>
-      <c r="B325" s="33"/>
-      <c r="C325" s="34"/>
+      <c r="A325" s="34"/>
+      <c r="B325" s="30"/>
+      <c r="C325" s="31"/>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A326" s="28" t="s">
+      <c r="A326" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="B326" s="31">
+      <c r="B326" s="28">
         <v>314.98</v>
       </c>
       <c r="C326" s="23"/>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A327" s="29"/>
-      <c r="B327" s="32">
+      <c r="A327" s="33"/>
+      <c r="B327" s="29">
         <v>396.85</v>
       </c>
       <c r="C327" s="23"/>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A328" s="29"/>
-      <c r="B328" s="32">
+      <c r="A328" s="33"/>
+      <c r="B328" s="29">
         <v>500</v>
       </c>
       <c r="C328" s="23"/>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A329" s="29"/>
-      <c r="B329" s="32">
+      <c r="A329" s="33"/>
+      <c r="B329" s="29">
         <v>629.96100000000001</v>
       </c>
       <c r="C329" s="23"/>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A330" s="29"/>
-      <c r="B330" s="32">
+      <c r="A330" s="33"/>
+      <c r="B330" s="29">
         <v>793.70100000000002</v>
       </c>
       <c r="C330" s="23"/>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A331" s="29"/>
-      <c r="B331" s="32">
+      <c r="A331" s="33"/>
+      <c r="B331" s="29">
         <v>1000</v>
       </c>
       <c r="C331" s="23"/>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A332" s="29"/>
-      <c r="B332" s="32">
+      <c r="A332" s="33"/>
+      <c r="B332" s="29">
         <v>1259.92</v>
       </c>
       <c r="C332" s="23"/>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A333" s="29"/>
-      <c r="B333" s="32">
+      <c r="A333" s="33"/>
+      <c r="B333" s="29">
         <v>1587.4</v>
       </c>
       <c r="C333" s="23"/>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A334" s="29"/>
-      <c r="B334" s="32">
+      <c r="A334" s="33"/>
+      <c r="B334" s="29">
         <v>2000</v>
       </c>
       <c r="C334" s="23"/>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A335" s="29"/>
-      <c r="B335" s="32">
+      <c r="A335" s="33"/>
+      <c r="B335" s="29">
         <v>2519.84</v>
       </c>
       <c r="C335" s="23"/>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A336" s="29"/>
-      <c r="B336" s="32">
+      <c r="A336" s="33"/>
+      <c r="B336" s="29">
         <v>3174.8</v>
       </c>
       <c r="C336" s="23"/>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A337" s="29"/>
-      <c r="B337" s="32">
+      <c r="A337" s="33"/>
+      <c r="B337" s="29">
         <v>4000</v>
       </c>
       <c r="C337" s="23"/>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A338" s="29"/>
-      <c r="B338" s="32">
+      <c r="A338" s="33"/>
+      <c r="B338" s="29">
         <v>5039.68</v>
       </c>
       <c r="C338" s="23"/>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A339" s="29"/>
-      <c r="B339" s="32">
+      <c r="A339" s="33"/>
+      <c r="B339" s="29">
         <v>6349.6</v>
       </c>
       <c r="C339" s="23"/>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A340" s="29"/>
-      <c r="B340" s="32">
+      <c r="A340" s="33"/>
+      <c r="B340" s="29">
         <v>8000</v>
       </c>
       <c r="C340" s="23"/>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A341" s="29"/>
-      <c r="B341" s="32">
+      <c r="A341" s="33"/>
+      <c r="B341" s="29">
         <v>10079.4</v>
       </c>
       <c r="C341" s="23"/>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A342" s="29"/>
-      <c r="B342" s="32">
+      <c r="A342" s="33"/>
+      <c r="B342" s="29">
         <v>12699.2</v>
       </c>
       <c r="C342" s="23"/>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A343" s="30"/>
-      <c r="B343" s="33"/>
-      <c r="C343" s="34"/>
+      <c r="A343" s="34"/>
+      <c r="B343" s="30"/>
+      <c r="C343" s="31"/>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A344" s="28" t="s">
+      <c r="A344" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="B344" s="31">
+      <c r="B344" s="28">
         <v>314.98</v>
       </c>
       <c r="C344" s="23"/>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A345" s="29"/>
-      <c r="B345" s="32">
+      <c r="A345" s="33"/>
+      <c r="B345" s="29">
         <v>396.85</v>
       </c>
       <c r="C345" s="23"/>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A346" s="29"/>
-      <c r="B346" s="32">
+      <c r="A346" s="33"/>
+      <c r="B346" s="29">
         <v>500</v>
       </c>
       <c r="C346" s="23"/>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A347" s="29"/>
-      <c r="B347" s="32">
+      <c r="A347" s="33"/>
+      <c r="B347" s="29">
         <v>629.96100000000001</v>
       </c>
       <c r="C347" s="23"/>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A348" s="29"/>
-      <c r="B348" s="32">
+      <c r="A348" s="33"/>
+      <c r="B348" s="29">
         <v>793.70100000000002</v>
       </c>
       <c r="C348" s="23"/>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A349" s="29"/>
-      <c r="B349" s="32">
+      <c r="A349" s="33"/>
+      <c r="B349" s="29">
         <v>1000</v>
       </c>
       <c r="C349" s="23"/>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A350" s="29"/>
-      <c r="B350" s="32">
+      <c r="A350" s="33"/>
+      <c r="B350" s="29">
         <v>1259.92</v>
       </c>
       <c r="C350" s="23"/>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351" s="29"/>
-      <c r="B351" s="32">
+      <c r="A351" s="33"/>
+      <c r="B351" s="29">
         <v>1587.4</v>
       </c>
       <c r="C351" s="23"/>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A352" s="29"/>
-      <c r="B352" s="32">
+      <c r="A352" s="33"/>
+      <c r="B352" s="29">
         <v>2000</v>
       </c>
       <c r="C352" s="23"/>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A353" s="29"/>
-      <c r="B353" s="32">
+      <c r="A353" s="33"/>
+      <c r="B353" s="29">
         <v>2519.84</v>
       </c>
       <c r="C353" s="23"/>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A354" s="29"/>
-      <c r="B354" s="32">
+      <c r="A354" s="33"/>
+      <c r="B354" s="29">
         <v>3174.8</v>
       </c>
       <c r="C354" s="23"/>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A355" s="29"/>
-      <c r="B355" s="32">
+      <c r="A355" s="33"/>
+      <c r="B355" s="29">
         <v>4000</v>
       </c>
       <c r="C355" s="23"/>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A356" s="29"/>
-      <c r="B356" s="32">
+      <c r="A356" s="33"/>
+      <c r="B356" s="29">
         <v>5039.68</v>
       </c>
       <c r="C356" s="23"/>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A357" s="29"/>
-      <c r="B357" s="32">
+      <c r="A357" s="33"/>
+      <c r="B357" s="29">
         <v>6349.6</v>
       </c>
       <c r="C357" s="23"/>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A358" s="29"/>
-      <c r="B358" s="32">
+      <c r="A358" s="33"/>
+      <c r="B358" s="29">
         <v>8000</v>
       </c>
       <c r="C358" s="23"/>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A359" s="29"/>
-      <c r="B359" s="32">
+      <c r="A359" s="33"/>
+      <c r="B359" s="29">
         <v>10079.4</v>
       </c>
       <c r="C359" s="23"/>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A360" s="29"/>
-      <c r="B360" s="32">
+      <c r="A360" s="33"/>
+      <c r="B360" s="29">
         <v>12699.2</v>
       </c>
       <c r="C360" s="23"/>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A361" s="30"/>
-      <c r="B361" s="33"/>
-      <c r="C361" s="34"/>
+      <c r="A361" s="34"/>
+      <c r="B361" s="30"/>
+      <c r="C361" s="31"/>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A362" s="28" t="s">
+      <c r="A362" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="B362" s="31">
+      <c r="B362" s="28">
         <v>314.98</v>
       </c>
       <c r="C362" s="23"/>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A363" s="29"/>
-      <c r="B363" s="32">
+      <c r="A363" s="33"/>
+      <c r="B363" s="29">
         <v>396.85</v>
       </c>
       <c r="C363" s="23"/>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A364" s="29"/>
-      <c r="B364" s="32">
+      <c r="A364" s="33"/>
+      <c r="B364" s="29">
         <v>500</v>
       </c>
       <c r="C364" s="23"/>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A365" s="29"/>
-      <c r="B365" s="32">
+      <c r="A365" s="33"/>
+      <c r="B365" s="29">
         <v>629.96100000000001</v>
       </c>
       <c r="C365" s="23"/>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A366" s="29"/>
-      <c r="B366" s="32">
+      <c r="A366" s="33"/>
+      <c r="B366" s="29">
         <v>793.70100000000002</v>
       </c>
       <c r="C366" s="23"/>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A367" s="29"/>
-      <c r="B367" s="32">
+      <c r="A367" s="33"/>
+      <c r="B367" s="29">
         <v>1000</v>
       </c>
       <c r="C367" s="23"/>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A368" s="29"/>
-      <c r="B368" s="32">
+      <c r="A368" s="33"/>
+      <c r="B368" s="29">
         <v>1259.92</v>
       </c>
       <c r="C368" s="23"/>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A369" s="29"/>
-      <c r="B369" s="32">
+      <c r="A369" s="33"/>
+      <c r="B369" s="29">
         <v>1587.4</v>
       </c>
       <c r="C369" s="23"/>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A370" s="29"/>
-      <c r="B370" s="32">
+      <c r="A370" s="33"/>
+      <c r="B370" s="29">
         <v>2000</v>
       </c>
       <c r="C370" s="23"/>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A371" s="29"/>
-      <c r="B371" s="32">
+      <c r="A371" s="33"/>
+      <c r="B371" s="29">
         <v>2519.84</v>
       </c>
       <c r="C371" s="23"/>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A372" s="29"/>
-      <c r="B372" s="32">
+      <c r="A372" s="33"/>
+      <c r="B372" s="29">
         <v>3174.8</v>
       </c>
       <c r="C372" s="23"/>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A373" s="29"/>
-      <c r="B373" s="32">
+      <c r="A373" s="33"/>
+      <c r="B373" s="29">
         <v>4000</v>
       </c>
       <c r="C373" s="23"/>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A374" s="29"/>
-      <c r="B374" s="32">
+      <c r="A374" s="33"/>
+      <c r="B374" s="29">
         <v>5039.68</v>
       </c>
       <c r="C374" s="23"/>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A375" s="29"/>
-      <c r="B375" s="32">
+      <c r="A375" s="33"/>
+      <c r="B375" s="29">
         <v>6349.6</v>
       </c>
       <c r="C375" s="23"/>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A376" s="29"/>
-      <c r="B376" s="32">
+      <c r="A376" s="33"/>
+      <c r="B376" s="29">
         <v>8000</v>
       </c>
       <c r="C376" s="23"/>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A377" s="29"/>
-      <c r="B377" s="32">
+      <c r="A377" s="33"/>
+      <c r="B377" s="29">
         <v>10079.4</v>
       </c>
       <c r="C377" s="23"/>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A378" s="29"/>
-      <c r="B378" s="32">
+      <c r="A378" s="33"/>
+      <c r="B378" s="29">
         <v>12699.2</v>
       </c>
       <c r="C378" s="23"/>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A379" s="30"/>
-      <c r="B379" s="33"/>
-      <c r="C379" s="34"/>
+      <c r="A379" s="34"/>
+      <c r="B379" s="30"/>
+      <c r="C379" s="31"/>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A380" s="28" t="s">
+      <c r="A380" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="B380" s="31">
+      <c r="B380" s="28">
         <v>314.98</v>
       </c>
       <c r="C380" s="23"/>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A381" s="29"/>
-      <c r="B381" s="32">
+      <c r="A381" s="33"/>
+      <c r="B381" s="29">
         <v>396.85</v>
       </c>
       <c r="C381" s="23"/>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A382" s="29"/>
-      <c r="B382" s="32">
+      <c r="A382" s="33"/>
+      <c r="B382" s="29">
         <v>500</v>
       </c>
       <c r="C382" s="23"/>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A383" s="29"/>
-      <c r="B383" s="32">
+      <c r="A383" s="33"/>
+      <c r="B383" s="29">
         <v>629.96100000000001</v>
       </c>
       <c r="C383" s="23"/>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A384" s="29"/>
-      <c r="B384" s="32">
+      <c r="A384" s="33"/>
+      <c r="B384" s="29">
         <v>793.70100000000002</v>
       </c>
       <c r="C384" s="23"/>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A385" s="29"/>
-      <c r="B385" s="32">
+      <c r="A385" s="33"/>
+      <c r="B385" s="29">
         <v>1000</v>
       </c>
       <c r="C385" s="23"/>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A386" s="29"/>
-      <c r="B386" s="32">
+      <c r="A386" s="33"/>
+      <c r="B386" s="29">
         <v>1259.92</v>
       </c>
       <c r="C386" s="23"/>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A387" s="29"/>
-      <c r="B387" s="32">
+      <c r="A387" s="33"/>
+      <c r="B387" s="29">
         <v>1587.4</v>
       </c>
       <c r="C387" s="23"/>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A388" s="29"/>
-      <c r="B388" s="32">
+      <c r="A388" s="33"/>
+      <c r="B388" s="29">
         <v>2000</v>
       </c>
       <c r="C388" s="23"/>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A389" s="29"/>
-      <c r="B389" s="32">
+      <c r="A389" s="33"/>
+      <c r="B389" s="29">
         <v>2519.84</v>
       </c>
       <c r="C389" s="23"/>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A390" s="29"/>
-      <c r="B390" s="32">
+      <c r="A390" s="33"/>
+      <c r="B390" s="29">
         <v>3174.8</v>
       </c>
       <c r="C390" s="23"/>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A391" s="29"/>
-      <c r="B391" s="32">
+      <c r="A391" s="33"/>
+      <c r="B391" s="29">
         <v>4000</v>
       </c>
       <c r="C391" s="23"/>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A392" s="29"/>
-      <c r="B392" s="32">
+      <c r="A392" s="33"/>
+      <c r="B392" s="29">
         <v>5039.68</v>
       </c>
       <c r="C392" s="23"/>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A393" s="29"/>
-      <c r="B393" s="32">
+      <c r="A393" s="33"/>
+      <c r="B393" s="29">
         <v>6349.6</v>
       </c>
       <c r="C393" s="23"/>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A394" s="29"/>
-      <c r="B394" s="32">
+      <c r="A394" s="33"/>
+      <c r="B394" s="29">
         <v>8000</v>
       </c>
       <c r="C394" s="23"/>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A395" s="29"/>
-      <c r="B395" s="32">
+      <c r="A395" s="33"/>
+      <c r="B395" s="29">
         <v>10079.4</v>
       </c>
       <c r="C395" s="23"/>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A396" s="29"/>
-      <c r="B396" s="32">
+      <c r="A396" s="33"/>
+      <c r="B396" s="29">
         <v>12699.2</v>
       </c>
       <c r="C396" s="23"/>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A397" s="30"/>
-      <c r="B397" s="33"/>
-      <c r="C397" s="34"/>
+      <c r="A397" s="34"/>
+      <c r="B397" s="30"/>
+      <c r="C397" s="31"/>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A398" s="28" t="s">
+      <c r="A398" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="B398" s="31">
+      <c r="B398" s="28">
         <v>315</v>
       </c>
       <c r="C398" s="23"/>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A399" s="29"/>
-      <c r="B399" s="32">
+      <c r="A399" s="33"/>
+      <c r="B399" s="29">
         <v>400</v>
       </c>
       <c r="C399" s="23"/>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A400" s="29"/>
-      <c r="B400" s="32">
+      <c r="A400" s="33"/>
+      <c r="B400" s="29">
         <v>500</v>
       </c>
       <c r="C400" s="23"/>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A401" s="29"/>
-      <c r="B401" s="32">
+      <c r="A401" s="33"/>
+      <c r="B401" s="29">
         <v>630</v>
       </c>
       <c r="C401" s="23"/>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A402" s="29"/>
-      <c r="B402" s="32">
+      <c r="A402" s="33"/>
+      <c r="B402" s="29">
         <v>800</v>
       </c>
       <c r="C402" s="23"/>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A403" s="29"/>
-      <c r="B403" s="32">
+      <c r="A403" s="33"/>
+      <c r="B403" s="29">
         <v>1000</v>
       </c>
       <c r="C403" s="23"/>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A404" s="29"/>
-      <c r="B404" s="32">
+      <c r="A404" s="33"/>
+      <c r="B404" s="29">
         <v>1250</v>
       </c>
       <c r="C404" s="23"/>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A405" s="29"/>
-      <c r="B405" s="32">
+      <c r="A405" s="33"/>
+      <c r="B405" s="29">
         <v>1600</v>
       </c>
       <c r="C405" s="23"/>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A406" s="29"/>
-      <c r="B406" s="32">
+      <c r="A406" s="33"/>
+      <c r="B406" s="29">
         <v>2000</v>
       </c>
       <c r="C406" s="23"/>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A407" s="29"/>
-      <c r="B407" s="32">
+      <c r="A407" s="33"/>
+      <c r="B407" s="29">
         <v>2500</v>
       </c>
       <c r="C407" s="23"/>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A408" s="29"/>
-      <c r="B408" s="32">
+      <c r="A408" s="33"/>
+      <c r="B408" s="29">
         <v>3150</v>
       </c>
       <c r="C408" s="23"/>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A409" s="29"/>
-      <c r="B409" s="32">
+      <c r="A409" s="33"/>
+      <c r="B409" s="29">
         <v>4000</v>
       </c>
       <c r="C409" s="23"/>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A410" s="29"/>
-      <c r="B410" s="32">
+      <c r="A410" s="33"/>
+      <c r="B410" s="29">
         <v>5000</v>
       </c>
       <c r="C410" s="23"/>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A411" s="29"/>
-      <c r="B411" s="32">
+      <c r="A411" s="33"/>
+      <c r="B411" s="29">
         <v>6300</v>
       </c>
       <c r="C411" s="23"/>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A412" s="29"/>
-      <c r="B412" s="32">
+      <c r="A412" s="33"/>
+      <c r="B412" s="29">
         <v>8000</v>
       </c>
       <c r="C412" s="23"/>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A413" s="29"/>
-      <c r="B413" s="32">
+      <c r="A413" s="33"/>
+      <c r="B413" s="29">
         <v>10000</v>
       </c>
       <c r="C413" s="23"/>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A414" s="29"/>
-      <c r="B414" s="32">
+      <c r="A414" s="33"/>
+      <c r="B414" s="29">
         <v>12700</v>
       </c>
       <c r="C414" s="23"/>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A415" s="30"/>
-      <c r="B415" s="33"/>
-      <c r="C415" s="34"/>
+      <c r="A415" s="34"/>
+      <c r="B415" s="30"/>
+      <c r="C415" s="31"/>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A416" s="28" t="s">
+      <c r="A416" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="B416" s="31">
+      <c r="B416" s="28">
         <v>315</v>
       </c>
       <c r="C416" s="23">
@@ -47112,8 +46998,8 @@
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A417" s="29"/>
-      <c r="B417" s="32">
+      <c r="A417" s="33"/>
+      <c r="B417" s="29">
         <v>400</v>
       </c>
       <c r="C417" s="23">
@@ -47121,8 +47007,8 @@
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A418" s="29"/>
-      <c r="B418" s="32">
+      <c r="A418" s="33"/>
+      <c r="B418" s="29">
         <v>500</v>
       </c>
       <c r="C418" s="23">
@@ -47130,8 +47016,8 @@
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A419" s="29"/>
-      <c r="B419" s="32">
+      <c r="A419" s="33"/>
+      <c r="B419" s="29">
         <v>630</v>
       </c>
       <c r="C419" s="23">
@@ -47139,8 +47025,8 @@
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A420" s="29"/>
-      <c r="B420" s="32">
+      <c r="A420" s="33"/>
+      <c r="B420" s="29">
         <v>800</v>
       </c>
       <c r="C420" s="23">
@@ -47148,8 +47034,8 @@
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A421" s="29"/>
-      <c r="B421" s="32">
+      <c r="A421" s="33"/>
+      <c r="B421" s="29">
         <v>1000</v>
       </c>
       <c r="C421" s="23">
@@ -47157,8 +47043,8 @@
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A422" s="29"/>
-      <c r="B422" s="32">
+      <c r="A422" s="33"/>
+      <c r="B422" s="29">
         <v>1250</v>
       </c>
       <c r="C422" s="23">
@@ -47166,8 +47052,8 @@
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A423" s="29"/>
-      <c r="B423" s="32">
+      <c r="A423" s="33"/>
+      <c r="B423" s="29">
         <v>1600</v>
       </c>
       <c r="C423" s="23">
@@ -47175,8 +47061,8 @@
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A424" s="29"/>
-      <c r="B424" s="32">
+      <c r="A424" s="33"/>
+      <c r="B424" s="29">
         <v>2000</v>
       </c>
       <c r="C424" s="23">
@@ -47184,8 +47070,8 @@
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A425" s="29"/>
-      <c r="B425" s="32">
+      <c r="A425" s="33"/>
+      <c r="B425" s="29">
         <v>2500</v>
       </c>
       <c r="C425" s="23">
@@ -47193,8 +47079,8 @@
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A426" s="29"/>
-      <c r="B426" s="32">
+      <c r="A426" s="33"/>
+      <c r="B426" s="29">
         <v>3150</v>
       </c>
       <c r="C426" s="23">
@@ -47202,8 +47088,8 @@
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A427" s="29"/>
-      <c r="B427" s="32">
+      <c r="A427" s="33"/>
+      <c r="B427" s="29">
         <v>4000</v>
       </c>
       <c r="C427" s="23">
@@ -47211,8 +47097,8 @@
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A428" s="29"/>
-      <c r="B428" s="32">
+      <c r="A428" s="33"/>
+      <c r="B428" s="29">
         <v>5000</v>
       </c>
       <c r="C428" s="23">
@@ -47220,8 +47106,8 @@
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A429" s="29"/>
-      <c r="B429" s="32">
+      <c r="A429" s="33"/>
+      <c r="B429" s="29">
         <v>6300</v>
       </c>
       <c r="C429" s="23">
@@ -47229,8 +47115,8 @@
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A430" s="29"/>
-      <c r="B430" s="32">
+      <c r="A430" s="33"/>
+      <c r="B430" s="29">
         <v>8000</v>
       </c>
       <c r="C430" s="23">
@@ -47238,8 +47124,8 @@
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A431" s="29"/>
-      <c r="B431" s="32">
+      <c r="A431" s="33"/>
+      <c r="B431" s="29">
         <v>10000</v>
       </c>
       <c r="C431" s="23">
@@ -47247,8 +47133,8 @@
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A432" s="29"/>
-      <c r="B432" s="32">
+      <c r="A432" s="33"/>
+      <c r="B432" s="29">
         <v>12700</v>
       </c>
       <c r="C432" s="23">
@@ -47256,750 +47142,768 @@
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A433" s="30"/>
-      <c r="B433" s="33"/>
-      <c r="C433" s="34"/>
+      <c r="A433" s="34"/>
+      <c r="B433" s="30"/>
+      <c r="C433" s="31"/>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A434" s="28" t="s">
+      <c r="A434" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="B434" s="31">
+      <c r="B434" s="28">
         <v>315</v>
       </c>
       <c r="C434" s="23"/>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A435" s="29"/>
-      <c r="B435" s="32">
+      <c r="A435" s="33"/>
+      <c r="B435" s="29">
         <v>400</v>
       </c>
       <c r="C435" s="23"/>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A436" s="29"/>
-      <c r="B436" s="32">
+      <c r="A436" s="33"/>
+      <c r="B436" s="29">
         <v>500</v>
       </c>
       <c r="C436" s="23"/>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A437" s="29"/>
-      <c r="B437" s="32">
+      <c r="A437" s="33"/>
+      <c r="B437" s="29">
         <v>630</v>
       </c>
       <c r="C437" s="23"/>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A438" s="29"/>
-      <c r="B438" s="32">
+      <c r="A438" s="33"/>
+      <c r="B438" s="29">
         <v>800</v>
       </c>
       <c r="C438" s="23"/>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A439" s="29"/>
-      <c r="B439" s="32">
+      <c r="A439" s="33"/>
+      <c r="B439" s="29">
         <v>1000</v>
       </c>
       <c r="C439" s="23"/>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A440" s="29"/>
-      <c r="B440" s="32">
+      <c r="A440" s="33"/>
+      <c r="B440" s="29">
         <v>1250</v>
       </c>
       <c r="C440" s="23"/>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A441" s="29"/>
-      <c r="B441" s="32">
+      <c r="A441" s="33"/>
+      <c r="B441" s="29">
         <v>1600</v>
       </c>
       <c r="C441" s="23"/>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A442" s="29"/>
-      <c r="B442" s="32">
+      <c r="A442" s="33"/>
+      <c r="B442" s="29">
         <v>2000</v>
       </c>
       <c r="C442" s="23"/>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A443" s="29"/>
-      <c r="B443" s="32">
+      <c r="A443" s="33"/>
+      <c r="B443" s="29">
         <v>2500</v>
       </c>
       <c r="C443" s="23"/>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A444" s="29"/>
-      <c r="B444" s="32">
+      <c r="A444" s="33"/>
+      <c r="B444" s="29">
         <v>3150</v>
       </c>
       <c r="C444" s="23"/>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A445" s="29"/>
-      <c r="B445" s="32">
+      <c r="A445" s="33"/>
+      <c r="B445" s="29">
         <v>4000</v>
       </c>
       <c r="C445" s="23"/>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A446" s="29"/>
-      <c r="B446" s="32">
+      <c r="A446" s="33"/>
+      <c r="B446" s="29">
         <v>5000</v>
       </c>
       <c r="C446" s="23"/>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A447" s="29"/>
-      <c r="B447" s="32">
+      <c r="A447" s="33"/>
+      <c r="B447" s="29">
         <v>6300</v>
       </c>
       <c r="C447" s="23"/>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A448" s="29"/>
-      <c r="B448" s="32">
+      <c r="A448" s="33"/>
+      <c r="B448" s="29">
         <v>8000</v>
       </c>
       <c r="C448" s="23"/>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A449" s="29"/>
-      <c r="B449" s="32">
+      <c r="A449" s="33"/>
+      <c r="B449" s="29">
         <v>10000</v>
       </c>
       <c r="C449" s="23"/>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A450" s="29"/>
-      <c r="B450" s="32">
+      <c r="A450" s="33"/>
+      <c r="B450" s="29">
         <v>12700</v>
       </c>
       <c r="C450" s="23"/>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A451" s="30"/>
-      <c r="B451" s="33"/>
-      <c r="C451" s="34"/>
+      <c r="A451" s="34"/>
+      <c r="B451" s="30"/>
+      <c r="C451" s="31"/>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A452" s="28" t="s">
+      <c r="A452" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="B452" s="31">
+      <c r="B452" s="28">
         <v>315</v>
       </c>
       <c r="C452" s="23"/>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A453" s="29"/>
-      <c r="B453" s="32">
+      <c r="A453" s="33"/>
+      <c r="B453" s="29">
         <v>400</v>
       </c>
       <c r="C453" s="23"/>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A454" s="29"/>
-      <c r="B454" s="32">
+      <c r="A454" s="33"/>
+      <c r="B454" s="29">
         <v>500</v>
       </c>
       <c r="C454" s="23"/>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A455" s="29"/>
-      <c r="B455" s="32">
+      <c r="A455" s="33"/>
+      <c r="B455" s="29">
         <v>630</v>
       </c>
       <c r="C455" s="23"/>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A456" s="29"/>
-      <c r="B456" s="32">
+      <c r="A456" s="33"/>
+      <c r="B456" s="29">
         <v>800</v>
       </c>
       <c r="C456" s="23"/>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A457" s="29"/>
-      <c r="B457" s="32">
+      <c r="A457" s="33"/>
+      <c r="B457" s="29">
         <v>1000</v>
       </c>
       <c r="C457" s="23"/>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A458" s="29"/>
-      <c r="B458" s="32">
+      <c r="A458" s="33"/>
+      <c r="B458" s="29">
         <v>1250</v>
       </c>
       <c r="C458" s="23"/>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A459" s="29"/>
-      <c r="B459" s="32">
+      <c r="A459" s="33"/>
+      <c r="B459" s="29">
         <v>1600</v>
       </c>
       <c r="C459" s="23"/>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A460" s="29"/>
-      <c r="B460" s="32">
+      <c r="A460" s="33"/>
+      <c r="B460" s="29">
         <v>2000</v>
       </c>
       <c r="C460" s="23"/>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A461" s="29"/>
-      <c r="B461" s="32">
+      <c r="A461" s="33"/>
+      <c r="B461" s="29">
         <v>2500</v>
       </c>
       <c r="C461" s="23"/>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A462" s="29"/>
-      <c r="B462" s="32">
+      <c r="A462" s="33"/>
+      <c r="B462" s="29">
         <v>3150</v>
       </c>
       <c r="C462" s="23"/>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A463" s="29"/>
-      <c r="B463" s="32">
+      <c r="A463" s="33"/>
+      <c r="B463" s="29">
         <v>4000</v>
       </c>
       <c r="C463" s="23"/>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A464" s="29"/>
-      <c r="B464" s="32">
+      <c r="A464" s="33"/>
+      <c r="B464" s="29">
         <v>5000</v>
       </c>
       <c r="C464" s="23"/>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A465" s="29"/>
-      <c r="B465" s="32">
+      <c r="A465" s="33"/>
+      <c r="B465" s="29">
         <v>6300</v>
       </c>
       <c r="C465" s="23"/>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A466" s="29"/>
-      <c r="B466" s="32">
+      <c r="A466" s="33"/>
+      <c r="B466" s="29">
         <v>8000</v>
       </c>
       <c r="C466" s="23"/>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A467" s="29"/>
-      <c r="B467" s="32">
+      <c r="A467" s="33"/>
+      <c r="B467" s="29">
         <v>10000</v>
       </c>
       <c r="C467" s="23"/>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A468" s="29"/>
-      <c r="B468" s="32">
+      <c r="A468" s="33"/>
+      <c r="B468" s="29">
         <v>12700</v>
       </c>
       <c r="C468" s="23"/>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A469" s="30"/>
-      <c r="B469" s="33"/>
-      <c r="C469" s="34"/>
+      <c r="A469" s="34"/>
+      <c r="B469" s="30"/>
+      <c r="C469" s="31"/>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B470" s="31"/>
+      <c r="B470" s="28"/>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B471" s="32"/>
+      <c r="B471" s="29"/>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B472" s="32"/>
+      <c r="B472" s="29"/>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B473" s="32"/>
+      <c r="B473" s="29"/>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B474" s="32"/>
+      <c r="B474" s="29"/>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B475" s="32"/>
+      <c r="B475" s="29"/>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B476" s="32"/>
+      <c r="B476" s="29"/>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B477" s="32"/>
+      <c r="B477" s="29"/>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B478" s="32"/>
+      <c r="B478" s="29"/>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B479" s="32"/>
+      <c r="B479" s="29"/>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B480" s="32"/>
+      <c r="B480" s="29"/>
     </row>
     <row r="481" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B481" s="32"/>
+      <c r="B481" s="29"/>
     </row>
     <row r="482" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B482" s="32"/>
+      <c r="B482" s="29"/>
     </row>
     <row r="483" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B483" s="32"/>
+      <c r="B483" s="29"/>
     </row>
     <row r="484" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B484" s="32"/>
+      <c r="B484" s="29"/>
     </row>
     <row r="485" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B485" s="32"/>
+      <c r="B485" s="29"/>
     </row>
     <row r="486" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B486" s="32"/>
+      <c r="B486" s="29"/>
     </row>
     <row r="487" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B487" s="33"/>
+      <c r="B487" s="30"/>
     </row>
     <row r="488" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B488" s="31"/>
+      <c r="B488" s="28"/>
     </row>
     <row r="489" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B489" s="32"/>
+      <c r="B489" s="29"/>
     </row>
     <row r="490" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B490" s="32"/>
+      <c r="B490" s="29"/>
     </row>
     <row r="491" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B491" s="32"/>
+      <c r="B491" s="29"/>
     </row>
     <row r="492" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B492" s="32"/>
+      <c r="B492" s="29"/>
     </row>
     <row r="493" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B493" s="32"/>
+      <c r="B493" s="29"/>
     </row>
     <row r="494" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B494" s="32"/>
+      <c r="B494" s="29"/>
     </row>
     <row r="495" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B495" s="32"/>
+      <c r="B495" s="29"/>
     </row>
     <row r="496" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B496" s="32"/>
+      <c r="B496" s="29"/>
     </row>
     <row r="497" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B497" s="32"/>
+      <c r="B497" s="29"/>
     </row>
     <row r="498" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B498" s="32"/>
+      <c r="B498" s="29"/>
     </row>
     <row r="499" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B499" s="32"/>
+      <c r="B499" s="29"/>
     </row>
     <row r="500" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B500" s="32"/>
+      <c r="B500" s="29"/>
     </row>
     <row r="501" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B501" s="32"/>
+      <c r="B501" s="29"/>
     </row>
     <row r="502" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B502" s="32"/>
+      <c r="B502" s="29"/>
     </row>
     <row r="503" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B503" s="32"/>
+      <c r="B503" s="29"/>
     </row>
     <row r="504" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B504" s="32"/>
+      <c r="B504" s="29"/>
     </row>
     <row r="505" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B505" s="33"/>
+      <c r="B505" s="30"/>
     </row>
     <row r="506" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B506" s="31"/>
+      <c r="B506" s="28"/>
     </row>
     <row r="507" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B507" s="32"/>
+      <c r="B507" s="29"/>
     </row>
     <row r="508" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B508" s="32"/>
+      <c r="B508" s="29"/>
     </row>
     <row r="509" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B509" s="32"/>
+      <c r="B509" s="29"/>
     </row>
     <row r="510" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B510" s="32"/>
+      <c r="B510" s="29"/>
     </row>
     <row r="511" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B511" s="32"/>
+      <c r="B511" s="29"/>
     </row>
     <row r="512" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B512" s="32"/>
+      <c r="B512" s="29"/>
     </row>
     <row r="513" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B513" s="32"/>
+      <c r="B513" s="29"/>
     </row>
     <row r="514" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B514" s="32"/>
+      <c r="B514" s="29"/>
     </row>
     <row r="515" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B515" s="32"/>
+      <c r="B515" s="29"/>
     </row>
     <row r="516" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B516" s="32"/>
+      <c r="B516" s="29"/>
     </row>
     <row r="517" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B517" s="32"/>
+      <c r="B517" s="29"/>
     </row>
     <row r="518" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B518" s="32"/>
+      <c r="B518" s="29"/>
     </row>
     <row r="519" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B519" s="32"/>
+      <c r="B519" s="29"/>
     </row>
     <row r="520" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B520" s="32"/>
+      <c r="B520" s="29"/>
     </row>
     <row r="521" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B521" s="32"/>
+      <c r="B521" s="29"/>
     </row>
     <row r="522" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B522" s="32"/>
+      <c r="B522" s="29"/>
     </row>
     <row r="523" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B523" s="33"/>
+      <c r="B523" s="30"/>
     </row>
     <row r="524" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B524" s="31"/>
+      <c r="B524" s="28"/>
     </row>
     <row r="525" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B525" s="32"/>
+      <c r="B525" s="29"/>
     </row>
     <row r="526" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B526" s="32"/>
+      <c r="B526" s="29"/>
     </row>
     <row r="527" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B527" s="32"/>
+      <c r="B527" s="29"/>
     </row>
     <row r="528" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B528" s="32"/>
+      <c r="B528" s="29"/>
     </row>
     <row r="529" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B529" s="32"/>
+      <c r="B529" s="29"/>
     </row>
     <row r="530" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B530" s="32"/>
+      <c r="B530" s="29"/>
     </row>
     <row r="531" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B531" s="32"/>
+      <c r="B531" s="29"/>
     </row>
     <row r="532" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B532" s="32"/>
+      <c r="B532" s="29"/>
     </row>
     <row r="533" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B533" s="32"/>
+      <c r="B533" s="29"/>
     </row>
     <row r="534" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B534" s="32"/>
+      <c r="B534" s="29"/>
     </row>
     <row r="535" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B535" s="32"/>
+      <c r="B535" s="29"/>
     </row>
     <row r="536" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B536" s="32"/>
+      <c r="B536" s="29"/>
     </row>
     <row r="537" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B537" s="32"/>
+      <c r="B537" s="29"/>
     </row>
     <row r="538" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B538" s="32"/>
+      <c r="B538" s="29"/>
     </row>
     <row r="539" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B539" s="32"/>
+      <c r="B539" s="29"/>
     </row>
     <row r="540" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B540" s="32"/>
+      <c r="B540" s="29"/>
     </row>
     <row r="541" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B541" s="33"/>
+      <c r="B541" s="30"/>
     </row>
     <row r="542" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B542" s="31"/>
+      <c r="B542" s="28"/>
     </row>
     <row r="543" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B543" s="32"/>
+      <c r="B543" s="29"/>
     </row>
     <row r="544" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B544" s="32"/>
+      <c r="B544" s="29"/>
     </row>
     <row r="545" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B545" s="32"/>
+      <c r="B545" s="29"/>
     </row>
     <row r="546" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B546" s="32"/>
+      <c r="B546" s="29"/>
     </row>
     <row r="547" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B547" s="32"/>
+      <c r="B547" s="29"/>
     </row>
     <row r="548" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B548" s="32"/>
+      <c r="B548" s="29"/>
     </row>
     <row r="549" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B549" s="32"/>
+      <c r="B549" s="29"/>
     </row>
     <row r="550" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B550" s="32"/>
+      <c r="B550" s="29"/>
     </row>
     <row r="551" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B551" s="32"/>
+      <c r="B551" s="29"/>
     </row>
     <row r="552" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B552" s="32"/>
+      <c r="B552" s="29"/>
     </row>
     <row r="553" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B553" s="32"/>
+      <c r="B553" s="29"/>
     </row>
     <row r="554" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B554" s="32"/>
+      <c r="B554" s="29"/>
     </row>
     <row r="555" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B555" s="32"/>
+      <c r="B555" s="29"/>
     </row>
     <row r="556" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B556" s="32"/>
+      <c r="B556" s="29"/>
     </row>
     <row r="557" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B557" s="32"/>
+      <c r="B557" s="29"/>
     </row>
     <row r="558" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B558" s="32"/>
+      <c r="B558" s="29"/>
     </row>
     <row r="559" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B559" s="33"/>
+      <c r="B559" s="30"/>
     </row>
     <row r="560" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B560" s="31"/>
+      <c r="B560" s="28"/>
     </row>
     <row r="561" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B561" s="32"/>
+      <c r="B561" s="29"/>
     </row>
     <row r="562" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B562" s="32"/>
+      <c r="B562" s="29"/>
     </row>
     <row r="563" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B563" s="32"/>
+      <c r="B563" s="29"/>
     </row>
     <row r="564" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B564" s="32"/>
+      <c r="B564" s="29"/>
     </row>
     <row r="565" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B565" s="32"/>
+      <c r="B565" s="29"/>
     </row>
     <row r="566" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B566" s="32"/>
+      <c r="B566" s="29"/>
     </row>
     <row r="567" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B567" s="32"/>
+      <c r="B567" s="29"/>
     </row>
     <row r="568" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B568" s="32"/>
+      <c r="B568" s="29"/>
     </row>
     <row r="569" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B569" s="32"/>
+      <c r="B569" s="29"/>
     </row>
     <row r="570" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B570" s="32"/>
+      <c r="B570" s="29"/>
     </row>
     <row r="571" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B571" s="32"/>
+      <c r="B571" s="29"/>
     </row>
     <row r="572" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B572" s="32"/>
+      <c r="B572" s="29"/>
     </row>
     <row r="573" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B573" s="32"/>
+      <c r="B573" s="29"/>
     </row>
     <row r="574" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B574" s="32"/>
+      <c r="B574" s="29"/>
     </row>
     <row r="575" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B575" s="32"/>
+      <c r="B575" s="29"/>
     </row>
     <row r="576" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B576" s="32"/>
+      <c r="B576" s="29"/>
     </row>
     <row r="577" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B577" s="33"/>
+      <c r="B577" s="30"/>
     </row>
     <row r="578" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B578" s="31"/>
+      <c r="B578" s="28"/>
     </row>
     <row r="579" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B579" s="32"/>
+      <c r="B579" s="29"/>
     </row>
     <row r="580" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B580" s="32"/>
+      <c r="B580" s="29"/>
     </row>
     <row r="581" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B581" s="32"/>
+      <c r="B581" s="29"/>
     </row>
     <row r="582" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B582" s="32"/>
+      <c r="B582" s="29"/>
     </row>
     <row r="583" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B583" s="32"/>
+      <c r="B583" s="29"/>
     </row>
     <row r="584" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B584" s="32"/>
+      <c r="B584" s="29"/>
     </row>
     <row r="585" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B585" s="32"/>
+      <c r="B585" s="29"/>
     </row>
     <row r="586" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B586" s="32"/>
+      <c r="B586" s="29"/>
     </row>
     <row r="587" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B587" s="32"/>
+      <c r="B587" s="29"/>
     </row>
     <row r="588" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B588" s="32"/>
+      <c r="B588" s="29"/>
     </row>
     <row r="589" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B589" s="32"/>
+      <c r="B589" s="29"/>
     </row>
     <row r="590" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B590" s="32"/>
+      <c r="B590" s="29"/>
     </row>
     <row r="591" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B591" s="32"/>
+      <c r="B591" s="29"/>
     </row>
     <row r="592" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B592" s="32"/>
+      <c r="B592" s="29"/>
     </row>
     <row r="593" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B593" s="32"/>
+      <c r="B593" s="29"/>
     </row>
     <row r="594" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B594" s="32"/>
+      <c r="B594" s="29"/>
     </row>
     <row r="595" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B595" s="33"/>
+      <c r="B595" s="30"/>
     </row>
     <row r="596" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B596" s="31"/>
+      <c r="B596" s="28"/>
     </row>
     <row r="597" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B597" s="32"/>
+      <c r="B597" s="29"/>
     </row>
     <row r="598" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B598" s="32"/>
+      <c r="B598" s="29"/>
     </row>
     <row r="599" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B599" s="32"/>
+      <c r="B599" s="29"/>
     </row>
     <row r="600" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B600" s="32"/>
+      <c r="B600" s="29"/>
     </row>
     <row r="601" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B601" s="32"/>
+      <c r="B601" s="29"/>
     </row>
     <row r="602" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B602" s="32"/>
+      <c r="B602" s="29"/>
     </row>
     <row r="603" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B603" s="32"/>
+      <c r="B603" s="29"/>
     </row>
     <row r="604" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B604" s="32"/>
+      <c r="B604" s="29"/>
     </row>
     <row r="605" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B605" s="32"/>
+      <c r="B605" s="29"/>
     </row>
     <row r="606" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B606" s="32"/>
+      <c r="B606" s="29"/>
     </row>
     <row r="607" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B607" s="32"/>
+      <c r="B607" s="29"/>
     </row>
     <row r="608" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B608" s="32"/>
+      <c r="B608" s="29"/>
     </row>
     <row r="609" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B609" s="32"/>
+      <c r="B609" s="29"/>
     </row>
     <row r="610" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B610" s="32"/>
+      <c r="B610" s="29"/>
     </row>
     <row r="611" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B611" s="32"/>
+      <c r="B611" s="29"/>
     </row>
     <row r="612" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B612" s="32"/>
+      <c r="B612" s="29"/>
     </row>
     <row r="613" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B613" s="33"/>
+      <c r="B613" s="30"/>
     </row>
     <row r="614" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B614" s="31"/>
+      <c r="B614" s="28"/>
     </row>
     <row r="615" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B615" s="32"/>
+      <c r="B615" s="29"/>
     </row>
     <row r="616" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B616" s="32"/>
+      <c r="B616" s="29"/>
     </row>
     <row r="617" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B617" s="32"/>
+      <c r="B617" s="29"/>
     </row>
     <row r="618" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B618" s="32"/>
+      <c r="B618" s="29"/>
     </row>
     <row r="619" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B619" s="32"/>
+      <c r="B619" s="29"/>
     </row>
     <row r="620" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B620" s="32"/>
+      <c r="B620" s="29"/>
     </row>
     <row r="621" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B621" s="32"/>
+      <c r="B621" s="29"/>
     </row>
     <row r="622" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B622" s="32"/>
+      <c r="B622" s="29"/>
     </row>
     <row r="623" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B623" s="32"/>
+      <c r="B623" s="29"/>
     </row>
     <row r="624" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B624" s="32"/>
+      <c r="B624" s="29"/>
     </row>
     <row r="625" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B625" s="32"/>
+      <c r="B625" s="29"/>
     </row>
     <row r="626" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B626" s="32"/>
+      <c r="B626" s="29"/>
     </row>
     <row r="627" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B627" s="32"/>
+      <c r="B627" s="29"/>
     </row>
     <row r="628" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B628" s="32"/>
+      <c r="B628" s="29"/>
     </row>
     <row r="629" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B629" s="32"/>
+      <c r="B629" s="29"/>
     </row>
     <row r="630" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B630" s="32"/>
+      <c r="B630" s="29"/>
     </row>
     <row r="631" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B631" s="33"/>
+      <c r="B631" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A92:A109"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A20:A37"/>
+    <mergeCell ref="A38:A55"/>
+    <mergeCell ref="A56:A73"/>
+    <mergeCell ref="A74:A91"/>
+    <mergeCell ref="A308:A325"/>
+    <mergeCell ref="A110:A127"/>
+    <mergeCell ref="A128:A145"/>
+    <mergeCell ref="A146:A163"/>
+    <mergeCell ref="A164:A181"/>
+    <mergeCell ref="A182:A199"/>
+    <mergeCell ref="A200:A217"/>
+    <mergeCell ref="A218:A235"/>
+    <mergeCell ref="A236:A253"/>
+    <mergeCell ref="A254:A271"/>
+    <mergeCell ref="A272:A289"/>
+    <mergeCell ref="A290:A307"/>
     <mergeCell ref="A434:A451"/>
     <mergeCell ref="A452:A469"/>
     <mergeCell ref="A326:A343"/>
@@ -48008,24 +47912,6 @@
     <mergeCell ref="A380:A397"/>
     <mergeCell ref="A398:A415"/>
     <mergeCell ref="A416:A433"/>
-    <mergeCell ref="A218:A235"/>
-    <mergeCell ref="A236:A253"/>
-    <mergeCell ref="A254:A271"/>
-    <mergeCell ref="A272:A289"/>
-    <mergeCell ref="A290:A307"/>
-    <mergeCell ref="A308:A325"/>
-    <mergeCell ref="A110:A127"/>
-    <mergeCell ref="A128:A145"/>
-    <mergeCell ref="A146:A163"/>
-    <mergeCell ref="A164:A181"/>
-    <mergeCell ref="A182:A199"/>
-    <mergeCell ref="A200:A217"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A20:A37"/>
-    <mergeCell ref="A38:A55"/>
-    <mergeCell ref="A56:A73"/>
-    <mergeCell ref="A74:A91"/>
-    <mergeCell ref="A92:A109"/>
   </mergeCells>
   <conditionalFormatting sqref="B632:B1048576 C1 C19 C37:C469">
     <cfRule type="colorScale" priority="1">
@@ -48037,7 +47923,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19 C37 C39:C55 C57:C73 C75:C91 C93:C109 C111:C127 C129:C145 C147:C163 C165:C181 C183:C199 C201:C217 C219:C235 C237:C253 C255:C271 C273:C289 C291:C307 C309:C325 C327:C343 C345:C361 C363:C379 C381:C397 C399:C415 C435:C451 C453:C469 C417:C433">
+  <conditionalFormatting sqref="C37 C19 C39:C55 C57:C73 C75:C91 C93:C109 C111:C127 C129:C145 C147:C163 C165:C181 C183:C199 C201:C217 C219:C235 C237:C253 C255:C271 C273:C289 C291:C307 C309:C325 C327:C343 C345:C361 C363:C379 C381:C397 C399:C415 C435:C451 C453:C469 C417:C433">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
